--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.228</v>
+        <v>8.5503</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7228</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.335655741784866</v>
+        <v>3.0328</v>
       </c>
       <c r="E2" t="n">
-        <v>88.38849999999999</v>
+        <v>8.5503</v>
       </c>
       <c r="F2" t="n">
-        <v>39.67594785625246</v>
+        <v>4.6011</v>
       </c>
       <c r="G2" t="n">
-        <v>48.71253466701766</v>
+        <v>3.9492</v>
       </c>
       <c r="H2" t="n">
-        <v>42.75706973558619</v>
+        <v>5.951</v>
       </c>
       <c r="I2" t="n">
-        <v>51.73964741112951</v>
+        <v>4.8234</v>
       </c>
       <c r="J2" t="n">
-        <v>48.71253466701766</v>
+        <v>3.9492</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -541,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>100.4522</v>
+        <v>8.772600000000001</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5774</v>
+        <v>5.5668</v>
       </c>
       <c r="C3" t="n">
-        <v>0.55774</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.533412774649087</v>
+        <v>1.8275</v>
       </c>
       <c r="E3" t="n">
-        <v>53.4815</v>
+        <v>5.5668</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.680442127431023</v>
+        <v>0.011</v>
       </c>
       <c r="G3" t="n">
-        <v>58.1618934759158</v>
+        <v>5.5558</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.680442127431023</v>
+        <v>0.011</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.663728288656028</v>
+        <v>0.0089</v>
       </c>
       <c r="J3" t="n">
-        <v>58.1618934759158</v>
+        <v>5.5558</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -587,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>52.4982</v>
+        <v>5.564699999999999</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -596,553 +584,553 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ArtFr0st</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.73</v>
+        <v>5.388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4730000000000001</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.199724187258691</v>
+        <v>1.7553</v>
       </c>
       <c r="E4" t="n">
-        <v>38.9621</v>
+        <v>5.388</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.050317042551957</v>
+        <v>4.0037</v>
       </c>
       <c r="G4" t="n">
-        <v>44.01237912883685</v>
+        <v>1.3843</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.050317042551957</v>
+        <v>4.0037</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.111308017877998</v>
+        <v>3.2451</v>
       </c>
       <c r="J4" t="n">
-        <v>44.01237912883685</v>
+        <v>1.3843</v>
       </c>
       <c r="K4" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M4" t="n">
-        <v>37.9011</v>
+        <v>4.6294</v>
       </c>
       <c r="N4" t="n">
-        <v>287</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6858</v>
+        <v>5.2428</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4685800000000001</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.183581331637487</v>
+        <v>1.6966</v>
       </c>
       <c r="E5" t="n">
-        <v>38.2597</v>
+        <v>5.2428</v>
       </c>
       <c r="F5" t="n">
-        <v>28.76430925734391</v>
+        <v>2.9241</v>
       </c>
       <c r="G5" t="n">
-        <v>9.49534821150781</v>
+        <v>2.3187</v>
       </c>
       <c r="H5" t="n">
-        <v>28.76430925734391</v>
+        <v>2.9241</v>
       </c>
       <c r="I5" t="n">
-        <v>23.20482091348752</v>
+        <v>2.37</v>
       </c>
       <c r="J5" t="n">
-        <v>9.49534821150781</v>
+        <v>2.3187</v>
       </c>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M5" t="n">
-        <v>32.7002</v>
+        <v>4.688700000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>133</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5749</v>
+        <v>4.2979</v>
       </c>
       <c r="C6" t="n">
-        <v>0.35749</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8145126116693915</v>
+        <v>1.3149</v>
       </c>
       <c r="E6" t="n">
-        <v>22.2008</v>
+        <v>4.2979</v>
       </c>
       <c r="F6" t="n">
-        <v>22.20081514635623</v>
+        <v>3.7355</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.5624</v>
       </c>
       <c r="H6" t="n">
-        <v>22.20081514635623</v>
+        <v>3.7355</v>
       </c>
       <c r="I6" t="n">
-        <v>27.23797488544546</v>
+        <v>3.0277</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5624</v>
       </c>
       <c r="K6" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>27.238</v>
+        <v>3.5901</v>
       </c>
       <c r="N6" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>danistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7984</v>
+        <v>4.1209</v>
       </c>
       <c r="C7" t="n">
-        <v>0.27984</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5942437000105312</v>
+        <v>1.2434</v>
       </c>
       <c r="E7" t="n">
-        <v>12.6165</v>
+        <v>4.1209</v>
       </c>
       <c r="F7" t="n">
-        <v>13.51110488520271</v>
+        <v>4.2576</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8945853713322425</v>
+        <v>-0.1367</v>
       </c>
       <c r="H7" t="n">
-        <v>13.51110488520271</v>
+        <v>4.5688</v>
       </c>
       <c r="I7" t="n">
-        <v>16.34957229806042</v>
+        <v>3.7031</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8945853713322425</v>
+        <v>-0.1367</v>
       </c>
       <c r="K7" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="L7" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>15.455</v>
+        <v>3.5664</v>
       </c>
       <c r="N7" t="n">
-        <v>287</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4829</v>
+        <v>3.794</v>
       </c>
       <c r="C8" t="n">
-        <v>0.24829</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5125790405437718</v>
+        <v>1.1113</v>
       </c>
       <c r="E8" t="n">
-        <v>9.0631</v>
+        <v>3.794</v>
       </c>
       <c r="F8" t="n">
-        <v>14.36196190803327</v>
+        <v>2.6479</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.298818279852457</v>
+        <v>1.1461</v>
       </c>
       <c r="H8" t="n">
-        <v>14.36196190803327</v>
+        <v>2.6479</v>
       </c>
       <c r="I8" t="n">
-        <v>13.8792068859145</v>
+        <v>2.1462</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.298818279852457</v>
+        <v>1.1461</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M8" t="n">
-        <v>8.580399999999999</v>
+        <v>3.2923</v>
       </c>
       <c r="N8" t="n">
-        <v>152</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>danistzz</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3925</v>
+        <v>3.5052</v>
       </c>
       <c r="C9" t="n">
-        <v>0.23925</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.489955598998988</v>
+        <v>0.9947</v>
       </c>
       <c r="E9" t="n">
-        <v>8.078799999999999</v>
+        <v>3.5052</v>
       </c>
       <c r="F9" t="n">
-        <v>25.8399250718926</v>
+        <v>3.2366</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.76116798449283</v>
+        <v>0.2686</v>
       </c>
       <c r="H9" t="n">
-        <v>25.8399250718926</v>
+        <v>3.2366</v>
       </c>
       <c r="I9" t="n">
-        <v>24.97135616191302</v>
+        <v>2.6234</v>
       </c>
       <c r="J9" t="n">
-        <v>-17.76116798449283</v>
+        <v>0.2686</v>
       </c>
       <c r="K9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>7.2102</v>
+        <v>2.892</v>
       </c>
       <c r="N9" t="n">
-        <v>152</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>ArtFr0st</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3542</v>
+        <v>3.4688</v>
       </c>
       <c r="C10" t="n">
-        <v>0.23542</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4804872949177854</v>
+        <v>0.98</v>
       </c>
       <c r="E10" t="n">
-        <v>7.6668</v>
+        <v>3.4688</v>
       </c>
       <c r="F10" t="n">
-        <v>35.03570808492127</v>
+        <v>-0.1398</v>
       </c>
       <c r="G10" t="n">
-        <v>-27.3689338995529</v>
+        <v>3.6086</v>
       </c>
       <c r="H10" t="n">
-        <v>36.07525143677978</v>
+        <v>-0.1398</v>
       </c>
       <c r="I10" t="n">
-        <v>29.10272384815848</v>
+        <v>-0.1133</v>
       </c>
       <c r="J10" t="n">
-        <v>-27.3689338995529</v>
+        <v>3.6086</v>
       </c>
       <c r="K10" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7338</v>
+        <v>3.4953</v>
       </c>
       <c r="N10" t="n">
-        <v>133</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6915</v>
+        <v>3.3503</v>
       </c>
       <c r="C11" t="n">
-        <v>0.16915</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3256757022947974</v>
+        <v>0.9321</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9306</v>
+        <v>3.3503</v>
       </c>
       <c r="F11" t="n">
-        <v>16.33176961432844</v>
+        <v>3.3503</v>
       </c>
       <c r="G11" t="n">
-        <v>-15.40112564298061</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>16.33176961432844</v>
+        <v>3.3503</v>
       </c>
       <c r="I11" t="n">
-        <v>16.05728609139855</v>
+        <v>3.3503</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.40112564298061</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="L11" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6562</v>
+        <v>3.3503</v>
       </c>
       <c r="N11" t="n">
-        <v>260</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5158</v>
+        <v>3.112</v>
       </c>
       <c r="C12" t="n">
-        <v>0.15158</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2874138348184173</v>
+        <v>0.8358</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7342</v>
+        <v>3.112</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7341985458411688</v>
+        <v>3.6239</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.5119</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7341985458411688</v>
+        <v>3.6239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7341985458411688</v>
+        <v>2.9372</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.5119</v>
       </c>
       <c r="K12" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7342</v>
+        <v>2.4253</v>
       </c>
       <c r="N12" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1606</v>
+        <v>3.0625</v>
       </c>
       <c r="C13" t="n">
-        <v>0.11606</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2134154923342211</v>
+        <v>0.8158</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.954</v>
+        <v>3.0625</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.953999221938704</v>
+        <v>3.726</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.6635</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.953999221938704</v>
+        <v>3.726</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.953999221938704</v>
+        <v>3.02</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.6635</v>
       </c>
       <c r="K13" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.954</v>
+        <v>2.3565</v>
       </c>
       <c r="N13" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0273</v>
+        <v>2.1054</v>
       </c>
       <c r="C14" t="n">
-        <v>0.10273</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1867429571854745</v>
+        <v>0.4292</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1146</v>
+        <v>2.1054</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.114569091777495</v>
+        <v>0.529</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.5763</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.114569091777495</v>
+        <v>0.529</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.974160535773713</v>
+        <v>0.4288</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.5763</v>
       </c>
       <c r="K14" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.9742</v>
+        <v>2.0051</v>
       </c>
       <c r="N14" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9563</v>
+        <v>1.7238</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09563000000000001</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1727776642159876</v>
+        <v>0.275</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.7222</v>
+        <v>1.7238</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.722224050463327</v>
+        <v>1.7238</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.722224050463327</v>
+        <v>1.7238</v>
       </c>
       <c r="I15" t="n">
-        <v>-7.020543793005428</v>
+        <v>1.7238</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.0205</v>
+        <v>1.7238</v>
       </c>
       <c r="N15" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
@@ -1152,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8409</v>
+        <v>1.6896</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08409</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1504550967020796</v>
+        <v>0.2612</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.6935</v>
+        <v>1.6896</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.693519022223862</v>
+        <v>1.6896</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.693519022223862</v>
+        <v>1.6896</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.818480202429553</v>
+        <v>1.6896</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1185,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.8185</v>
+        <v>1.6896</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1194,124 +1182,124 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7296</v>
+        <v>1.3268</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07296000000000001</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1293024152914583</v>
+        <v>0.1146</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.6139</v>
+        <v>1.3268</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.613910150197303</v>
+        <v>-0.5537</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.8805</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.613910150197303</v>
+        <v>-0.5537</v>
       </c>
       <c r="I17" t="n">
-        <v>-8.893558914936346</v>
+        <v>-0.4488</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.8805</v>
       </c>
       <c r="K17" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.893599999999999</v>
+        <v>1.4317</v>
       </c>
       <c r="N17" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6768</v>
+        <v>1.1298</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06768</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.119415632347178</v>
+        <v>0.0351</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.0441</v>
+        <v>1.1298</v>
       </c>
       <c r="F18" t="n">
-        <v>22.92334956946056</v>
+        <v>2.1298</v>
       </c>
       <c r="G18" t="n">
-        <v>-30.96745138800803</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>22.92334956946056</v>
+        <v>2.1298</v>
       </c>
       <c r="I18" t="n">
-        <v>18.49278620729591</v>
+        <v>1.7263</v>
       </c>
       <c r="J18" t="n">
-        <v>-30.96745138800803</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="L18" t="n">
         <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.4747</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.553</v>
+        <v>1.0774</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05530000000000001</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09655012917785105</v>
+        <v>0.0139</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.039</v>
+        <v>1.0774</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.039020895006956</v>
+        <v>1.0774</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.039020895006956</v>
+        <v>1.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-11.08989118210938</v>
+        <v>1.0774</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.0899</v>
+        <v>1.0774</v>
       </c>
       <c r="N19" t="n">
         <v>146</v>
@@ -1332,78 +1320,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3897</v>
+        <v>1.0221</v>
       </c>
       <c r="C20" t="n">
-        <v>0.03897</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06710631648986137</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.3202</v>
+        <v>1.0221</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.32017402380745</v>
+        <v>1.0221</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.32017402380745</v>
+        <v>1.0221</v>
       </c>
       <c r="I20" t="n">
-        <v>-10.32017402380745</v>
+        <v>1.0221</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-10.3202</v>
+        <v>1.0221</v>
       </c>
       <c r="N20" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4821</v>
+        <v>0.9558</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.04821</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08365781908286342</v>
+        <v>-0.0352</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.8802</v>
+        <v>0.9558</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.8801921181586</v>
+        <v>0.9558</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-16.8801921181586</v>
+        <v>0.9558</v>
       </c>
       <c r="I21" t="n">
-        <v>-19.71719919684072</v>
+        <v>0.9558</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1415,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-19.7172</v>
+        <v>0.9558</v>
       </c>
       <c r="N21" t="n">
         <v>139</v>
@@ -1424,584 +1412,584 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.6052</v>
+        <v>0.8711</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.06052</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.106131904584715</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-17.8581</v>
+        <v>0.8711</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.85807990948298</v>
+        <v>0.8711</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-17.85807990948298</v>
+        <v>0.8711</v>
       </c>
       <c r="I22" t="n">
-        <v>-20.85943787746331</v>
+        <v>0.8711</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-20.8594</v>
+        <v>0.8711</v>
       </c>
       <c r="N22" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.3061</v>
+        <v>0.7877</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.13061</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2431952068477552</v>
+        <v>-0.1031</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.822</v>
+        <v>0.7877</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.822137002092306</v>
+        <v>0.7877</v>
       </c>
       <c r="G23" t="n">
-        <v>-15.99981315744323</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.822137002092306</v>
+        <v>0.7877</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.690672514662182</v>
+        <v>0.7877</v>
       </c>
       <c r="J23" t="n">
-        <v>-15.99981315744323</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="L23" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-23.6905</v>
+        <v>0.7877</v>
       </c>
       <c r="N23" t="n">
-        <v>260</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.9941</v>
+        <v>0.5379</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.19941</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3942380216072734</v>
+        <v>-0.2041</v>
       </c>
       <c r="E24" t="n">
-        <v>-30.3941</v>
+        <v>0.5379</v>
       </c>
       <c r="F24" t="n">
-        <v>20.91908492306801</v>
+        <v>0.5379</v>
       </c>
       <c r="G24" t="n">
-        <v>-51.31317900847915</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>20.91908492306801</v>
+        <v>0.5379</v>
       </c>
       <c r="I24" t="n">
-        <v>20.56750366385678</v>
+        <v>0.5379</v>
       </c>
       <c r="J24" t="n">
-        <v>-51.31317900847915</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L24" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-30.7457</v>
+        <v>0.5379</v>
       </c>
       <c r="N24" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2.0935</v>
+        <v>0.3473</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.20935</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4175295563264493</v>
+        <v>-0.2811</v>
       </c>
       <c r="E25" t="n">
-        <v>-31.4076</v>
+        <v>0.3473</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.40755055914456</v>
+        <v>0.3473</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-31.40755055914456</v>
+        <v>0.3473</v>
       </c>
       <c r="I25" t="n">
-        <v>-38.53363345911853</v>
+        <v>0.3473</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-38.5336</v>
+        <v>0.3473</v>
       </c>
       <c r="N25" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.096</v>
+        <v>0.1942</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2096</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4181307301810725</v>
+        <v>-0.3429</v>
       </c>
       <c r="E26" t="n">
-        <v>-31.4337</v>
+        <v>0.1942</v>
       </c>
       <c r="F26" t="n">
-        <v>-31.43370871240294</v>
+        <v>1.1942</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>-31.43370871240294</v>
+        <v>1.1942</v>
       </c>
       <c r="I26" t="n">
-        <v>-31.43370871240294</v>
+        <v>0.9679</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K26" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>-31.4337</v>
+        <v>-0.03210000000000002</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.2561</v>
+        <v>-0.1502</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.22561</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4564635517244318</v>
+        <v>-0.482</v>
       </c>
       <c r="E27" t="n">
-        <v>-33.1016</v>
+        <v>-0.1502</v>
       </c>
       <c r="F27" t="n">
-        <v>-33.10163856837767</v>
+        <v>0.8498</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>-33.10163856837767</v>
+        <v>0.8498</v>
       </c>
       <c r="I27" t="n">
-        <v>-21.14054227896389</v>
+        <v>0.6888</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>-21.1405</v>
+        <v>-0.3112</v>
       </c>
       <c r="N27" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.4678</v>
+        <v>-0.4374</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.24678</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5087716231748156</v>
+        <v>-0.5981</v>
       </c>
       <c r="E28" t="n">
-        <v>-35.3777</v>
+        <v>-0.4374</v>
       </c>
       <c r="F28" t="n">
-        <v>5.758126717627224</v>
+        <v>-0.4374</v>
       </c>
       <c r="G28" t="n">
-        <v>-41.13578334488606</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>5.758126717627224</v>
+        <v>-0.4374</v>
       </c>
       <c r="I28" t="n">
-        <v>5.661351478675506</v>
+        <v>-0.4374</v>
       </c>
       <c r="J28" t="n">
-        <v>-41.13578334488606</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-35.4744</v>
+        <v>-0.4374</v>
       </c>
       <c r="N28" t="n">
-        <v>260</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.8102</v>
+        <v>-0.4538</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.28102</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5973910158171951</v>
+        <v>-0.6047</v>
       </c>
       <c r="E29" t="n">
-        <v>-39.2336</v>
+        <v>-0.4538</v>
       </c>
       <c r="F29" t="n">
-        <v>-39.2336454341193</v>
+        <v>-0.4538</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-39.2336454341193</v>
+        <v>-0.4538</v>
       </c>
       <c r="I29" t="n">
-        <v>-39.2336454341193</v>
+        <v>-0.4538</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-39.2336</v>
+        <v>-0.4538</v>
       </c>
       <c r="N29" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.8612</v>
+        <v>-0.4989</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.28612</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6110131878989996</v>
+        <v>-0.6229</v>
       </c>
       <c r="E30" t="n">
-        <v>-39.8264</v>
+        <v>-0.4989</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4833024895909024</v>
+        <v>-0.4989</v>
       </c>
       <c r="G30" t="n">
-        <v>-40.30967307682128</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4833024895909024</v>
+        <v>-0.4989</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3898910840397196</v>
+        <v>-0.4989</v>
       </c>
       <c r="J30" t="n">
-        <v>-40.30967307682128</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L30" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-39.9198</v>
+        <v>-0.4989</v>
       </c>
       <c r="N30" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.9175</v>
+        <v>-0.5672</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.29175</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6262116904012568</v>
+        <v>-0.6505</v>
       </c>
       <c r="E31" t="n">
-        <v>-40.4877</v>
+        <v>-0.5672</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2703718172778659</v>
+        <v>-0.5672</v>
       </c>
       <c r="G31" t="n">
-        <v>-40.21731288848008</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2703718172778659</v>
+        <v>-0.5672</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2612836889660048</v>
+        <v>-0.5672</v>
       </c>
       <c r="J31" t="n">
-        <v>-40.21731288848008</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L31" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-40.4786</v>
+        <v>-0.5672</v>
       </c>
       <c r="N31" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-3.0289</v>
+        <v>-0.8045</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.30289</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6566833301635164</v>
+        <v>-0.7464</v>
       </c>
       <c r="E32" t="n">
-        <v>-41.8136</v>
+        <v>-0.8045</v>
       </c>
       <c r="F32" t="n">
-        <v>-41.81356043505929</v>
+        <v>0.2125</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-1.017</v>
       </c>
       <c r="H32" t="n">
-        <v>-41.81356043505929</v>
+        <v>0.2125</v>
       </c>
       <c r="I32" t="n">
-        <v>-26.70445876524795</v>
+        <v>0.1722</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-1.017</v>
       </c>
       <c r="K32" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M32" t="n">
-        <v>-26.7045</v>
+        <v>-0.8447999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.0848</v>
+        <v>-0.8582</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.30848</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6721997514321767</v>
+        <v>-0.7681</v>
       </c>
       <c r="E33" t="n">
-        <v>-42.4887</v>
+        <v>-0.8582</v>
       </c>
       <c r="F33" t="n">
-        <v>3.526741289253188</v>
+        <v>-0.8582</v>
       </c>
       <c r="G33" t="n">
-        <v>-46.01544905889118</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.526741289253188</v>
+        <v>-0.8582</v>
       </c>
       <c r="I33" t="n">
-        <v>2.845102216540387</v>
+        <v>-0.8582</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.01544905889118</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-43.1703</v>
+        <v>-0.8582</v>
       </c>
       <c r="N33" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.1052</v>
+        <v>-0.8711</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.31052</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6778764420421722</v>
+        <v>-0.7733</v>
       </c>
       <c r="E34" t="n">
-        <v>-42.7357</v>
+        <v>-0.8711</v>
       </c>
       <c r="F34" t="n">
-        <v>-42.73571076525189</v>
+        <v>-0.8711</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-42.73571076525189</v>
+        <v>-0.8711</v>
       </c>
       <c r="I34" t="n">
-        <v>-27.29339511058104</v>
+        <v>-0.8711</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2013,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-27.2934</v>
+        <v>-0.8711</v>
       </c>
       <c r="N34" t="n">
         <v>76</v>
@@ -2022,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.1489</v>
+        <v>-0.8864</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.31489</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6901524411873844</v>
+        <v>-0.7794</v>
       </c>
       <c r="E35" t="n">
-        <v>-43.2699</v>
+        <v>-0.8864</v>
       </c>
       <c r="F35" t="n">
-        <v>-43.2698615181011</v>
+        <v>-0.0507</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.8357</v>
       </c>
       <c r="H35" t="n">
-        <v>-43.2698615181011</v>
+        <v>-0.0507</v>
       </c>
       <c r="I35" t="n">
-        <v>-27.63453340651835</v>
+        <v>-0.0411</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.8357</v>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M35" t="n">
-        <v>-27.6345</v>
+        <v>-0.8768</v>
       </c>
       <c r="N35" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.3903</v>
+        <v>-1.0011</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.33903</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7595266459806761</v>
+        <v>-0.8258</v>
       </c>
       <c r="E36" t="n">
-        <v>-46.2885</v>
+        <v>-1.0011</v>
       </c>
       <c r="F36" t="n">
-        <v>-13.26700073242972</v>
+        <v>-1.0011</v>
       </c>
       <c r="G36" t="n">
-        <v>-33.02145693253608</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-13.26700073242972</v>
+        <v>-1.0011</v>
       </c>
       <c r="I36" t="n">
-        <v>-12.8210511279783</v>
+        <v>-1.0011</v>
       </c>
       <c r="J36" t="n">
-        <v>-33.02145693253608</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="L36" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-45.8425</v>
+        <v>-1.0011</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-4.1357</v>
+        <v>-1.2715</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.41357</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9922977184163285</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-56.4167</v>
+        <v>-1.2715</v>
       </c>
       <c r="F37" t="n">
-        <v>-56.41674474875189</v>
+        <v>-1.2715</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-56.41674474875189</v>
+        <v>-1.2715</v>
       </c>
       <c r="I37" t="n">
-        <v>-69.21718263292249</v>
+        <v>-1.2715</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-69.21720000000001</v>
+        <v>-1.2715</v>
       </c>
       <c r="N37" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38">
@@ -2164,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.4557</v>
+        <v>-1.6703</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.44557</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.101426986499582</v>
+        <v>-1.0961</v>
       </c>
       <c r="E38" t="n">
-        <v>-61.1652</v>
+        <v>-1.6703</v>
       </c>
       <c r="F38" t="n">
-        <v>-61.16515504228695</v>
+        <v>-1.6703</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-61.16515504228695</v>
+        <v>-1.6703</v>
       </c>
       <c r="I38" t="n">
-        <v>-39.06346036314124</v>
+        <v>-1.6703</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-39.0635</v>
+        <v>-1.6703</v>
       </c>
       <c r="N38" t="n">
         <v>76</v>
@@ -2206,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.4931</v>
+        <v>-2.5455</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.44931</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.114574739080533</v>
+        <v>-1.4497</v>
       </c>
       <c r="E39" t="n">
-        <v>-61.7372</v>
+        <v>-2.5455</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8340798045968196</v>
+        <v>-1.7465</v>
       </c>
       <c r="G39" t="n">
-        <v>-62.57131715613751</v>
+        <v>-0.799</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8340798045968196</v>
+        <v>-1.7465</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8200616566204024</v>
+        <v>-1.4156</v>
       </c>
       <c r="J39" t="n">
-        <v>-62.57131715613751</v>
+        <v>-0.799</v>
       </c>
       <c r="K39" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L39" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>-61.7513</v>
+        <v>-2.2146</v>
       </c>
       <c r="N39" t="n">
-        <v>260</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.624</v>
+        <v>-3.1565</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4624</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.161205675244653</v>
+        <v>-1.6965</v>
       </c>
       <c r="E40" t="n">
-        <v>-63.7662</v>
+        <v>-3.1565</v>
       </c>
       <c r="F40" t="n">
-        <v>-31.78875744879784</v>
+        <v>-3.1565</v>
       </c>
       <c r="G40" t="n">
-        <v>-31.97747561734768</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-31.78875744879784</v>
+        <v>-3.1565</v>
       </c>
       <c r="I40" t="n">
-        <v>-30.72022778665337</v>
+        <v>-3.1565</v>
       </c>
       <c r="J40" t="n">
-        <v>-31.97747561734768</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L40" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-62.6977</v>
+        <v>-3.1565</v>
       </c>
       <c r="N40" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
@@ -2302,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.5331</v>
+        <v>-3.5035</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5533100000000001</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.514790006672349</v>
+        <v>-1.8367</v>
       </c>
       <c r="E41" t="n">
-        <v>-79.15130000000001</v>
+        <v>-3.5035</v>
       </c>
       <c r="F41" t="n">
-        <v>-23.38913412745286</v>
+        <v>-3.2791</v>
       </c>
       <c r="G41" t="n">
-        <v>-55.76218772810082</v>
+        <v>-0.2244</v>
       </c>
       <c r="H41" t="n">
-        <v>-23.38913412745286</v>
+        <v>-3.2791</v>
       </c>
       <c r="I41" t="n">
-        <v>-28.30281776767405</v>
+        <v>-2.6578</v>
       </c>
       <c r="J41" t="n">
-        <v>-55.76218772810082</v>
+        <v>-0.2244</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2335,7 +2323,7 @@
         <v>143</v>
       </c>
       <c r="M41" t="n">
-        <v>-84.065</v>
+        <v>-2.8822</v>
       </c>
       <c r="N41" t="n">
         <v>287</v>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9297944567491098</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>19.5256835917313</v>
+        <v>15.2943</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9193047629678864</v>
+        <v>0.7169</v>
       </c>
       <c r="J3" t="n">
-        <v>19.30540002232561</v>
+        <v>15.0549</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01674724803206259</v>
+        <v>-0.1595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3516922086733145</v>
+        <v>-3.3495</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.93</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07272545997206482</v>
+        <v>-0.2146</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.527234659413361</v>
+        <v>-4.5066</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4280487250896762</v>
+        <v>-0.3412</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.9890232268832</v>
+        <v>-7.1652</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1225925033479975</v>
+        <v>0.1477</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.574442570307947</v>
+        <v>3.1017</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1534017413443046</v>
+        <v>0.1252</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.221436568230398</v>
+        <v>2.6292</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6372100521666633</v>
+        <v>-0.195</v>
       </c>
       <c r="J9" t="n">
-        <v>-13.38141109549993</v>
+        <v>-4.095</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.760322314753158</v>
+        <v>-0.2413</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.96676860981632</v>
+        <v>-5.0673</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.564839535423658</v>
+        <v>-0.6737</v>
       </c>
       <c r="J11" t="n">
-        <v>-32.86163024389682</v>
+        <v>-14.1477</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0.908169181005847</v>
+        <v>0.7749</v>
       </c>
       <c r="J12" t="n">
-        <v>19.97972198212863</v>
+        <v>17.0478</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3995219752546556</v>
+        <v>0.3144</v>
       </c>
       <c r="J13" t="n">
-        <v>8.789483455602424</v>
+        <v>6.9168</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2577481169512698</v>
+        <v>0.2233</v>
       </c>
       <c r="J14" t="n">
-        <v>5.670458572927936</v>
+        <v>4.9126</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2577481169512698</v>
+        <v>0.2233</v>
       </c>
       <c r="J15" t="n">
-        <v>5.670458572927936</v>
+        <v>4.9126</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6181665666712066</v>
+        <v>-0.3322</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.59966446676655</v>
+        <v>-7.3084</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2505651379441219</v>
+        <v>0.4114</v>
       </c>
       <c r="J17" t="n">
-        <v>5.512433034770683</v>
+        <v>9.050800000000001</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.110081081067917</v>
+        <v>0.1869</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.421783783494173</v>
+        <v>4.1118</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2055483728561619</v>
+        <v>0.1266</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.522064202835561</v>
+        <v>2.7852</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.73</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.239771169796179</v>
+        <v>-0.4636</v>
       </c>
       <c r="J20" t="n">
-        <v>-27.27496573551593</v>
+        <v>-10.1992</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5391952824346</v>
+        <v>-0.6459</v>
       </c>
       <c r="J21" t="n">
-        <v>-33.86229621356119</v>
+        <v>-14.2098</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5852148069405877</v>
+        <v>0.2713</v>
       </c>
       <c r="J22" t="n">
-        <v>-9.363436911049403</v>
+        <v>4.3408</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7280972867727314</v>
+        <v>0.1467</v>
       </c>
       <c r="J23" t="n">
-        <v>-11.6495565883637</v>
+        <v>2.3472</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.797341320933553</v>
+        <v>-0.4687</v>
       </c>
       <c r="J24" t="n">
-        <v>-28.75746113493685</v>
+        <v>-7.4992</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.915498433126697</v>
+        <v>-0.5273</v>
       </c>
       <c r="J25" t="n">
-        <v>-30.64797493002715</v>
+        <v>-8.4368</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.512092288960512</v>
+        <v>-0.8717</v>
       </c>
       <c r="J26" t="n">
-        <v>-40.1934766233682</v>
+        <v>-13.9472</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.91</v>
       </c>
       <c r="I27" t="n">
-        <v>1.41040752437869</v>
+        <v>1.832</v>
       </c>
       <c r="J27" t="n">
-        <v>22.56652039005903</v>
+        <v>29.312</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9770808576785521</v>
+        <v>1.2238</v>
       </c>
       <c r="J28" t="n">
-        <v>15.63329372285683</v>
+        <v>19.5808</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6887022401887696</v>
+        <v>0.9455</v>
       </c>
       <c r="J29" t="n">
-        <v>11.01923584302031</v>
+        <v>15.128</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5564981816829694</v>
+        <v>0.7754</v>
       </c>
       <c r="J30" t="n">
-        <v>8.90397090692751</v>
+        <v>12.4064</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4405653219907177</v>
+        <v>0.6037</v>
       </c>
       <c r="J31" t="n">
-        <v>7.049045151851484</v>
+        <v>9.6592</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3853492573841649</v>
+        <v>0.1911</v>
       </c>
       <c r="J32" t="n">
-        <v>-6.936286632914967</v>
+        <v>3.4398</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4648730048855539</v>
+        <v>0.1096</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.367714087939971</v>
+        <v>1.9728</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6851987390054574</v>
+        <v>-0.0698</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.33357730209823</v>
+        <v>-1.2564</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.48</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.093631642282882</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-37.68536956109188</v>
+        <v>-13.545</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.255270041798373</v>
+        <v>-0.849</v>
       </c>
       <c r="J36" t="n">
-        <v>-40.59486075237071</v>
+        <v>-15.282</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.079351771323936</v>
+        <v>1.2554</v>
       </c>
       <c r="J37" t="n">
-        <v>19.42833188383084</v>
+        <v>22.5972</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.51</v>
       </c>
       <c r="I38" t="n">
-        <v>1.024602950796954</v>
+        <v>1.1755</v>
       </c>
       <c r="J38" t="n">
-        <v>18.44285311434517</v>
+        <v>21.159</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.44</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9179048485464045</v>
+        <v>1.0295</v>
       </c>
       <c r="J39" t="n">
-        <v>16.52228727383528</v>
+        <v>18.531</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2542718919145976</v>
+        <v>0.1819</v>
       </c>
       <c r="J40" t="n">
-        <v>4.576894054462756</v>
+        <v>3.2742</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2393915825779211</v>
+        <v>0.1541</v>
       </c>
       <c r="J41" t="n">
-        <v>4.309048486402581</v>
+        <v>2.7738</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2754636811489833</v>
+        <v>0.3701</v>
       </c>
       <c r="J42" t="n">
-        <v>7.988446753320517</v>
+        <v>10.7329</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.6467251686223437</v>
+        <v>-0.1556</v>
       </c>
       <c r="J43" t="n">
-        <v>-18.75502989004797</v>
+        <v>-4.5124</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6467251686223437</v>
+        <v>-0.1556</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.75502989004797</v>
+        <v>-4.5124</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8519327516946892</v>
+        <v>-0.247</v>
       </c>
       <c r="J45" t="n">
-        <v>-24.70604979914599</v>
+        <v>-7.163</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9233847440162092</v>
+        <v>-0.2801</v>
       </c>
       <c r="J46" t="n">
-        <v>-26.77815757647006</v>
+        <v>-8.1229</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7787705436347707</v>
+        <v>0.98</v>
       </c>
       <c r="J47" t="n">
-        <v>22.58434576540835</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4972375557192384</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>14.41988911585791</v>
+        <v>16.7649</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4341310555022714</v>
+        <v>0.4971</v>
       </c>
       <c r="J49" t="n">
-        <v>12.58980060956587</v>
+        <v>14.4159</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.04637408362382682</v>
+        <v>-0.1415</v>
       </c>
       <c r="J50" t="n">
-        <v>-1.344848425090978</v>
+        <v>-4.1035</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.663715494222231</v>
+        <v>-0.6548</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.2477493324447</v>
+        <v>-18.9892</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3589825012130665</v>
+        <v>0.5927</v>
       </c>
       <c r="J52" t="n">
-        <v>7.538632525474395</v>
+        <v>12.4467</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.08755052063669293</v>
+        <v>0.1113</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.838560933370551</v>
+        <v>2.3373</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.7583343219548724</v>
+        <v>-0.3571</v>
       </c>
       <c r="J54" t="n">
-        <v>-15.92502076105232</v>
+        <v>-7.4991</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8855836401336999</v>
+        <v>-0.445</v>
       </c>
       <c r="J55" t="n">
-        <v>-18.5972564428077</v>
+        <v>-9.345000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.084426199921825</v>
+        <v>-0.5923</v>
       </c>
       <c r="J56" t="n">
-        <v>-22.77295019835833</v>
+        <v>-12.4383</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5137105762393258</v>
+        <v>0.8123</v>
       </c>
       <c r="J57" t="n">
-        <v>10.78792210102584</v>
+        <v>17.0583</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1939988412970613</v>
+        <v>0.1839</v>
       </c>
       <c r="J58" t="n">
-        <v>4.073975667238288</v>
+        <v>3.8619</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1764803023686373</v>
+        <v>0.1482</v>
       </c>
       <c r="J59" t="n">
-        <v>3.706086349741383</v>
+        <v>3.1122</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.143858292961223</v>
+        <v>0.0742</v>
       </c>
       <c r="J60" t="n">
-        <v>3.021024152185683</v>
+        <v>1.5582</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.99</v>
       </c>
       <c r="I61" t="n">
-        <v>0.08299314735428667</v>
+        <v>-0.1301</v>
       </c>
       <c r="J61" t="n">
-        <v>1.74285609444002</v>
+        <v>-2.7321</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1222947303770884</v>
+        <v>0.7916</v>
       </c>
       <c r="J62" t="n">
-        <v>1.956715686033415</v>
+        <v>12.6656</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.512156324353106</v>
+        <v>0.0804</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.194501189649696</v>
+        <v>1.2864</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>0.51</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.52404076973556</v>
+        <v>-0.7125</v>
       </c>
       <c r="J64" t="n">
-        <v>-24.38465231576896</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.595648310386397</v>
+        <v>-0.7748</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.53037296618235</v>
+        <v>-12.3968</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.37</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.713637038505218</v>
+        <v>-0.8825</v>
       </c>
       <c r="J66" t="n">
-        <v>-27.41819261608348</v>
+        <v>-14.12</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9120590991762693</v>
+        <v>1.7465</v>
       </c>
       <c r="J67" t="n">
-        <v>14.59294558682031</v>
+        <v>27.944</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.78</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8467588792313968</v>
+        <v>1.6135</v>
       </c>
       <c r="J68" t="n">
-        <v>13.54814206770235</v>
+        <v>25.816</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1.53</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5992203892573366</v>
+        <v>1.1278</v>
       </c>
       <c r="J69" t="n">
-        <v>9.587526228117385</v>
+        <v>18.0448</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3231997129047572</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>5.171195406476116</v>
+        <v>10.4592</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.06998799663057462</v>
+        <v>-0.0708</v>
       </c>
       <c r="J71" t="n">
-        <v>1.119807946089194</v>
+        <v>-1.1328</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4176834091944739</v>
+        <v>0.8216</v>
       </c>
       <c r="J72" t="n">
-        <v>7.518301365500531</v>
+        <v>14.7888</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9752619850810476</v>
+        <v>-0.476</v>
       </c>
       <c r="J73" t="n">
-        <v>-17.55471573145886</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.009790775448926</v>
+        <v>-0.5043</v>
       </c>
       <c r="J74" t="n">
-        <v>-18.17623395808067</v>
+        <v>-9.077400000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.074684180163609</v>
+        <v>-0.5592</v>
       </c>
       <c r="J75" t="n">
-        <v>-19.34431524294497</v>
+        <v>-10.0656</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.163802858556484</v>
+        <v>-0.638</v>
       </c>
       <c r="J76" t="n">
-        <v>-20.94845145401671</v>
+        <v>-11.484</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9864324294154564</v>
+        <v>1.7826</v>
       </c>
       <c r="J77" t="n">
-        <v>17.75578372947821</v>
+        <v>32.0868</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5064246059732757</v>
+        <v>0.7652</v>
       </c>
       <c r="J78" t="n">
-        <v>9.115642907518962</v>
+        <v>13.7736</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2754374794733821</v>
+        <v>0.3891</v>
       </c>
       <c r="J79" t="n">
-        <v>4.957874630520878</v>
+        <v>7.0038</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2275563424534903</v>
+        <v>0.2841</v>
       </c>
       <c r="J80" t="n">
-        <v>4.096014164162825</v>
+        <v>5.1138</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01499202918704003</v>
+        <v>-0.3835</v>
       </c>
       <c r="J81" t="n">
-        <v>0.2698565253667206</v>
+        <v>-6.903</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.25</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1677517615538884</v>
+        <v>0.5013</v>
       </c>
       <c r="J82" t="n">
-        <v>3.187283469523879</v>
+        <v>9.524699999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.6745852444922625</v>
+        <v>-0.2592</v>
       </c>
       <c r="J83" t="n">
-        <v>-12.81711964535299</v>
+        <v>-4.9248</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.7263811399614212</v>
+        <v>-0.2947</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.801241659267</v>
+        <v>-5.5993</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.814039010583012</v>
+        <v>-0.3597</v>
       </c>
       <c r="J85" t="n">
-        <v>-15.46674120107723</v>
+        <v>-6.8343</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.098578823449216</v>
+        <v>-0.5976</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.87299764553511</v>
+        <v>-11.3544</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7727924238216786</v>
+        <v>1.3424</v>
       </c>
       <c r="J87" t="n">
-        <v>14.68305605261189</v>
+        <v>25.5056</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7133131539211026</v>
+        <v>1.2045</v>
       </c>
       <c r="J88" t="n">
-        <v>13.55294992450095</v>
+        <v>22.8855</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>1.42</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6376105058348609</v>
+        <v>1.0396</v>
       </c>
       <c r="J89" t="n">
-        <v>12.11459961086236</v>
+        <v>19.7524</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2436193957518407</v>
+        <v>0.3576</v>
       </c>
       <c r="J90" t="n">
-        <v>4.628768519284972</v>
+        <v>6.7944</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8019581842597813</v>
+        <v>-1.2883</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.23720550093584</v>
+        <v>-24.4777</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.89</v>
       </c>
       <c r="I92" t="n">
-        <v>0.7529798264169301</v>
+        <v>1.9555</v>
       </c>
       <c r="J92" t="n">
-        <v>21.08343513967404</v>
+        <v>54.754</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2393523212673562</v>
+        <v>0.4317</v>
       </c>
       <c r="J93" t="n">
-        <v>6.701864995485974</v>
+        <v>12.0876</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1504153842308482</v>
+        <v>0.2589</v>
       </c>
       <c r="J94" t="n">
-        <v>4.211630758463749</v>
+        <v>7.2492</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2864984355624955</v>
+        <v>-0.8698</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.021956195749874</v>
+        <v>-24.3544</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.72</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2950981617314972</v>
+        <v>-0.8923</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.262748528481922</v>
+        <v>-24.9844</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.11</v>
       </c>
       <c r="I97" t="n">
-        <v>0.06125052235629763</v>
+        <v>0.2802</v>
       </c>
       <c r="J97" t="n">
-        <v>1.715014625976333</v>
+        <v>7.8456</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0486681266757903</v>
+        <v>0.2637</v>
       </c>
       <c r="J98" t="n">
-        <v>1.362707546922128</v>
+        <v>7.3836</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>0.82</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4057394170604909</v>
+        <v>-0.3268</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.36070367769375</v>
+        <v>-9.150399999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4820767309433162</v>
+        <v>-0.417</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.49814846641285</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5053041662867107</v>
+        <v>-0.4455</v>
       </c>
       <c r="J101" t="n">
-        <v>-14.1485166560279</v>
+        <v>-12.474</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6406279314589255</v>
+        <v>1.5995</v>
       </c>
       <c r="J102" t="n">
-        <v>13.45318656063744</v>
+        <v>33.5895</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6057101872438487</v>
+        <v>1.4895</v>
       </c>
       <c r="J103" t="n">
-        <v>12.71991393212082</v>
+        <v>31.2795</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.41</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4264701763407686</v>
+        <v>0.9923</v>
       </c>
       <c r="J104" t="n">
-        <v>8.95587370315614</v>
+        <v>20.8383</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.07463877974218835</v>
+        <v>0.1998</v>
       </c>
       <c r="J105" t="n">
-        <v>1.567414374585955</v>
+        <v>4.1958</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.54</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4511071054347422</v>
+        <v>-1.2947</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.473249214129586</v>
+        <v>-27.1887</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1010693844144534</v>
+        <v>0.5164</v>
       </c>
       <c r="J107" t="n">
-        <v>2.122457072703521</v>
+        <v>10.8444</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2230177020533675</v>
+        <v>-0.0567</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.683371743120716</v>
+        <v>-1.1907</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4381842933701287</v>
+        <v>-0.2927</v>
       </c>
       <c r="J109" t="n">
-        <v>-9.201870160772703</v>
+        <v>-6.1467</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5456100286200249</v>
+        <v>-0.4187</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.45781060102052</v>
+        <v>-8.7927</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7593114600844173</v>
+        <v>-0.7095</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.94554066177276</v>
+        <v>-14.8995</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4106797788698985</v>
+        <v>1.0286</v>
       </c>
       <c r="J112" t="n">
-        <v>9.445634914007666</v>
+        <v>23.6578</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.32</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3554514501059174</v>
+        <v>0.875</v>
       </c>
       <c r="J113" t="n">
-        <v>8.175383352436102</v>
+        <v>20.125</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1021046701187311</v>
+        <v>0.3065</v>
       </c>
       <c r="J114" t="n">
-        <v>2.348407412730814</v>
+        <v>7.0495</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.02</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.01748967131186051</v>
+        <v>0.0058</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.4022624401727918</v>
+        <v>0.1334</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2700360071156337</v>
+        <v>-0.6392</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.210828163659575</v>
+        <v>-14.7016</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1842051158319564</v>
+        <v>0.472</v>
       </c>
       <c r="J117" t="n">
-        <v>4.236717664134996</v>
+        <v>10.856</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.02</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1145859193454191</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.63547614494464</v>
+        <v>1.7342</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1761042093370297</v>
+        <v>-0.0262</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.050396814751683</v>
+        <v>-0.6026</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.92</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.313452164031283</v>
+        <v>-0.1877</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.209399772719509</v>
+        <v>-4.3171</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.52561127321034</v>
+        <v>-0.4644</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.08905928383782</v>
+        <v>-10.6812</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6414581604951777</v>
+        <v>1.5111</v>
       </c>
       <c r="J122" t="n">
-        <v>11.5462468889132</v>
+        <v>27.1998</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4075044535224421</v>
+        <v>0.8834</v>
       </c>
       <c r="J123" t="n">
-        <v>7.335080163403958</v>
+        <v>15.9012</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3965086924579159</v>
+        <v>0.8597</v>
       </c>
       <c r="J124" t="n">
-        <v>7.137156464242486</v>
+        <v>15.4746</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>1.34</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3722691833641448</v>
+        <v>0.8105</v>
       </c>
       <c r="J125" t="n">
-        <v>6.700845300554607</v>
+        <v>14.589</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.15190187471508</v>
+        <v>-0.6363</v>
       </c>
       <c r="J126" t="n">
-        <v>-2.73423374487144</v>
+        <v>-11.4534</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2656344857531683</v>
+        <v>0.8702</v>
       </c>
       <c r="J127" t="n">
-        <v>4.781420743557029</v>
+        <v>15.6636</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.478282016892691</v>
+        <v>-0.2579</v>
       </c>
       <c r="J128" t="n">
-        <v>-8.609076304068438</v>
+        <v>-4.6422</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>0.71</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.6563817005136789</v>
+        <v>-0.4766</v>
       </c>
       <c r="J129" t="n">
-        <v>-11.81487060924622</v>
+        <v>-8.578799999999999</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6666144803187063</v>
+        <v>-0.4905</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.99906064573671</v>
+        <v>-8.829000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8254509449844911</v>
+        <v>-0.7219</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.85811700972084</v>
+        <v>-12.9942</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.44</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3738246512491001</v>
+        <v>0.6813</v>
       </c>
       <c r="J132" t="n">
-        <v>13.4576874449676</v>
+        <v>24.5268</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1125828681577499</v>
+        <v>0.2952</v>
       </c>
       <c r="J133" t="n">
-        <v>4.052983253678997</v>
+        <v>10.6272</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.01739507036873841</v>
+        <v>0.1949</v>
       </c>
       <c r="J134" t="n">
-        <v>0.6262225332745827</v>
+        <v>7.0164</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4123250099774156</v>
+        <v>-0.4338</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.84370035918696</v>
+        <v>-15.6168</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4371828270042704</v>
+        <v>-0.4744</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.73858177215373</v>
+        <v>-17.0784</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.325270093268159</v>
+        <v>0.9646</v>
       </c>
       <c r="J137" t="n">
-        <v>11.70972335765373</v>
+        <v>34.7256</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2236714348787722</v>
+        <v>0.6622</v>
       </c>
       <c r="J138" t="n">
-        <v>8.052171655635799</v>
+        <v>23.8392</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2053464876055468</v>
+        <v>0.6116</v>
       </c>
       <c r="J139" t="n">
-        <v>7.392473553799684</v>
+        <v>22.0176</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>1.11</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1043159138667389</v>
+        <v>0.3578</v>
       </c>
       <c r="J140" t="n">
-        <v>3.7553728992026</v>
+        <v>12.8808</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5533678927510232</v>
+        <v>-1.1854</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.92124413903683</v>
+        <v>-42.6744</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.007343483400851828</v>
+        <v>0.4014</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.1321827012153329</v>
+        <v>7.2252</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1216236663689878</v>
+        <v>0.2029</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.18922599464178</v>
+        <v>3.6522</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.88</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2982576715275002</v>
+        <v>-0.1734</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.368638087495003</v>
+        <v>-3.1212</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.57702307542867</v>
+        <v>-0.55</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.38641535771606</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.42</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7398383035114364</v>
+        <v>-0.8355</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.31708946320586</v>
+        <v>-15.039</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.9</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6888195868119128</v>
+        <v>1.9089</v>
       </c>
       <c r="J147" t="n">
-        <v>12.39875256261443</v>
+        <v>34.3602</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.3</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3309630818810038</v>
+        <v>0.7411</v>
       </c>
       <c r="J148" t="n">
-        <v>5.957335473858069</v>
+        <v>13.3398</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2285581107388139</v>
+        <v>0.5181</v>
       </c>
       <c r="J149" t="n">
-        <v>4.114045993298651</v>
+        <v>9.325799999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1041102595277019</v>
+        <v>0.116</v>
       </c>
       <c r="J150" t="n">
-        <v>1.873984671498635</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.04049657037898013</v>
+        <v>-0.4974</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.7289382668216423</v>
+        <v>-8.953200000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.81</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6186510523259228</v>
+        <v>0.9937</v>
       </c>
       <c r="J152" t="n">
-        <v>9.898416837214764</v>
+        <v>15.8992</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5212279211966122</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>8.339646739145795</v>
+        <v>12.5408</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.166272054123036</v>
+        <v>0.206</v>
       </c>
       <c r="J154" t="n">
-        <v>2.660352865968576</v>
+        <v>3.296</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1456719307442314</v>
+        <v>0.1623</v>
       </c>
       <c r="J155" t="n">
-        <v>2.330750891907703</v>
+        <v>2.5968</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.08552992907183529</v>
+        <v>0.0174</v>
       </c>
       <c r="J156" t="n">
-        <v>1.368478865149365</v>
+        <v>0.2784</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.2426832864191363</v>
+        <v>0.0822</v>
       </c>
       <c r="J157" t="n">
-        <v>-3.88293258270618</v>
+        <v>1.3152</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2922968931411646</v>
+        <v>-0.0416</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.676750290258634</v>
+        <v>-0.6656</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.89</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3578738919861477</v>
+        <v>-0.1534</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.725982271778363</v>
+        <v>-2.4544</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5257048993520383</v>
+        <v>-0.3596</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.411278389632614</v>
+        <v>-5.7536</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7463569773974058</v>
+        <v>-0.7033</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.94171163835849</v>
+        <v>-11.2528</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.055686638674738</v>
+        <v>0.3198</v>
       </c>
       <c r="J162" t="n">
-        <v>1.614912521567402</v>
+        <v>9.2742</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1643347739756079</v>
+        <v>-0.0439</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.76570844529263</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3646608806115301</v>
+        <v>-0.2533</v>
       </c>
       <c r="J164" t="n">
-        <v>-10.57516553773437</v>
+        <v>-7.3457</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3646608806115301</v>
+        <v>-0.2533</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.57516553773437</v>
+        <v>-7.3457</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4713072747742924</v>
+        <v>-0.3795</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.66791096845448</v>
+        <v>-11.0055</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.51</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4879083826396609</v>
+        <v>1.2521</v>
       </c>
       <c r="J167" t="n">
-        <v>14.14934309655017</v>
+        <v>36.3109</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2576759598156812</v>
+        <v>0.6319</v>
       </c>
       <c r="J168" t="n">
-        <v>7.472602834654754</v>
+        <v>18.3251</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1104161460322446</v>
+        <v>0.3337</v>
       </c>
       <c r="J169" t="n">
-        <v>3.202068234935094</v>
+        <v>9.677300000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.08707444551995266</v>
+        <v>0.2758</v>
       </c>
       <c r="J170" t="n">
-        <v>2.525158920078627</v>
+        <v>7.9982</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1541644451345438</v>
+        <v>-0.4133</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.47076890890177</v>
+        <v>-11.9857</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.02643649436944232</v>
+        <v>0.3436</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.502293393019404</v>
+        <v>6.5284</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>0.98</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2028829992962988</v>
+        <v>0.0242</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.854776986629678</v>
+        <v>0.4598</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.6287098605373233</v>
+        <v>-0.4786</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.94548735020914</v>
+        <v>-9.093400000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6513142816388919</v>
+        <v>-0.5067</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.37497135113895</v>
+        <v>-9.6273</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.64</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6938946953742656</v>
+        <v>-0.5613</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.18399921211105</v>
+        <v>-10.6647</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.88</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7482192929472304</v>
+        <v>1.8803</v>
       </c>
       <c r="J177" t="n">
-        <v>14.21616656599738</v>
+        <v>35.7257</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2515229126594388</v>
+        <v>0.5437</v>
       </c>
       <c r="J178" t="n">
-        <v>4.778935340529338</v>
+        <v>10.3303</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1719067677931032</v>
+        <v>0.3379</v>
       </c>
       <c r="J179" t="n">
-        <v>3.266228588068961</v>
+        <v>6.4201</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1537313594107851</v>
+        <v>0.2849</v>
       </c>
       <c r="J180" t="n">
-        <v>2.920895828804917</v>
+        <v>5.4131</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>0.04153078838680302</v>
+        <v>-0.1494</v>
       </c>
       <c r="J181" t="n">
-        <v>0.7890849793492574</v>
+        <v>-2.8386</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.53</v>
       </c>
       <c r="I182" t="n">
-        <v>0.442768149701773</v>
+        <v>1.3078</v>
       </c>
       <c r="J182" t="n">
-        <v>12.84027634135142</v>
+        <v>37.9262</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.332938397913073</v>
+        <v>0.9122</v>
       </c>
       <c r="J183" t="n">
-        <v>9.655213539479117</v>
+        <v>26.4538</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1111764288610391</v>
+        <v>0.2959</v>
       </c>
       <c r="J184" t="n">
-        <v>3.224116436970134</v>
+        <v>8.581099999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1480050626222751</v>
+        <v>-0.4874</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.292146816045978</v>
+        <v>-14.1346</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1937201691814674</v>
+        <v>-0.5411</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.617884906262555</v>
+        <v>-15.6919</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.04554392007408836</v>
+        <v>0.0622</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.320773682148562</v>
+        <v>1.8038</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>0.97</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.08373260261053582</v>
+        <v>-0.0209</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.428245475705539</v>
+        <v>-0.6061</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1100823398087468</v>
+        <v>-0.063</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.192387854453658</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3395513330135466</v>
+        <v>-0.3321</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.846988657392851</v>
+        <v>-9.6309</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4971079823654423</v>
+        <v>-0.5476</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.41613148859783</v>
+        <v>-15.8804</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4306430907474006</v>
+        <v>1.2406</v>
       </c>
       <c r="J192" t="n">
-        <v>9.904791087190214</v>
+        <v>28.5338</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2266799351516085</v>
+        <v>0.5366</v>
       </c>
       <c r="J193" t="n">
-        <v>5.213638508486995</v>
+        <v>12.3418</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.04859349497966092</v>
+        <v>0.0319</v>
       </c>
       <c r="J194" t="n">
-        <v>1.117650384532201</v>
+        <v>0.7337</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1401566462501</v>
+        <v>-0.4369</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.2236028637523</v>
+        <v>-10.0487</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.86</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2046619967706983</v>
+        <v>-0.5464</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.70722592572606</v>
+        <v>-12.5672</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1440214051349358</v>
+        <v>0.325</v>
       </c>
       <c r="J197" t="n">
-        <v>3.312492318103523</v>
+        <v>7.475</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1110968058395628</v>
+        <v>0.2772</v>
       </c>
       <c r="J198" t="n">
-        <v>2.555226534309945</v>
+        <v>6.3756</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3093670047367297</v>
+        <v>-0.2977</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.115441108944783</v>
+        <v>-6.8471</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.391678191782813</v>
+        <v>-0.4048</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.008598411004698</v>
+        <v>-9.3104</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4526897306670938</v>
+        <v>-0.489</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.41186380534316</v>
+        <v>-11.247</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1529487129801935</v>
+        <v>0.5216</v>
       </c>
       <c r="J202" t="n">
-        <v>3.364871685564256</v>
+        <v>11.4752</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.12</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.03058439605595181</v>
+        <v>0.277</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.6728567132309398</v>
+        <v>6.094</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1527590697577885</v>
+        <v>0.1116</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.360699534671347</v>
+        <v>2.4552</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1823564901025193</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.011842782255425</v>
+        <v>1.3794</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8768009668086645</v>
+        <v>-0.9379</v>
       </c>
       <c r="J206" t="n">
-        <v>-19.28962126979062</v>
+        <v>-20.6338</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4024492265652215</v>
+        <v>1.1182</v>
       </c>
       <c r="J207" t="n">
-        <v>8.853882984434872</v>
+        <v>24.6004</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.350546010879519</v>
+        <v>0.97</v>
       </c>
       <c r="J208" t="n">
-        <v>7.712012239349417</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.28</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2489290379259739</v>
+        <v>0.7139</v>
       </c>
       <c r="J209" t="n">
-        <v>5.476438834371426</v>
+        <v>15.7058</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.07477356957724471</v>
+        <v>0.3258</v>
       </c>
       <c r="J210" t="n">
-        <v>1.645018530699384</v>
+        <v>7.1676</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1405267737298947</v>
+        <v>-0.3103</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.091589022057683</v>
+        <v>-6.8266</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.43</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2277330380317363</v>
+        <v>0.7331</v>
       </c>
       <c r="J212" t="n">
-        <v>4.554660760634725</v>
+        <v>14.662</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1294615616850823</v>
+        <v>0.1924</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.589231233701646</v>
+        <v>3.848</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.74</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5694637495092628</v>
+        <v>-0.432</v>
       </c>
       <c r="J214" t="n">
-        <v>-11.38927499018526</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.7318967588718762</v>
+        <v>-0.6594</v>
       </c>
       <c r="J215" t="n">
-        <v>-14.63793517743752</v>
+        <v>-13.188</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.51</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7801584266674274</v>
+        <v>-0.733</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.60316853334855</v>
+        <v>-14.66</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.8</v>
       </c>
       <c r="I217" t="n">
-        <v>0.622941176830809</v>
+        <v>1.7289</v>
       </c>
       <c r="J217" t="n">
-        <v>12.45882353661618</v>
+        <v>34.578</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.62</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5282662366898049</v>
+        <v>1.4008</v>
       </c>
       <c r="J218" t="n">
-        <v>10.5653247337961</v>
+        <v>28.016</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.37</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3471293013811499</v>
+        <v>0.8859</v>
       </c>
       <c r="J219" t="n">
-        <v>6.942586027622999</v>
+        <v>17.718</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0204176987578223</v>
+        <v>-0.2181</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.408353975156446</v>
+        <v>-4.362</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2651769187766439</v>
+        <v>-0.7551</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.303538375532878</v>
+        <v>-15.102</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.65</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3694512107603545</v>
+        <v>0.9452</v>
       </c>
       <c r="J222" t="n">
-        <v>8.1279266367278</v>
+        <v>20.7944</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.13</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.01424117371696835</v>
+        <v>0.293</v>
       </c>
       <c r="J223" t="n">
-        <v>-0.3133058217733036</v>
+        <v>6.446</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5123229759399511</v>
+        <v>-0.3583</v>
       </c>
       <c r="J224" t="n">
-        <v>-11.27110547067893</v>
+        <v>-7.8826</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6985565901835044</v>
+        <v>-0.6147</v>
       </c>
       <c r="J225" t="n">
-        <v>-15.3682449840371</v>
+        <v>-13.5234</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7318965285955507</v>
+        <v>-0.6639</v>
       </c>
       <c r="J226" t="n">
-        <v>-16.10172362910211</v>
+        <v>-14.6058</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.72</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6202076322958678</v>
+        <v>1.6208</v>
       </c>
       <c r="J227" t="n">
-        <v>13.64456791050909</v>
+        <v>35.6576</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2826654370720147</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>6.218639615584324</v>
+        <v>15.8004</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2826654370720147</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J229" t="n">
-        <v>6.218639615584324</v>
+        <v>15.8004</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.01300020972481952</v>
+        <v>0.1301</v>
       </c>
       <c r="J230" t="n">
-        <v>0.2860046139460294</v>
+        <v>2.8622</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.256806067954489</v>
+        <v>-0.6181</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.649733494998757</v>
+        <v>-13.5982</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1479218524334932</v>
+        <v>0.4282</v>
       </c>
       <c r="J232" t="n">
-        <v>3.106358901103358</v>
+        <v>8.9922</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1402833785703846</v>
+        <v>0.4141</v>
       </c>
       <c r="J233" t="n">
-        <v>2.945950949978076</v>
+        <v>8.696099999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1716363005491367</v>
+        <v>-0.0334</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.604362311531871</v>
+        <v>-0.7014</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5413766240215169</v>
+        <v>-0.4436</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.36890910445185</v>
+        <v>-9.3156</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6801788756394445</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.28375638842833</v>
+        <v>-13.1565</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.37</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4806168637903939</v>
+        <v>1.0136</v>
       </c>
       <c r="J237" t="n">
-        <v>10.09295413959827</v>
+        <v>21.2856</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.2</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3352725124194209</v>
+        <v>0.6178</v>
       </c>
       <c r="J238" t="n">
-        <v>7.040722760807839</v>
+        <v>12.9738</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1223837480551039</v>
+        <v>0.1482</v>
       </c>
       <c r="J239" t="n">
-        <v>2.570058709157182</v>
+        <v>3.1122</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>0.05292053549509217</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>1.111331245396936</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2183082559613574</v>
+        <v>-0.7212</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.584473375188506</v>
+        <v>-15.1452</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1814320377412021</v>
+        <v>0.4173</v>
       </c>
       <c r="J242" t="n">
-        <v>3.991504830306446</v>
+        <v>9.1806</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.07628264236501596</v>
+        <v>0.2784</v>
       </c>
       <c r="J243" t="n">
-        <v>1.678218132030351</v>
+        <v>6.1248</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3387093367802066</v>
+        <v>-0.3279</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.451605409164545</v>
+        <v>-7.2138</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5201289802708358</v>
+        <v>-0.5716</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.44283756595839</v>
+        <v>-12.5752</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.554976735494446</v>
+        <v>-0.6232</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.20948818087781</v>
+        <v>-13.7104</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.38</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4123451208758225</v>
+        <v>1.02</v>
       </c>
       <c r="J247" t="n">
-        <v>9.071592659268095</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3141823447719281</v>
+        <v>0.7008</v>
       </c>
       <c r="J248" t="n">
-        <v>6.912011584982419</v>
+        <v>15.4176</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.08046320112999913</v>
+        <v>0.0571</v>
       </c>
       <c r="J249" t="n">
-        <v>1.770190424859981</v>
+        <v>1.2562</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05105128150129565</v>
+        <v>-0.0848</v>
       </c>
       <c r="J250" t="n">
-        <v>1.123128193028504</v>
+        <v>-1.8656</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0671039187323148</v>
+        <v>-0.4462</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.476286212110926</v>
+        <v>-9.8164</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.55</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4966830449789378</v>
+        <v>0.7643</v>
       </c>
       <c r="J252" t="n">
-        <v>11.42371003451557</v>
+        <v>17.5789</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1567239053384488</v>
+        <v>0.2409</v>
       </c>
       <c r="J253" t="n">
-        <v>3.604649822784322</v>
+        <v>5.5407</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>1.12</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1106127792952951</v>
+        <v>0.1745</v>
       </c>
       <c r="J254" t="n">
-        <v>2.544093923791787</v>
+        <v>4.0135</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>1.1</v>
       </c>
       <c r="I255" t="n">
-        <v>0.08986931067854644</v>
+        <v>0.1411</v>
       </c>
       <c r="J255" t="n">
-        <v>2.066994145606568</v>
+        <v>3.2453</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.03130759207199794</v>
+        <v>-0.1248</v>
       </c>
       <c r="J256" t="n">
-        <v>-0.7200746176559526</v>
+        <v>-2.8704</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.09</v>
       </c>
       <c r="I257" t="n">
-        <v>0.03558566590329186</v>
+        <v>0.2591</v>
       </c>
       <c r="J257" t="n">
-        <v>0.8184703157757128</v>
+        <v>5.9593</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.06306286529369817</v>
+        <v>0.0639</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.450445901755058</v>
+        <v>1.4697</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>0.83</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3429006161408412</v>
+        <v>-0.2976</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.886714171239347</v>
+        <v>-6.8448</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>0.77</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4216657441412274</v>
+        <v>-0.3924</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.69831211524823</v>
+        <v>-9.0252</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.518899428088902</v>
+        <v>-0.5199</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.93468684604475</v>
+        <v>-11.9577</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.09214395868618896</v>
+        <v>0.1492</v>
       </c>
       <c r="J262" t="n">
-        <v>-1.842879173723779</v>
+        <v>2.984</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>0.86</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.2739830291373143</v>
+        <v>-0.1973</v>
       </c>
       <c r="J263" t="n">
-        <v>-5.479660582746285</v>
+        <v>-3.946</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3622511757680575</v>
+        <v>-0.2946</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.24502351536115</v>
+        <v>-5.892</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4412196515495593</v>
+        <v>-0.3834</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.824393030991187</v>
+        <v>-7.668</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5964997123485979</v>
+        <v>-0.5976</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.92999424697196</v>
+        <v>-11.952</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.73</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5938294598684323</v>
+        <v>1.6351</v>
       </c>
       <c r="J267" t="n">
-        <v>11.87658919736865</v>
+        <v>32.702</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>1.33</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3536444342999782</v>
+        <v>0.834</v>
       </c>
       <c r="J268" t="n">
-        <v>7.072888685999564</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.202950391953566</v>
+        <v>0.4839</v>
       </c>
       <c r="J269" t="n">
-        <v>4.05900783907132</v>
+        <v>9.678000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>1.05</v>
       </c>
       <c r="I270" t="n">
-        <v>0.07599783628957739</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="J270" t="n">
-        <v>1.519956725791548</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.02383428950408021</v>
+        <v>-0.4046</v>
       </c>
       <c r="J271" t="n">
-        <v>-0.4766857900816042</v>
+        <v>-8.092000000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4674071085020117</v>
+        <v>1.21</v>
       </c>
       <c r="J272" t="n">
-        <v>8.413327953036211</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4465357415281286</v>
+        <v>1.149</v>
       </c>
       <c r="J273" t="n">
-        <v>8.037643347506316</v>
+        <v>20.682</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4392489738423794</v>
+        <v>1.1283</v>
       </c>
       <c r="J274" t="n">
-        <v>7.906481529162829</v>
+        <v>20.3094</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>1.21</v>
       </c>
       <c r="I275" t="n">
-        <v>0.17262730726587</v>
+        <v>0.4432</v>
       </c>
       <c r="J275" t="n">
-        <v>3.10729153078566</v>
+        <v>7.9776</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>1.2</v>
       </c>
       <c r="I276" t="n">
-        <v>0.1657037073993855</v>
+        <v>0.4192</v>
       </c>
       <c r="J276" t="n">
-        <v>2.982666733188938</v>
+        <v>7.5456</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>0.98</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.21931501681723</v>
+        <v>0.0573</v>
       </c>
       <c r="J277" t="n">
-        <v>-3.947670302710141</v>
+        <v>1.0314</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.79</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4458571588901687</v>
+        <v>-0.283</v>
       </c>
       <c r="J278" t="n">
-        <v>-8.025428860023037</v>
+        <v>-5.094</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4781661946778956</v>
+        <v>-0.3178</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.606991504202121</v>
+        <v>-5.7204</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6789339846321059</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.22081172337791</v>
+        <v>-9.426600000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7749826751537944</v>
+        <v>-0.6471</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.9496881527683</v>
+        <v>-11.6478</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>2.29</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8258804992010178</v>
+        <v>2.0593</v>
       </c>
       <c r="J282" t="n">
-        <v>11.56232698881425</v>
+        <v>28.8302</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>2.05</v>
       </c>
       <c r="I283" t="n">
-        <v>0.73467787381281</v>
+        <v>1.991</v>
       </c>
       <c r="J283" t="n">
-        <v>10.28549023337934</v>
+        <v>27.874</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.52</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3737969983805858</v>
+        <v>1.0437</v>
       </c>
       <c r="J284" t="n">
-        <v>5.233157977328201</v>
+        <v>14.6118</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>1.1</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1169628596520126</v>
+        <v>0.12</v>
       </c>
       <c r="J285" t="n">
-        <v>1.637480035128176</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>0.04702840241854744</v>
+        <v>-0.3512</v>
       </c>
       <c r="J286" t="n">
-        <v>0.6583976338596642</v>
+        <v>-4.9168</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.4638480235849749</v>
+        <v>-0.1465</v>
       </c>
       <c r="J287" t="n">
-        <v>-6.493872330189649</v>
+        <v>-2.051</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.4845559988229317</v>
+        <v>-0.1789</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.783783983521043</v>
+        <v>-2.5046</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.5059266165612828</v>
+        <v>-0.2109</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.08297263185796</v>
+        <v>-2.9526</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.713592744013644</v>
+        <v>-0.4516</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.990298416191017</v>
+        <v>-6.3224</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.22</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.145894093761242</v>
+        <v>-1.0456</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.04251731265738</v>
+        <v>-14.6384</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.191886383473678</v>
+        <v>0.018</v>
       </c>
       <c r="J292" t="n">
-        <v>-3.453954902526203</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>0.89</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2714443252151736</v>
+        <v>-0.1331</v>
       </c>
       <c r="J293" t="n">
-        <v>-4.885997853873126</v>
+        <v>-2.3958</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>0.83</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3400982159543755</v>
+        <v>-0.2364</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.121767887178759</v>
+        <v>-4.2552</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5480214237042426</v>
+        <v>-0.4944</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.864385626676366</v>
+        <v>-8.8992</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6445033474088409</v>
+        <v>-0.6438</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.60106025335913</v>
+        <v>-11.5884</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>2.01</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7564982500027208</v>
+        <v>2.0131</v>
       </c>
       <c r="J297" t="n">
-        <v>13.61696850004897</v>
+        <v>36.2358</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2965617178359927</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>5.338110921047868</v>
+        <v>12.456</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.2</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2024452913231374</v>
+        <v>0.4454</v>
       </c>
       <c r="J299" t="n">
-        <v>3.644015243816473</v>
+        <v>8.017200000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>1.19</v>
       </c>
       <c r="I300" t="n">
-        <v>0.1942319976123425</v>
+        <v>0.4206</v>
       </c>
       <c r="J300" t="n">
-        <v>3.496175957022165</v>
+        <v>7.5708</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.01163870622115783</v>
+        <v>-0.4531</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.2094967119808409</v>
+        <v>-8.155799999999999</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>1.01</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.1683780609217987</v>
+        <v>0.2003</v>
       </c>
       <c r="J302" t="n">
-        <v>-2.694048974748779</v>
+        <v>3.2048</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>0.66</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.4904617996361334</v>
+        <v>-0.4386</v>
       </c>
       <c r="J303" t="n">
-        <v>-7.847388794178134</v>
+        <v>-7.0176</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.6097705754974142</v>
+        <v>-0.583</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.756329207958627</v>
+        <v>-9.327999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.55</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.639981376716645</v>
+        <v>-0.6269</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.23970202746632</v>
+        <v>-10.0304</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.44</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7335410380040436</v>
+        <v>-0.7758</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.7366566080647</v>
+        <v>-12.4128</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>2.15</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8276031627793685</v>
+        <v>2.0593</v>
       </c>
       <c r="J307" t="n">
-        <v>13.2416506044699</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3849442045315162</v>
+        <v>0.9193</v>
       </c>
       <c r="J308" t="n">
-        <v>6.15910727250426</v>
+        <v>14.7088</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3040707855667021</v>
+        <v>0.7169</v>
       </c>
       <c r="J309" t="n">
-        <v>4.865132569067233</v>
+        <v>11.4704</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2184675493694874</v>
+        <v>0.4462</v>
       </c>
       <c r="J310" t="n">
-        <v>3.495480789911798</v>
+        <v>7.1392</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.1606410228345524</v>
+        <v>0.2278</v>
       </c>
       <c r="J311" t="n">
-        <v>2.570256365352838</v>
+        <v>3.6448</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.5503</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.538</v>
       </c>
       <c r="D2" t="n">
         <v>3.0328</v>
@@ -545,7 +545,7 @@
         <v>5.5668</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.0013</v>
       </c>
       <c r="D3" t="n">
         <v>1.8275</v>
@@ -591,7 +591,7 @@
         <v>5.388</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.9692</v>
       </c>
       <c r="D4" t="n">
         <v>1.7553</v>
@@ -637,7 +637,7 @@
         <v>5.2428</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.9431</v>
       </c>
       <c r="D5" t="n">
         <v>1.6966</v>
@@ -683,7 +683,7 @@
         <v>4.2979</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.7731</v>
       </c>
       <c r="D6" t="n">
         <v>1.3149</v>
@@ -729,7 +729,7 @@
         <v>4.1209</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.7413</v>
       </c>
       <c r="D7" t="n">
         <v>1.2434</v>
@@ -775,7 +775,7 @@
         <v>3.794</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.6825</v>
       </c>
       <c r="D8" t="n">
         <v>1.1113</v>
@@ -821,7 +821,7 @@
         <v>3.5052</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0.9947</v>
@@ -867,7 +867,7 @@
         <v>3.4688</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="D10" t="n">
         <v>0.98</v>
@@ -913,7 +913,7 @@
         <v>3.3503</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.6026</v>
       </c>
       <c r="D11" t="n">
         <v>0.9321</v>
@@ -959,7 +959,7 @@
         <v>3.112</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.5598</v>
       </c>
       <c r="D12" t="n">
         <v>0.8358</v>
@@ -1005,7 +1005,7 @@
         <v>3.0625</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="D13" t="n">
         <v>0.8158</v>
@@ -1051,7 +1051,7 @@
         <v>2.1054</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.3787</v>
       </c>
       <c r="D14" t="n">
         <v>0.4292</v>
@@ -1097,7 +1097,7 @@
         <v>1.7238</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.3101</v>
       </c>
       <c r="D15" t="n">
         <v>0.275</v>
@@ -1143,7 +1143,7 @@
         <v>1.6896</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.3039</v>
       </c>
       <c r="D16" t="n">
         <v>0.2612</v>
@@ -1189,7 +1189,7 @@
         <v>1.3268</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2387</v>
       </c>
       <c r="D17" t="n">
         <v>0.1146</v>
@@ -1235,7 +1235,7 @@
         <v>1.1298</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2032</v>
       </c>
       <c r="D18" t="n">
         <v>0.0351</v>
@@ -1281,7 +1281,7 @@
         <v>1.0774</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1938</v>
       </c>
       <c r="D19" t="n">
         <v>0.0139</v>
@@ -1327,7 +1327,7 @@
         <v>1.0221</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1839</v>
       </c>
       <c r="D20" t="n">
         <v>-0.008500000000000001</v>
@@ -1373,7 +1373,7 @@
         <v>0.9558</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1719</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0352</v>
@@ -1419,7 +1419,7 @@
         <v>0.8711</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1567</v>
       </c>
       <c r="D22" t="n">
         <v>-0.06950000000000001</v>
@@ -1465,7 +1465,7 @@
         <v>0.7877</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1417</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1031</v>
@@ -1511,7 +1511,7 @@
         <v>0.5379</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0968</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2041</v>
@@ -1557,7 +1557,7 @@
         <v>0.3473</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="D25" t="n">
         <v>-0.2811</v>
@@ -1603,7 +1603,7 @@
         <v>0.1942</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3429</v>
@@ -1649,7 +1649,7 @@
         <v>-0.1502</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.027</v>
       </c>
       <c r="D27" t="n">
         <v>-0.482</v>
@@ -1695,7 +1695,7 @@
         <v>-0.4374</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="D28" t="n">
         <v>-0.5981</v>
@@ -1741,7 +1741,7 @@
         <v>-0.4538</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="D29" t="n">
         <v>-0.6047</v>
@@ -1787,7 +1787,7 @@
         <v>-0.4989</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0897</v>
       </c>
       <c r="D30" t="n">
         <v>-0.6229</v>
@@ -1833,7 +1833,7 @@
         <v>-0.5672</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.102</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6505</v>
@@ -1879,7 +1879,7 @@
         <v>-0.8045</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1447</v>
       </c>
       <c r="D32" t="n">
         <v>-0.7464</v>
@@ -1925,7 +1925,7 @@
         <v>-0.8582</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.1544</v>
       </c>
       <c r="D33" t="n">
         <v>-0.7681</v>
@@ -1971,7 +1971,7 @@
         <v>-0.8711</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1567</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7733</v>
@@ -2017,7 +2017,7 @@
         <v>-0.8864</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.1594</v>
       </c>
       <c r="D35" t="n">
         <v>-0.7794</v>
@@ -2063,7 +2063,7 @@
         <v>-1.0011</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.1801</v>
       </c>
       <c r="D36" t="n">
         <v>-0.8258</v>
@@ -2109,7 +2109,7 @@
         <v>-1.2715</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.2287</v>
       </c>
       <c r="D37" t="n">
         <v>-0.9350000000000001</v>
@@ -2155,7 +2155,7 @@
         <v>-1.6703</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.3004</v>
       </c>
       <c r="D38" t="n">
         <v>-1.0961</v>
@@ -2201,7 +2201,7 @@
         <v>-2.5455</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.4579</v>
       </c>
       <c r="D39" t="n">
         <v>-1.4497</v>
@@ -2247,7 +2247,7 @@
         <v>-3.1565</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.5678</v>
       </c>
       <c r="D40" t="n">
         <v>-1.6965</v>
@@ -2293,7 +2293,7 @@
         <v>-3.5035</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.6302</v>
       </c>
       <c r="D41" t="n">
         <v>-1.8367</v>

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.538</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0328</v>
+        <v>2.9625</v>
       </c>
       <c r="E2" t="n">
         <v>8.5503</v>
@@ -548,7 +548,7 @@
         <v>1.0013</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8275</v>
+        <v>1.7739</v>
       </c>
       <c r="E3" t="n">
         <v>5.5668</v>
@@ -594,7 +594,7 @@
         <v>0.9692</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7553</v>
+        <v>1.7027</v>
       </c>
       <c r="E4" t="n">
         <v>5.388</v>
@@ -640,7 +640,7 @@
         <v>0.9431</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6966</v>
+        <v>1.6448</v>
       </c>
       <c r="E5" t="n">
         <v>5.2428</v>
@@ -686,7 +686,7 @@
         <v>0.7731</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3149</v>
+        <v>1.2684</v>
       </c>
       <c r="E6" t="n">
         <v>4.2979</v>
@@ -732,7 +732,7 @@
         <v>0.7413</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2434</v>
+        <v>1.1979</v>
       </c>
       <c r="E7" t="n">
         <v>4.1209</v>
@@ -778,7 +778,7 @@
         <v>0.6825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1113</v>
+        <v>1.0676</v>
       </c>
       <c r="E8" t="n">
         <v>3.794</v>
@@ -824,7 +824,7 @@
         <v>0.6304999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9947</v>
+        <v>0.9526</v>
       </c>
       <c r="E9" t="n">
         <v>3.5052</v>
@@ -870,7 +870,7 @@
         <v>0.624</v>
       </c>
       <c r="D10" t="n">
-        <v>0.98</v>
+        <v>0.9381</v>
       </c>
       <c r="E10" t="n">
         <v>3.4688</v>
@@ -916,7 +916,7 @@
         <v>0.6026</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9321</v>
+        <v>0.8908</v>
       </c>
       <c r="E11" t="n">
         <v>3.3503</v>
@@ -962,7 +962,7 @@
         <v>0.5598</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8358</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>3.112</v>
@@ -1008,7 +1008,7 @@
         <v>0.5508999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8158</v>
+        <v>0.7762</v>
       </c>
       <c r="E13" t="n">
         <v>3.0625</v>
@@ -1054,7 +1054,7 @@
         <v>0.3787</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4292</v>
+        <v>0.3949</v>
       </c>
       <c r="E14" t="n">
         <v>2.1054</v>
@@ -1100,7 +1100,7 @@
         <v>0.3101</v>
       </c>
       <c r="D15" t="n">
-        <v>0.275</v>
+        <v>0.2429</v>
       </c>
       <c r="E15" t="n">
         <v>1.7238</v>
@@ -1146,7 +1146,7 @@
         <v>0.3039</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2612</v>
+        <v>0.2292</v>
       </c>
       <c r="E16" t="n">
         <v>1.6896</v>
@@ -1192,7 +1192,7 @@
         <v>0.2387</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1146</v>
+        <v>0.0847</v>
       </c>
       <c r="E17" t="n">
         <v>1.3268</v>
@@ -1238,7 +1238,7 @@
         <v>0.2032</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0351</v>
+        <v>0.0062</v>
       </c>
       <c r="E18" t="n">
         <v>1.1298</v>
@@ -1284,7 +1284,7 @@
         <v>0.1938</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0139</v>
+        <v>-0.0147</v>
       </c>
       <c r="E19" t="n">
         <v>1.0774</v>
@@ -1330,7 +1330,7 @@
         <v>0.1839</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0367</v>
       </c>
       <c r="E20" t="n">
         <v>1.0221</v>
@@ -1376,7 +1376,7 @@
         <v>0.1719</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0352</v>
+        <v>-0.0631</v>
       </c>
       <c r="E21" t="n">
         <v>0.9558</v>
@@ -1422,7 +1422,7 @@
         <v>0.1567</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0969</v>
       </c>
       <c r="E22" t="n">
         <v>0.8711</v>
@@ -1468,7 +1468,7 @@
         <v>0.1417</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1031</v>
+        <v>-0.1301</v>
       </c>
       <c r="E23" t="n">
         <v>0.7877</v>
@@ -1514,7 +1514,7 @@
         <v>0.0968</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2041</v>
+        <v>-0.2296</v>
       </c>
       <c r="E24" t="n">
         <v>0.5379</v>
@@ -1560,7 +1560,7 @@
         <v>0.0625</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2811</v>
+        <v>-0.3055</v>
       </c>
       <c r="E25" t="n">
         <v>0.3473</v>
@@ -1606,7 +1606,7 @@
         <v>0.0349</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3429</v>
+        <v>-0.3665</v>
       </c>
       <c r="E26" t="n">
         <v>0.1942</v>
@@ -1652,7 +1652,7 @@
         <v>-0.027</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.482</v>
+        <v>-0.5038</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1502</v>
@@ -1698,7 +1698,7 @@
         <v>-0.07870000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5981</v>
+        <v>-0.6182</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4374</v>
@@ -1744,7 +1744,7 @@
         <v>-0.08160000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6047</v>
+        <v>-0.6247</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4538</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0897</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6229</v>
+        <v>-0.6427</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4989</v>
@@ -1836,7 +1836,7 @@
         <v>-0.102</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6505</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>-0.5672</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1447</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7464</v>
+        <v>-0.7644</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8045</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1544</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7681</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8582</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1567</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7733</v>
+        <v>-0.791</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8711</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1594</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7794</v>
+        <v>-0.7971</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8864</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1801</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8258</v>
+        <v>-0.8427</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0011</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2287</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9505</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2715</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3004</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0961</v>
+        <v>-1.1094</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6703</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4579</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4497</v>
+        <v>-1.458</v>
       </c>
       <c r="E39" t="n">
         <v>-2.5455</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5678</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6965</v>
+        <v>-1.7015</v>
       </c>
       <c r="E40" t="n">
         <v>-3.1565</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6302</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8367</v>
+        <v>-1.8397</v>
       </c>
       <c r="E41" t="n">
         <v>-3.5035</v>

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5503</v>
+        <v>8.0939</v>
       </c>
       <c r="C2" t="n">
-        <v>1.538</v>
+        <v>1.4559</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9625</v>
+        <v>3.016</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5503</v>
+        <v>8.0939</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6011</v>
+        <v>4.4518</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9492</v>
+        <v>3.6421</v>
       </c>
       <c r="H2" t="n">
-        <v>5.951</v>
+        <v>10.7444</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8234</v>
+        <v>5.5866</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9492</v>
+        <v>3.6421</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>8.772600000000001</v>
+        <v>9.2287</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5668</v>
+        <v>5.4979</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0013</v>
+        <v>0.9889</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7739</v>
+        <v>1.844</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5668</v>
+        <v>5.4979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.011</v>
+        <v>0.7862</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5558</v>
+        <v>4.7117</v>
       </c>
       <c r="H3" t="n">
-        <v>0.011</v>
+        <v>0.7862</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0089</v>
+        <v>0.4088</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5558</v>
+        <v>4.7117</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>5.564699999999999</v>
+        <v>5.120500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -584,173 +584,173 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.388</v>
+        <v>5.299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9692</v>
+        <v>0.9532</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7027</v>
+        <v>1.7542</v>
       </c>
       <c r="E4" t="n">
-        <v>5.388</v>
+        <v>5.299</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0037</v>
+        <v>2.9756</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3843</v>
+        <v>2.3234</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0037</v>
+        <v>4.9977</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2451</v>
+        <v>2.5986</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3843</v>
+        <v>2.3234</v>
       </c>
       <c r="K4" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6294</v>
+        <v>4.922</v>
       </c>
       <c r="N4" t="n">
-        <v>133</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2428</v>
+        <v>4.8913</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9431</v>
+        <v>0.8798</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6448</v>
+        <v>1.5702</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2428</v>
+        <v>4.8913</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9241</v>
+        <v>3.5943</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3187</v>
+        <v>1.297</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9241</v>
+        <v>7.1777</v>
       </c>
       <c r="I5" t="n">
-        <v>2.37</v>
+        <v>3.7321</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3187</v>
+        <v>1.297</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>4.688700000000001</v>
+        <v>5.0291</v>
       </c>
       <c r="N5" t="n">
-        <v>287</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>zorte</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2979</v>
+        <v>3.9154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7731</v>
+        <v>0.7043</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2684</v>
+        <v>1.1296</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2979</v>
+        <v>3.9154</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7355</v>
+        <v>2.9378</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5624</v>
+        <v>0.9776</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7355</v>
+        <v>4.8647</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0277</v>
+        <v>2.5294</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5624</v>
+        <v>0.9776</v>
       </c>
       <c r="K6" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5901</v>
+        <v>3.507</v>
       </c>
       <c r="N6" t="n">
-        <v>152</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>danistzz</t>
+          <t>zorte</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1209</v>
+        <v>3.9001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7413</v>
+        <v>0.7015</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1979</v>
+        <v>1.1227</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1209</v>
+        <v>3.9001</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2576</v>
+        <v>3.3145</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1367</v>
+        <v>0.5856</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5688</v>
+        <v>6.1921</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7031</v>
+        <v>3.2196</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1367</v>
+        <v>0.5856</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5664</v>
+        <v>3.8052</v>
       </c>
       <c r="N7" t="n">
         <v>152</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>danistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.794</v>
+        <v>3.8395</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6825</v>
+        <v>0.6906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0676</v>
+        <v>1.0953</v>
       </c>
       <c r="E8" t="n">
-        <v>3.794</v>
+        <v>3.8395</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6479</v>
+        <v>3.7824</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1461</v>
+        <v>0.0571</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6479</v>
+        <v>7.8405</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1462</v>
+        <v>4.0767</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1461</v>
+        <v>0.0571</v>
       </c>
       <c r="K8" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2923</v>
+        <v>4.1338</v>
       </c>
       <c r="N8" t="n">
-        <v>260</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5052</v>
+        <v>3.7457</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6738</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9526</v>
+        <v>1.053</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5052</v>
+        <v>3.7457</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2366</v>
+        <v>2.947</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2686</v>
+        <v>0.7987</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2366</v>
+        <v>4.897</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6234</v>
+        <v>2.5462</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2686</v>
+        <v>0.7987</v>
       </c>
       <c r="K9" t="n">
         <v>117</v>
@@ -851,7 +851,7 @@
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>2.892</v>
+        <v>3.3449</v>
       </c>
       <c r="N9" t="n">
         <v>260</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4688</v>
+        <v>3.6644</v>
       </c>
       <c r="C10" t="n">
-        <v>0.624</v>
+        <v>0.6591</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9381</v>
+        <v>1.0163</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4688</v>
+        <v>3.6644</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1398</v>
+        <v>0.0892</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6086</v>
+        <v>3.5752</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1398</v>
+        <v>0.0892</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1133</v>
+        <v>0.0464</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6086</v>
+        <v>3.5752</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4953</v>
+        <v>3.6216</v>
       </c>
       <c r="N10" t="n">
         <v>287</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3503</v>
+        <v>3.2405</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6026</v>
+        <v>0.5829</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8908</v>
+        <v>0.8249</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3503</v>
+        <v>3.2405</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3503</v>
+        <v>3.2405</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3503</v>
+        <v>3.7559</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3503</v>
+        <v>3.7559</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3503</v>
+        <v>3.7559</v>
       </c>
       <c r="N11" t="n">
         <v>146</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.112</v>
+        <v>3.2063</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5598</v>
+        <v>0.5767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8095</v>
       </c>
       <c r="E12" t="n">
-        <v>3.112</v>
+        <v>3.2063</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6239</v>
+        <v>3.5585</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5119</v>
+        <v>-0.3522</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6239</v>
+        <v>7.0518</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9372</v>
+        <v>3.6666</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5119</v>
+        <v>-0.3522</v>
       </c>
       <c r="K12" t="n">
         <v>96</v>
@@ -989,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4253</v>
+        <v>3.3144</v>
       </c>
       <c r="N12" t="n">
         <v>133</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0625</v>
+        <v>3.0386</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5466</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7762</v>
+        <v>0.7338</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0625</v>
+        <v>3.0386</v>
       </c>
       <c r="F13" t="n">
-        <v>3.726</v>
+        <v>3.4783</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6635</v>
+        <v>-0.4397</v>
       </c>
       <c r="H13" t="n">
-        <v>3.726</v>
+        <v>6.7691</v>
       </c>
       <c r="I13" t="n">
-        <v>3.02</v>
+        <v>3.5196</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6635</v>
+        <v>-0.4397</v>
       </c>
       <c r="K13" t="n">
         <v>96</v>
@@ -1035,7 +1035,7 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3565</v>
+        <v>3.0799</v>
       </c>
       <c r="N13" t="n">
         <v>133</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1054</v>
+        <v>2.513</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3787</v>
+        <v>0.452</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3949</v>
+        <v>0.4965</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1054</v>
+        <v>2.513</v>
       </c>
       <c r="F14" t="n">
-        <v>0.529</v>
+        <v>1.0576</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5763</v>
+        <v>1.4554</v>
       </c>
       <c r="H14" t="n">
-        <v>0.529</v>
+        <v>1.0576</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4288</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5763</v>
+        <v>1.4554</v>
       </c>
       <c r="K14" t="n">
         <v>117</v>
@@ -1081,7 +1081,7 @@
         <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0051</v>
+        <v>2.0053</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3101</v>
+        <v>0.4067</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2429</v>
+        <v>0.3828</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7238</v>
+        <v>2.2612</v>
       </c>
       <c r="N15" t="n">
         <v>139</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3039</v>
+        <v>0.3737</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2292</v>
+        <v>0.2999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6896</v>
+        <v>2.0775</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1182,277 +1182,277 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3268</v>
+        <v>1.967</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2387</v>
+        <v>0.3538</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0847</v>
+        <v>0.25</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3268</v>
+        <v>1.967</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5537</v>
+        <v>1.967</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8805</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5537</v>
+        <v>1.967</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4488</v>
+        <v>1.967</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8805</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L17" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4317</v>
+        <v>1.967</v>
       </c>
       <c r="N17" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1298</v>
+        <v>1.8376</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2032</v>
+        <v>0.3305</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0062</v>
+        <v>0.1916</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1298</v>
+        <v>1.8376</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1298</v>
+        <v>1.8376</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1298</v>
+        <v>1.8376</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7263</v>
+        <v>1.8376</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L18" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7262999999999999</v>
+        <v>1.8376</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0774</v>
+        <v>1.814</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1938</v>
+        <v>0.3263</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0147</v>
+        <v>0.1809</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0774</v>
+        <v>1.814</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0774</v>
+        <v>2.5792</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7652</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0774</v>
+        <v>3.6011</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0774</v>
+        <v>1.8724</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7652</v>
       </c>
       <c r="K19" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0774</v>
+        <v>1.1072</v>
       </c>
       <c r="N19" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0221</v>
+        <v>1.6883</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1839</v>
+        <v>0.3037</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0367</v>
+        <v>0.1242</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0221</v>
+        <v>1.6883</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0221</v>
+        <v>-0.1331</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.8214</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0221</v>
+        <v>-0.1331</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0221</v>
+        <v>-0.0692</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.8214</v>
       </c>
       <c r="K20" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0221</v>
+        <v>1.7522</v>
       </c>
       <c r="N20" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9558</v>
+        <v>1.6692</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1719</v>
+        <v>0.3003</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0631</v>
+        <v>0.1155</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9558</v>
+        <v>1.6692</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9558</v>
+        <v>2.3784</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9558</v>
+        <v>2.8935</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9558</v>
+        <v>1.5045</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9558</v>
+        <v>0.7952999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1567</v>
+        <v>0.2657</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0969</v>
+        <v>0.0287</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8711</v>
+        <v>1.4769</v>
       </c>
       <c r="N22" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1417</v>
+        <v>0.2246</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1301</v>
+        <v>-0.0743</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7877</v>
+        <v>1.2486</v>
       </c>
       <c r="N23" t="n">
         <v>146</v>
@@ -1504,127 +1504,127 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0968</v>
+        <v>0.2015</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2296</v>
+        <v>-0.1323</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5379</v>
+        <v>1.1202</v>
       </c>
       <c r="N24" t="n">
-        <v>139</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0625</v>
+        <v>0.1998</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3055</v>
+        <v>-0.1366</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3473</v>
+        <v>1.1107</v>
       </c>
       <c r="N25" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1942</v>
+        <v>0.7605</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0349</v>
+        <v>0.1368</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3665</v>
+        <v>-0.2947</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1942</v>
+        <v>0.7605</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1942</v>
+        <v>1.6578</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>-0.8973</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1942</v>
+        <v>1.6578</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9679</v>
+        <v>0.862</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>-0.8973</v>
       </c>
       <c r="K26" t="n">
         <v>96</v>
@@ -1633,7 +1633,7 @@
         <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03210000000000002</v>
+        <v>-0.0353</v>
       </c>
       <c r="N26" t="n">
         <v>133</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1502</v>
+        <v>0.5662</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.027</v>
+        <v>0.1018</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5038</v>
+        <v>-0.3824</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1502</v>
+        <v>0.5662</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8498</v>
+        <v>0.5662</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8498</v>
+        <v>0.5662</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6888</v>
+        <v>0.5662</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="L27" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3112</v>
+        <v>0.5662</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4374</v>
+        <v>0.2092</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.0376</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6182</v>
+        <v>-0.5436</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4374</v>
+        <v>0.2092</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4374</v>
+        <v>0.7551</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4374</v>
+        <v>0.7551</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4374</v>
+        <v>0.3926</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4374</v>
+        <v>-0.1533</v>
       </c>
       <c r="N28" t="n">
-        <v>119</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.0221</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6247</v>
+        <v>-0.5826</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4538</v>
+        <v>0.1227</v>
       </c>
       <c r="N29" t="n">
         <v>76</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0897</v>
+        <v>0.0133</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6427</v>
+        <v>-0.6047</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4989</v>
+        <v>0.0737</v>
       </c>
       <c r="N30" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.102</v>
+        <v>0.0112</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.6098</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5672</v>
+        <v>0.0625</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1872,124 +1872,124 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8045</v>
+        <v>-0.2693</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1447</v>
+        <v>-0.0484</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7644</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8045</v>
+        <v>-0.2693</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2125</v>
+        <v>-0.2693</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.017</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2125</v>
+        <v>-0.2693</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1722</v>
+        <v>-0.2693</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.017</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="L32" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8447999999999999</v>
+        <v>-0.2693</v>
       </c>
       <c r="N32" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8582</v>
+        <v>-0.2724</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1544</v>
+        <v>-0.049</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.761</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8582</v>
+        <v>-0.2724</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8582</v>
+        <v>0.5977</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8582</v>
+        <v>0.5977</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8582</v>
+        <v>0.3108</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="K33" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8582</v>
+        <v>-0.5592999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>119</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1567</v>
+        <v>-0.0784</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.791</v>
+        <v>-0.8348</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8711</v>
+        <v>-0.436</v>
       </c>
       <c r="N34" t="n">
         <v>76</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8864</v>
+        <v>-0.5013</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1594</v>
+        <v>-0.0902</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7971</v>
+        <v>-0.8643</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8864</v>
+        <v>-0.5013</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0507</v>
+        <v>-0.5013</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8357</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0507</v>
+        <v>-0.5013</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0411</v>
+        <v>-0.5013</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8357</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="L35" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8768</v>
+        <v>-0.5013</v>
       </c>
       <c r="N35" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1801</v>
+        <v>-0.1053</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8427</v>
+        <v>-0.9024</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0011</v>
+        <v>-0.5856</v>
       </c>
       <c r="N36" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2287</v>
+        <v>-0.1315</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9505</v>
+        <v>-0.968</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2715</v>
+        <v>-0.7309</v>
       </c>
       <c r="N37" t="n">
         <v>119</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3004</v>
+        <v>-0.2175</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1094</v>
+        <v>-1.1838</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6703</v>
+        <v>-1.2089</v>
       </c>
       <c r="N38" t="n">
         <v>76</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.5455</v>
+        <v>-2.7944</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4579</v>
+        <v>-0.5026</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.458</v>
+        <v>-1.8995</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.5455</v>
+        <v>-2.7944</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7465</v>
+        <v>-2.7944</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.799</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7465</v>
+        <v>-2.7944</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4156</v>
+        <v>-2.7944</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.799</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L39" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.2146</v>
+        <v>-2.7944</v>
       </c>
       <c r="N39" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.1565</v>
+        <v>-2.8932</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5678</v>
+        <v>-0.5204</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7015</v>
+        <v>-1.9441</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.1565</v>
+        <v>-2.8932</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.1565</v>
+        <v>-2.3681</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.5251</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.1565</v>
+        <v>-2.3681</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.1565</v>
+        <v>-1.2313</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.5251</v>
       </c>
       <c r="K40" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.1565</v>
+        <v>-1.7564</v>
       </c>
       <c r="N40" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.5035</v>
+        <v>-4.1647</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6302</v>
+        <v>-0.7491</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8397</v>
+        <v>-2.5182</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.5035</v>
+        <v>-4.1647</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2791</v>
+        <v>-4.6621</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2244</v>
+        <v>0.4974</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2791</v>
+        <v>-4.6621</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6578</v>
+        <v>-2.4241</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.2244</v>
+        <v>0.4974</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>143</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8822</v>
+        <v>-1.9267</v>
       </c>
       <c r="N41" t="n">
         <v>287</v>
@@ -2429,10 +2429,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.6459</v>
       </c>
       <c r="J2" t="n">
-        <v>15.2943</v>
+        <v>13.5639</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7169</v>
+        <v>0.6348</v>
       </c>
       <c r="J3" t="n">
-        <v>15.0549</v>
+        <v>13.3308</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1595</v>
+        <v>-0.0786</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.3495</v>
+        <v>-1.6506</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.93</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2146</v>
+        <v>-0.1159</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.5066</v>
+        <v>-2.4339</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3412</v>
+        <v>-0.2042</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.1652</v>
+        <v>-4.2882</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1477</v>
+        <v>0.0968</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1017</v>
+        <v>2.0328</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1252</v>
+        <v>0.076</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6292</v>
+        <v>1.596</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.195</v>
+        <v>-0.143</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.095</v>
+        <v>-3.003</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2413</v>
+        <v>-0.1631</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.0673</v>
+        <v>-3.4251</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6737</v>
+        <v>-0.4512</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.1477</v>
+        <v>-9.475199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7749</v>
+        <v>0.6925</v>
       </c>
       <c r="J12" t="n">
-        <v>17.0478</v>
+        <v>15.235</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3144</v>
+        <v>0.2828</v>
       </c>
       <c r="J13" t="n">
-        <v>6.9168</v>
+        <v>6.2216</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2233</v>
+        <v>0.2214</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9126</v>
+        <v>4.8708</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2233</v>
+        <v>0.2214</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9126</v>
+        <v>4.8708</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3322</v>
+        <v>-0.197</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.3084</v>
+        <v>-4.334</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4114</v>
+        <v>0.3576</v>
       </c>
       <c r="J17" t="n">
-        <v>9.050800000000001</v>
+        <v>7.8672</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1869</v>
+        <v>0.1394</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1118</v>
+        <v>3.0668</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1266</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7852</v>
+        <v>1.8502</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.73</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4636</v>
+        <v>-0.2982</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.1992</v>
+        <v>-6.5604</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6459</v>
+        <v>-0.4298</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.2098</v>
+        <v>-9.4556</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2713</v>
+        <v>0.2762</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3408</v>
+        <v>4.4192</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1467</v>
+        <v>0.1165</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3472</v>
+        <v>1.864</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4687</v>
+        <v>-0.3142</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.4992</v>
+        <v>-5.0272</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5273</v>
+        <v>-0.3519</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.4368</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8717</v>
+        <v>-0.6025</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.9472</v>
+        <v>-9.640000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.91</v>
       </c>
       <c r="I27" t="n">
-        <v>1.832</v>
+        <v>1.5576</v>
       </c>
       <c r="J27" t="n">
-        <v>29.312</v>
+        <v>24.9216</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2238</v>
+        <v>1.1836</v>
       </c>
       <c r="J28" t="n">
-        <v>19.5808</v>
+        <v>18.9376</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9455</v>
+        <v>1.0439</v>
       </c>
       <c r="J29" t="n">
-        <v>15.128</v>
+        <v>16.7024</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7754</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>12.4064</v>
+        <v>14.5248</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6037</v>
+        <v>0.731</v>
       </c>
       <c r="J31" t="n">
-        <v>9.6592</v>
+        <v>11.696</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1911</v>
+        <v>0.1723</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4398</v>
+        <v>3.1014</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1096</v>
+        <v>0.0728</v>
       </c>
       <c r="J33" t="n">
-        <v>1.9728</v>
+        <v>1.3104</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0698</v>
+        <v>-0.0805</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.2564</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.48</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.5113</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.545</v>
+        <v>-9.2034</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.849</v>
+        <v>-0.5849</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.282</v>
+        <v>-10.5282</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2554</v>
+        <v>1.1746</v>
       </c>
       <c r="J37" t="n">
-        <v>22.5972</v>
+        <v>21.1428</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.51</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1755</v>
+        <v>1.1255</v>
       </c>
       <c r="J38" t="n">
-        <v>21.159</v>
+        <v>20.259</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.44</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0295</v>
+        <v>1.0374</v>
       </c>
       <c r="J39" t="n">
-        <v>18.531</v>
+        <v>18.6732</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1819</v>
+        <v>0.2704</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2742</v>
+        <v>4.8672</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1541</v>
+        <v>0.2417</v>
       </c>
       <c r="J41" t="n">
-        <v>2.7738</v>
+        <v>4.3506</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3701</v>
+        <v>0.4163</v>
       </c>
       <c r="J42" t="n">
-        <v>10.7329</v>
+        <v>12.0727</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1556</v>
+        <v>-0.0956</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.5124</v>
+        <v>-2.7724</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1556</v>
+        <v>-0.0956</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.5124</v>
+        <v>-2.7724</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.163</v>
+        <v>-4.3819</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2801</v>
+        <v>-0.1724</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.1229</v>
+        <v>-4.9996</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.98</v>
+        <v>0.962</v>
       </c>
       <c r="J47" t="n">
-        <v>28.42</v>
+        <v>27.898</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="J48" t="n">
-        <v>16.7649</v>
+        <v>16.1443</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4971</v>
+        <v>0.4803</v>
       </c>
       <c r="J49" t="n">
-        <v>14.4159</v>
+        <v>13.9287</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.1035</v>
+        <v>-2.2823</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6548</v>
+        <v>-0.5985</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.9892</v>
+        <v>-17.3565</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5927</v>
+        <v>0.5576</v>
       </c>
       <c r="J52" t="n">
-        <v>12.4467</v>
+        <v>11.7096</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1113</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>2.3373</v>
+        <v>1.8564</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3571</v>
+        <v>-0.2274</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.4991</v>
+        <v>-4.7754</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.445</v>
+        <v>-0.2863</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.345000000000001</v>
+        <v>-6.0123</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5923</v>
+        <v>-0.3906</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.4383</v>
+        <v>-8.2026</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8123</v>
+        <v>0.6005</v>
       </c>
       <c r="J57" t="n">
-        <v>17.0583</v>
+        <v>12.6105</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1839</v>
+        <v>0.2118</v>
       </c>
       <c r="J58" t="n">
-        <v>3.8619</v>
+        <v>4.4478</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1482</v>
+        <v>0.1806</v>
       </c>
       <c r="J59" t="n">
-        <v>3.1122</v>
+        <v>3.7926</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0742</v>
+        <v>0.1138</v>
       </c>
       <c r="J60" t="n">
-        <v>1.5582</v>
+        <v>2.3898</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.99</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1301</v>
+        <v>-0.073</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.7321</v>
+        <v>-1.533</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7916</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>12.6656</v>
+        <v>11.8304</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0804</v>
+        <v>0.0384</v>
       </c>
       <c r="J63" t="n">
-        <v>1.2864</v>
+        <v>0.6143999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.51</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7125</v>
+        <v>-0.4818</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.4</v>
+        <v>-7.7088</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7748</v>
+        <v>-0.5281</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.3968</v>
+        <v>-8.4496</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.37</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8825</v>
+        <v>-0.611</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.12</v>
+        <v>-9.776</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7465</v>
+        <v>1.2431</v>
       </c>
       <c r="J67" t="n">
-        <v>27.944</v>
+        <v>19.8896</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.78</v>
       </c>
       <c r="I68" t="n">
-        <v>1.6135</v>
+        <v>1.1415</v>
       </c>
       <c r="J68" t="n">
-        <v>25.816</v>
+        <v>18.264</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.53</v>
       </c>
       <c r="I69" t="n">
-        <v>1.1278</v>
+        <v>0.8542</v>
       </c>
       <c r="J69" t="n">
-        <v>18.0448</v>
+        <v>13.6672</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.5968</v>
       </c>
       <c r="J70" t="n">
-        <v>10.4592</v>
+        <v>9.5488</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0708</v>
+        <v>0.0166</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.1328</v>
+        <v>0.2656</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8216</v>
+        <v>0.7585</v>
       </c>
       <c r="J72" t="n">
-        <v>14.7888</v>
+        <v>13.653</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.476</v>
+        <v>-0.3131</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.568</v>
+        <v>-5.6358</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5043</v>
+        <v>-0.3321</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.077400000000001</v>
+        <v>-5.9778</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5592</v>
+        <v>-0.3698</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.0656</v>
+        <v>-6.6564</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.638</v>
+        <v>-0.4259</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.484</v>
+        <v>-7.6662</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7826</v>
+        <v>1.2752</v>
       </c>
       <c r="J77" t="n">
-        <v>32.0868</v>
+        <v>22.9536</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7652</v>
+        <v>0.6071</v>
       </c>
       <c r="J78" t="n">
-        <v>13.7736</v>
+        <v>10.9278</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3891</v>
+        <v>0.4147</v>
       </c>
       <c r="J79" t="n">
-        <v>7.0038</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2841</v>
+        <v>0.3531</v>
       </c>
       <c r="J80" t="n">
-        <v>5.1138</v>
+        <v>6.3558</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3835</v>
+        <v>-0.302</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.903</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.25</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5013</v>
+        <v>0.483</v>
       </c>
       <c r="J82" t="n">
-        <v>9.524699999999999</v>
+        <v>9.177</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2592</v>
+        <v>-0.1729</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.9248</v>
+        <v>-3.2851</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2947</v>
+        <v>-0.193</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.5993</v>
+        <v>-3.667</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3597</v>
+        <v>-0.2328</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.8343</v>
+        <v>-4.4232</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5976</v>
+        <v>-0.3954</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.3544</v>
+        <v>-7.5126</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3424</v>
+        <v>0.9474</v>
       </c>
       <c r="J87" t="n">
-        <v>25.5056</v>
+        <v>18.0006</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2045</v>
+        <v>0.8593</v>
       </c>
       <c r="J88" t="n">
-        <v>22.8855</v>
+        <v>16.3267</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.42</v>
       </c>
       <c r="I89" t="n">
-        <v>1.0396</v>
+        <v>0.7569</v>
       </c>
       <c r="J89" t="n">
-        <v>19.7524</v>
+        <v>14.3811</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3576</v>
+        <v>0.3902</v>
       </c>
       <c r="J90" t="n">
-        <v>6.7944</v>
+        <v>7.4138</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2883</v>
+        <v>-1.3057</v>
       </c>
       <c r="J91" t="n">
-        <v>-24.4777</v>
+        <v>-24.8083</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.89</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9555</v>
+        <v>1.6597</v>
       </c>
       <c r="J92" t="n">
-        <v>54.754</v>
+        <v>46.4716</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4317</v>
+        <v>0.4263</v>
       </c>
       <c r="J93" t="n">
-        <v>12.0876</v>
+        <v>11.9364</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2589</v>
+        <v>0.2933</v>
       </c>
       <c r="J94" t="n">
-        <v>7.2492</v>
+        <v>8.212400000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.8698</v>
+        <v>-0.8307</v>
       </c>
       <c r="J95" t="n">
-        <v>-24.3544</v>
+        <v>-23.2596</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.72</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8923</v>
+        <v>-0.8554</v>
       </c>
       <c r="J96" t="n">
-        <v>-24.9844</v>
+        <v>-23.9512</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.11</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2802</v>
+        <v>0.296</v>
       </c>
       <c r="J97" t="n">
-        <v>7.8456</v>
+        <v>8.288</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2637</v>
+        <v>0.275</v>
       </c>
       <c r="J98" t="n">
-        <v>7.3836</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.82</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3268</v>
+        <v>-0.2076</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.150399999999999</v>
+        <v>-5.8128</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.417</v>
+        <v>-0.2671</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.676</v>
+        <v>-7.4788</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4455</v>
+        <v>-0.2865</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.474</v>
+        <v>-8.022</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>1.5995</v>
+        <v>1.3922</v>
       </c>
       <c r="J102" t="n">
-        <v>33.5895</v>
+        <v>29.2362</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.4895</v>
+        <v>1.3197</v>
       </c>
       <c r="J103" t="n">
-        <v>31.2795</v>
+        <v>27.7137</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.41</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9923</v>
+        <v>1.0017</v>
       </c>
       <c r="J104" t="n">
-        <v>20.8383</v>
+        <v>21.0357</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1998</v>
+        <v>0.2823</v>
       </c>
       <c r="J105" t="n">
-        <v>4.1958</v>
+        <v>5.9283</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.54</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.2947</v>
+        <v>-1.3139</v>
       </c>
       <c r="J106" t="n">
-        <v>-27.1887</v>
+        <v>-27.5919</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5164</v>
+        <v>0.6078</v>
       </c>
       <c r="J107" t="n">
-        <v>10.8444</v>
+        <v>12.7638</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0567</v>
+        <v>-0.0618</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.1907</v>
+        <v>-1.2978</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2927</v>
+        <v>-0.1926</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.1467</v>
+        <v>-4.0446</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4187</v>
+        <v>-0.2713</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.7927</v>
+        <v>-5.6973</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7095</v>
+        <v>-0.478</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.8995</v>
+        <v>-10.038</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0286</v>
+        <v>1.0074</v>
       </c>
       <c r="J112" t="n">
-        <v>23.6578</v>
+        <v>23.1702</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.32</v>
       </c>
       <c r="I113" t="n">
-        <v>0.875</v>
+        <v>0.8613</v>
       </c>
       <c r="J113" t="n">
-        <v>20.125</v>
+        <v>19.8099</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3065</v>
+        <v>0.3447</v>
       </c>
       <c r="J114" t="n">
-        <v>7.0495</v>
+        <v>7.9281</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.02</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0058</v>
+        <v>0.0641</v>
       </c>
       <c r="J115" t="n">
-        <v>0.1334</v>
+        <v>1.4743</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6392</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.7016</v>
+        <v>-13.3423</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.472</v>
+        <v>0.552</v>
       </c>
       <c r="J117" t="n">
-        <v>10.856</v>
+        <v>12.696</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.02</v>
       </c>
       <c r="I118" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0684</v>
       </c>
       <c r="J118" t="n">
-        <v>1.7342</v>
+        <v>1.5732</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0262</v>
+        <v>-0.0198</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.6026</v>
+        <v>-0.4554</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.92</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1877</v>
+        <v>-0.1102</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.3171</v>
+        <v>-2.5346</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4644</v>
+        <v>-0.2964</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.6812</v>
+        <v>-6.8172</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5111</v>
+        <v>1.3357</v>
       </c>
       <c r="J122" t="n">
-        <v>27.1998</v>
+        <v>24.0426</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8834</v>
+        <v>0.92</v>
       </c>
       <c r="J123" t="n">
-        <v>15.9012</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8597</v>
+        <v>0.8991</v>
       </c>
       <c r="J124" t="n">
-        <v>15.4746</v>
+        <v>16.1838</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.34</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8105</v>
+        <v>0.8562</v>
       </c>
       <c r="J125" t="n">
-        <v>14.589</v>
+        <v>15.4116</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6363</v>
+        <v>-0.5705</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.4534</v>
+        <v>-10.269</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8702</v>
+        <v>1.0709</v>
       </c>
       <c r="J127" t="n">
-        <v>15.6636</v>
+        <v>19.2762</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2579</v>
+        <v>-0.1728</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.6422</v>
+        <v>-3.1104</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.71</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.578799999999999</v>
+        <v>-5.5818</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4905</v>
+        <v>-0.3197</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.829000000000001</v>
+        <v>-5.7546</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7219</v>
+        <v>-0.4874</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.9942</v>
+        <v>-8.773199999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.44</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6813</v>
+        <v>0.8377</v>
       </c>
       <c r="J132" t="n">
-        <v>24.5268</v>
+        <v>30.1572</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2952</v>
+        <v>0.3349</v>
       </c>
       <c r="J133" t="n">
-        <v>10.6272</v>
+        <v>12.0564</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1949</v>
+        <v>0.2176</v>
       </c>
       <c r="J134" t="n">
-        <v>7.0164</v>
+        <v>7.8336</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4338</v>
+        <v>-0.2731</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.6168</v>
+        <v>-9.8316</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4744</v>
+        <v>-0.3022</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.0784</v>
+        <v>-10.8792</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9646</v>
+        <v>0.946</v>
       </c>
       <c r="J137" t="n">
-        <v>34.7256</v>
+        <v>34.056</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6622</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>23.8392</v>
+        <v>22.8816</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6116</v>
+        <v>0.5856</v>
       </c>
       <c r="J139" t="n">
-        <v>22.0176</v>
+        <v>21.0816</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.11</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3578</v>
+        <v>0.3512</v>
       </c>
       <c r="J140" t="n">
-        <v>12.8808</v>
+        <v>12.6432</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.1854</v>
+        <v>-1.1852</v>
       </c>
       <c r="J141" t="n">
-        <v>-42.6744</v>
+        <v>-42.6672</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4014</v>
+        <v>0.4504</v>
       </c>
       <c r="J142" t="n">
-        <v>7.2252</v>
+        <v>8.107200000000001</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2029</v>
+        <v>0.1909</v>
       </c>
       <c r="J143" t="n">
-        <v>3.6522</v>
+        <v>3.4362</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.88</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1734</v>
+        <v>-0.1389</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.1212</v>
+        <v>-2.5002</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.55</v>
+        <v>-0.3627</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.9</v>
+        <v>-6.5286</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.42</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8355</v>
+        <v>-0.5745</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.039</v>
+        <v>-10.341</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.9</v>
       </c>
       <c r="I147" t="n">
-        <v>1.9089</v>
+        <v>1.6086</v>
       </c>
       <c r="J147" t="n">
-        <v>34.3602</v>
+        <v>28.9548</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.3</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7411</v>
+        <v>0.7759</v>
       </c>
       <c r="J148" t="n">
-        <v>13.3398</v>
+        <v>13.9662</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5181</v>
+        <v>0.5946</v>
       </c>
       <c r="J149" t="n">
-        <v>9.325799999999999</v>
+        <v>10.7028</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.116</v>
+        <v>0.1962</v>
       </c>
       <c r="J150" t="n">
-        <v>2.088</v>
+        <v>3.5316</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4974</v>
+        <v>-0.4221</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.953200000000001</v>
+        <v>-7.5978</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.81</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9937</v>
+        <v>0.913</v>
       </c>
       <c r="J152" t="n">
-        <v>15.8992</v>
+        <v>14.608</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>12.5408</v>
+        <v>11.3792</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.206</v>
+        <v>0.2284</v>
       </c>
       <c r="J154" t="n">
-        <v>3.296</v>
+        <v>3.6544</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1623</v>
+        <v>0.1891</v>
       </c>
       <c r="J155" t="n">
-        <v>2.5968</v>
+        <v>3.0256</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0174</v>
+        <v>0.0581</v>
       </c>
       <c r="J156" t="n">
-        <v>0.2784</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0822</v>
+        <v>0.0339</v>
       </c>
       <c r="J157" t="n">
-        <v>1.3152</v>
+        <v>0.5424</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0416</v>
+        <v>-0.056</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.6656</v>
+        <v>-0.896</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.89</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1534</v>
+        <v>-0.1275</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.4544</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3596</v>
+        <v>-0.2378</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.7536</v>
+        <v>-3.8048</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7033</v>
+        <v>-0.4737</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.2528</v>
+        <v>-7.5792</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3198</v>
+        <v>0.3488</v>
       </c>
       <c r="J162" t="n">
-        <v>9.2742</v>
+        <v>10.1152</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.2731</v>
+        <v>-1.2789</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2533</v>
+        <v>-0.1587</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.3457</v>
+        <v>-4.6023</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2533</v>
+        <v>-0.1587</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.3457</v>
+        <v>-4.6023</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3795</v>
+        <v>-0.2403</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.0055</v>
+        <v>-6.9687</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.51</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2521</v>
+        <v>1.1594</v>
       </c>
       <c r="J167" t="n">
-        <v>36.3109</v>
+        <v>33.6226</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6319</v>
+        <v>0.6348</v>
       </c>
       <c r="J168" t="n">
-        <v>18.3251</v>
+        <v>18.4092</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3337</v>
+        <v>0.389</v>
       </c>
       <c r="J169" t="n">
-        <v>9.677300000000001</v>
+        <v>11.281</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2758</v>
+        <v>0.335</v>
       </c>
       <c r="J170" t="n">
-        <v>7.9982</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4133</v>
+        <v>-0.3394</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.9857</v>
+        <v>-9.842599999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3436</v>
+        <v>0.3728</v>
       </c>
       <c r="J172" t="n">
-        <v>6.5284</v>
+        <v>7.0832</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.98</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0242</v>
+        <v>-0.0131</v>
       </c>
       <c r="J173" t="n">
-        <v>0.4598</v>
+        <v>-0.2489</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4786</v>
+        <v>-0.3142</v>
       </c>
       <c r="J174" t="n">
-        <v>-9.093400000000001</v>
+        <v>-5.9698</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5067</v>
+        <v>-0.3332</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.6273</v>
+        <v>-6.3308</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.64</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5613</v>
+        <v>-0.371</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.6647</v>
+        <v>-7.049</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.88</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8803</v>
+        <v>1.5851</v>
       </c>
       <c r="J177" t="n">
-        <v>35.7257</v>
+        <v>30.1169</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5437</v>
+        <v>0.6183</v>
       </c>
       <c r="J178" t="n">
-        <v>10.3303</v>
+        <v>11.7477</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3379</v>
+        <v>0.4199</v>
       </c>
       <c r="J179" t="n">
-        <v>6.4201</v>
+        <v>7.9781</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2849</v>
+        <v>0.367</v>
       </c>
       <c r="J180" t="n">
-        <v>5.4131</v>
+        <v>6.973</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1494</v>
+        <v>-0.0677</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.8386</v>
+        <v>-1.2863</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.53</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3078</v>
+        <v>1.194</v>
       </c>
       <c r="J182" t="n">
-        <v>37.9262</v>
+        <v>34.626</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9122</v>
+        <v>0.9023</v>
       </c>
       <c r="J183" t="n">
-        <v>26.4538</v>
+        <v>26.1667</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2959</v>
+        <v>0.3419</v>
       </c>
       <c r="J184" t="n">
-        <v>8.581099999999999</v>
+        <v>9.915100000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4874</v>
+        <v>-0.4189</v>
       </c>
       <c r="J185" t="n">
-        <v>-14.1346</v>
+        <v>-12.1481</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5411</v>
+        <v>-0.4752</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.6919</v>
+        <v>-13.7808</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0622</v>
+        <v>0.0274</v>
       </c>
       <c r="J187" t="n">
-        <v>1.8038</v>
+        <v>0.7946</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.97</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0209</v>
+        <v>-0.0373</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.6061</v>
+        <v>-1.0817</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.063</v>
+        <v>-0.0639</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.827</v>
+        <v>-1.8531</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3321</v>
+        <v>-0.2142</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.6309</v>
+        <v>-6.2118</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5476</v>
+        <v>-0.3592</v>
       </c>
       <c r="J191" t="n">
-        <v>-15.8804</v>
+        <v>-10.4168</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2406</v>
+        <v>1.1475</v>
       </c>
       <c r="J192" t="n">
-        <v>28.5338</v>
+        <v>26.3925</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5366</v>
+        <v>0.5111</v>
       </c>
       <c r="J193" t="n">
-        <v>12.3418</v>
+        <v>11.7553</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0319</v>
+        <v>0.0761</v>
       </c>
       <c r="J194" t="n">
-        <v>0.7337</v>
+        <v>1.7503</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4369</v>
+        <v>-0.3734</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.0487</v>
+        <v>-8.588200000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.86</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5464</v>
+        <v>-0.4861</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.5672</v>
+        <v>-11.1803</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.325</v>
+        <v>0.3541</v>
       </c>
       <c r="J197" t="n">
-        <v>7.475</v>
+        <v>8.144299999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2772</v>
+        <v>0.2931</v>
       </c>
       <c r="J198" t="n">
-        <v>6.3756</v>
+        <v>6.7413</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2977</v>
+        <v>-0.1882</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.8471</v>
+        <v>-4.3286</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4048</v>
+        <v>-0.2583</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.3104</v>
+        <v>-5.9409</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.489</v>
+        <v>-0.3164</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.247</v>
+        <v>-7.2772</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5216</v>
+        <v>0.6166</v>
       </c>
       <c r="J202" t="n">
-        <v>11.4752</v>
+        <v>13.5652</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.12</v>
       </c>
       <c r="I203" t="n">
-        <v>0.277</v>
+        <v>0.2987</v>
       </c>
       <c r="J203" t="n">
-        <v>6.094</v>
+        <v>6.5714</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1116</v>
+        <v>0.1005</v>
       </c>
       <c r="J204" t="n">
-        <v>2.4552</v>
+        <v>2.211</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0452</v>
       </c>
       <c r="J205" t="n">
-        <v>1.3794</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9379</v>
+        <v>-0.6567</v>
       </c>
       <c r="J206" t="n">
-        <v>-20.6338</v>
+        <v>-14.4474</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1182</v>
+        <v>1.0801</v>
       </c>
       <c r="J207" t="n">
-        <v>24.6004</v>
+        <v>23.7622</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.97</v>
+        <v>0.9759</v>
       </c>
       <c r="J208" t="n">
-        <v>21.34</v>
+        <v>21.4698</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.28</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7139</v>
+        <v>0.7369</v>
       </c>
       <c r="J209" t="n">
-        <v>15.7058</v>
+        <v>16.2118</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3258</v>
+        <v>0.4009</v>
       </c>
       <c r="J210" t="n">
-        <v>7.1676</v>
+        <v>8.819800000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3103</v>
+        <v>-0.2284</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.8266</v>
+        <v>-5.0248</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.43</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7331</v>
+        <v>0.9165</v>
       </c>
       <c r="J212" t="n">
-        <v>14.662</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1924</v>
+        <v>0.1803</v>
       </c>
       <c r="J213" t="n">
-        <v>3.848</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.74</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.432</v>
+        <v>-0.2805</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.640000000000001</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6594</v>
+        <v>-0.4407</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.188</v>
+        <v>-8.814</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.51</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.733</v>
+        <v>-0.4958</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.66</v>
+        <v>-9.916</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.8</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7289</v>
+        <v>1.4796</v>
       </c>
       <c r="J217" t="n">
-        <v>34.578</v>
+        <v>29.592</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.62</v>
       </c>
       <c r="I218" t="n">
-        <v>1.4008</v>
+        <v>1.2643</v>
       </c>
       <c r="J218" t="n">
-        <v>28.016</v>
+        <v>25.286</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.37</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8859</v>
+        <v>0.9207</v>
       </c>
       <c r="J219" t="n">
-        <v>17.718</v>
+        <v>18.414</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2181</v>
+        <v>-0.1314</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.362</v>
+        <v>-2.628</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7551</v>
+        <v>-0.7008</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.102</v>
+        <v>-14.016</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.65</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9452</v>
+        <v>1.1301</v>
       </c>
       <c r="J222" t="n">
-        <v>20.7944</v>
+        <v>24.8622</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.13</v>
       </c>
       <c r="I223" t="n">
-        <v>0.293</v>
+        <v>0.3187</v>
       </c>
       <c r="J223" t="n">
-        <v>6.446</v>
+        <v>7.0114</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3583</v>
+        <v>-0.224</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.8826</v>
+        <v>-4.928</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6147</v>
+        <v>-0.4063</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.5234</v>
+        <v>-8.938599999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6639</v>
+        <v>-0.4431</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.6058</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.72</v>
       </c>
       <c r="I227" t="n">
-        <v>1.6208</v>
+        <v>1.405</v>
       </c>
       <c r="J227" t="n">
-        <v>35.6576</v>
+        <v>30.91</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7381</v>
       </c>
       <c r="J228" t="n">
-        <v>15.8004</v>
+        <v>16.2382</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7381</v>
       </c>
       <c r="J229" t="n">
-        <v>15.8004</v>
+        <v>16.2382</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.1301</v>
+        <v>0.2052</v>
       </c>
       <c r="J230" t="n">
-        <v>2.8622</v>
+        <v>4.5144</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6181</v>
+        <v>-0.5527</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.5982</v>
+        <v>-12.1594</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4282</v>
+        <v>0.4918</v>
       </c>
       <c r="J232" t="n">
-        <v>8.9922</v>
+        <v>10.3278</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4141</v>
+        <v>0.4733</v>
       </c>
       <c r="J233" t="n">
-        <v>8.696099999999999</v>
+        <v>9.939299999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0334</v>
+        <v>-0.0327</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.7014</v>
+        <v>-0.6867</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4436</v>
+        <v>-0.2828</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.3156</v>
+        <v>-5.9388</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.4151</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.1565</v>
+        <v>-8.7171</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.37</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0136</v>
+        <v>0.9898</v>
       </c>
       <c r="J237" t="n">
-        <v>21.2856</v>
+        <v>20.7858</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.2</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6178</v>
+        <v>0.5889</v>
       </c>
       <c r="J238" t="n">
-        <v>12.9738</v>
+        <v>12.3669</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1482</v>
+        <v>0.1806</v>
       </c>
       <c r="J239" t="n">
-        <v>3.1122</v>
+        <v>3.7926</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0183</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.47</v>
+        <v>-0.3843</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7212</v>
+        <v>-0.6707</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.1452</v>
+        <v>-14.0847</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4173</v>
+        <v>0.4726</v>
       </c>
       <c r="J242" t="n">
-        <v>9.1806</v>
+        <v>10.3972</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2784</v>
+        <v>0.2899</v>
       </c>
       <c r="J243" t="n">
-        <v>6.1248</v>
+        <v>6.3778</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3279</v>
+        <v>-0.213</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.2138</v>
+        <v>-4.686</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5716</v>
+        <v>-0.3767</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.5752</v>
+        <v>-8.2874</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6232</v>
+        <v>-0.414</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.7104</v>
+        <v>-9.108000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.38</v>
       </c>
       <c r="I247" t="n">
-        <v>1.02</v>
+        <v>0.9979</v>
       </c>
       <c r="J247" t="n">
-        <v>22.44</v>
+        <v>21.9538</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7008</v>
+        <v>0.6788</v>
       </c>
       <c r="J248" t="n">
-        <v>15.4176</v>
+        <v>14.9336</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0571</v>
+        <v>0.107</v>
       </c>
       <c r="J249" t="n">
-        <v>1.2562</v>
+        <v>2.354</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0848</v>
+        <v>-0.0255</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.8656</v>
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4462</v>
+        <v>-0.38</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.8164</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.55</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7643</v>
+        <v>0.6821</v>
       </c>
       <c r="J252" t="n">
-        <v>17.5789</v>
+        <v>15.6883</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2409</v>
+        <v>0.2344</v>
       </c>
       <c r="J253" t="n">
-        <v>5.5407</v>
+        <v>5.3912</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.12</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1745</v>
+        <v>0.182</v>
       </c>
       <c r="J254" t="n">
-        <v>4.0135</v>
+        <v>4.186</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.1</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1411</v>
+        <v>0.1542</v>
       </c>
       <c r="J255" t="n">
-        <v>3.2453</v>
+        <v>3.5466</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1248</v>
+        <v>-0.0539</v>
       </c>
       <c r="J256" t="n">
-        <v>-2.8704</v>
+        <v>-1.2397</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.09</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2591</v>
+        <v>0.2034</v>
       </c>
       <c r="J257" t="n">
-        <v>5.9593</v>
+        <v>4.6782</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0639</v>
+        <v>0.0219</v>
       </c>
       <c r="J258" t="n">
-        <v>1.4697</v>
+        <v>0.5037</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.83</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2976</v>
+        <v>-0.1937</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.8448</v>
+        <v>-4.4551</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.77</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3924</v>
+        <v>-0.2532</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.0252</v>
+        <v>-5.8236</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5199</v>
+        <v>-0.3398</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.9577</v>
+        <v>-7.8154</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1492</v>
+        <v>0.1221</v>
       </c>
       <c r="J262" t="n">
-        <v>2.984</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.86</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1973</v>
+        <v>-0.1572</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.946</v>
+        <v>-3.144</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2946</v>
+        <v>-0.2071</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.892</v>
+        <v>-4.142</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3834</v>
+        <v>-0.2548</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.668</v>
+        <v>-5.096</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5976</v>
+        <v>-0.3971</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.952</v>
+        <v>-7.942</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.73</v>
       </c>
       <c r="I267" t="n">
-        <v>1.6351</v>
+        <v>1.4148</v>
       </c>
       <c r="J267" t="n">
-        <v>32.702</v>
+        <v>28.296</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.33</v>
       </c>
       <c r="I268" t="n">
-        <v>0.834</v>
+        <v>0.849</v>
       </c>
       <c r="J268" t="n">
-        <v>16.68</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4839</v>
+        <v>0.5523</v>
       </c>
       <c r="J269" t="n">
-        <v>9.678000000000001</v>
+        <v>11.046</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.05</v>
       </c>
       <c r="I270" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1406</v>
       </c>
       <c r="J270" t="n">
-        <v>1.294</v>
+        <v>2.812</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4046</v>
+        <v>-0.3257</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.092000000000001</v>
+        <v>-6.514</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>1.21</v>
+        <v>1.1535</v>
       </c>
       <c r="J272" t="n">
-        <v>21.78</v>
+        <v>20.763</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>1.149</v>
+        <v>1.1173</v>
       </c>
       <c r="J273" t="n">
-        <v>20.682</v>
+        <v>20.1114</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1283</v>
+        <v>1.1052</v>
       </c>
       <c r="J274" t="n">
-        <v>20.3094</v>
+        <v>19.8936</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.21</v>
       </c>
       <c r="I275" t="n">
-        <v>0.4432</v>
+        <v>0.5463</v>
       </c>
       <c r="J275" t="n">
-        <v>7.9776</v>
+        <v>9.833399999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.2</v>
       </c>
       <c r="I276" t="n">
-        <v>0.4192</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="J276" t="n">
-        <v>7.5456</v>
+        <v>9.390599999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.98</v>
       </c>
       <c r="I277" t="n">
-        <v>0.0573</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>1.0314</v>
+        <v>0.1728</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.79</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.283</v>
+        <v>-0.2195</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.094</v>
+        <v>-3.951</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3178</v>
+        <v>-0.2389</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.7204</v>
+        <v>-4.3002</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.3504</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.426600000000001</v>
+        <v>-6.3072</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6471</v>
+        <v>-0.4346</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.6478</v>
+        <v>-7.8228</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.29</v>
       </c>
       <c r="I282" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J282" t="n">
-        <v>28.8302</v>
+        <v>25.6732</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>2.05</v>
       </c>
       <c r="I283" t="n">
-        <v>1.991</v>
+        <v>1.6997</v>
       </c>
       <c r="J283" t="n">
-        <v>27.874</v>
+        <v>23.7958</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.52</v>
       </c>
       <c r="I284" t="n">
-        <v>1.0437</v>
+        <v>1.1106</v>
       </c>
       <c r="J284" t="n">
-        <v>14.6118</v>
+        <v>15.5484</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.1</v>
       </c>
       <c r="I285" t="n">
-        <v>0.12</v>
+        <v>0.2195</v>
       </c>
       <c r="J285" t="n">
-        <v>1.68</v>
+        <v>3.073</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3512</v>
+        <v>-0.2631</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.9168</v>
+        <v>-3.6834</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1465</v>
+        <v>-0.1395</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.051</v>
+        <v>-1.953</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1789</v>
+        <v>-0.1619</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.5046</v>
+        <v>-2.2666</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2109</v>
+        <v>-0.1838</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.9526</v>
+        <v>-2.5732</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4516</v>
+        <v>-0.3213</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.3224</v>
+        <v>-4.4982</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.22</v>
       </c>
       <c r="I291" t="n">
-        <v>-1.0456</v>
+        <v>-0.7413</v>
       </c>
       <c r="J291" t="n">
-        <v>-14.6384</v>
+        <v>-10.3782</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I292" t="n">
-        <v>0.018</v>
+        <v>-0.0197</v>
       </c>
       <c r="J292" t="n">
-        <v>0.324</v>
+        <v>-0.3546</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.89</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1331</v>
+        <v>-0.1204</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.3958</v>
+        <v>-2.1672</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.83</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2364</v>
+        <v>-0.1849</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.2552</v>
+        <v>-3.3282</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4944</v>
+        <v>-0.3278</v>
       </c>
       <c r="J295" t="n">
-        <v>-8.8992</v>
+        <v>-5.9004</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6438</v>
+        <v>-0.431</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.5884</v>
+        <v>-7.758</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.01</v>
       </c>
       <c r="I297" t="n">
-        <v>2.0131</v>
+        <v>1.7218</v>
       </c>
       <c r="J297" t="n">
-        <v>36.2358</v>
+        <v>30.9924</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.7699</v>
       </c>
       <c r="J298" t="n">
-        <v>12.456</v>
+        <v>13.8582</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.2</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4454</v>
+        <v>0.5364</v>
       </c>
       <c r="J299" t="n">
-        <v>8.017200000000001</v>
+        <v>9.655200000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.19</v>
       </c>
       <c r="I300" t="n">
-        <v>0.4206</v>
+        <v>0.5117</v>
       </c>
       <c r="J300" t="n">
-        <v>7.5708</v>
+        <v>9.210599999999999</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4531</v>
+        <v>-0.3736</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.155799999999999</v>
+        <v>-6.7248</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.01</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2003</v>
+        <v>0.1907</v>
       </c>
       <c r="J302" t="n">
-        <v>3.2048</v>
+        <v>3.0512</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.66</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.4386</v>
+        <v>-0.3273</v>
       </c>
       <c r="J303" t="n">
-        <v>-7.0176</v>
+        <v>-5.2368</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.583</v>
+        <v>-0.3991</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.327999999999999</v>
+        <v>-6.3856</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.55</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.6269</v>
+        <v>-0.427</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.0304</v>
+        <v>-6.832</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.44</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7758</v>
+        <v>-0.5304</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.4128</v>
+        <v>-8.4864</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.15</v>
       </c>
       <c r="I307" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J307" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9193</v>
+        <v>1.0097</v>
       </c>
       <c r="J308" t="n">
-        <v>14.7088</v>
+        <v>16.1552</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7169</v>
+        <v>0.8347</v>
       </c>
       <c r="J309" t="n">
-        <v>11.4704</v>
+        <v>13.3552</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.4462</v>
+        <v>0.5577</v>
       </c>
       <c r="J310" t="n">
-        <v>7.1392</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.2278</v>
+        <v>0.3282</v>
       </c>
       <c r="J311" t="n">
-        <v>3.6448</v>
+        <v>5.2512</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0939</v>
+        <v>8.2803</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4559</v>
+        <v>1.4894</v>
       </c>
       <c r="D2" t="n">
-        <v>3.016</v>
+        <v>3.1452</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0939</v>
+        <v>8.2803</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4518</v>
+        <v>4.5422</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6421</v>
+        <v>3.7381</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7444</v>
+        <v>10.0922</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5866</v>
+        <v>5.4497</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6421</v>
+        <v>3.7381</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>9.2287</v>
+        <v>9.187799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4979</v>
+        <v>5.8273</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9889</v>
+        <v>1.0482</v>
       </c>
       <c r="D3" t="n">
-        <v>1.844</v>
+        <v>2.0285</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4979</v>
+        <v>5.8273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7862</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7117</v>
+        <v>5.0425</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7862</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4088</v>
+        <v>0.4238</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7117</v>
+        <v>5.0425</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>5.120500000000001</v>
+        <v>5.4663</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.299</v>
+        <v>5.3061</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9532</v>
+        <v>0.9544</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7542</v>
+        <v>1.7912</v>
       </c>
       <c r="E4" t="n">
-        <v>5.299</v>
+        <v>5.3061</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9756</v>
+        <v>2.9046</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3234</v>
+        <v>2.4015</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9977</v>
+        <v>4.6891</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5986</v>
+        <v>2.5321</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3234</v>
+        <v>2.4015</v>
       </c>
       <c r="K4" t="n">
         <v>144</v>
@@ -621,7 +621,7 @@
         <v>143</v>
       </c>
       <c r="M4" t="n">
-        <v>4.922</v>
+        <v>4.9336</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8913</v>
+        <v>4.9649</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8798</v>
+        <v>0.8931</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5702</v>
+        <v>1.6359</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8913</v>
+        <v>4.9649</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5943</v>
+        <v>3.5436</v>
       </c>
       <c r="G5" t="n">
-        <v>1.297</v>
+        <v>1.4213</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1777</v>
+        <v>6.7973</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7321</v>
+        <v>3.6705</v>
       </c>
       <c r="J5" t="n">
-        <v>1.297</v>
+        <v>1.4213</v>
       </c>
       <c r="K5" t="n">
         <v>96</v>
@@ -667,7 +667,7 @@
         <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0291</v>
+        <v>5.0918</v>
       </c>
       <c r="N5" t="n">
         <v>133</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9154</v>
+        <v>3.8813</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7043</v>
+        <v>0.6982</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1296</v>
+        <v>1.1426</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9154</v>
+        <v>3.8813</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9378</v>
+        <v>2.8327</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9776</v>
+        <v>1.0486</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8647</v>
+        <v>4.4519</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5294</v>
+        <v>2.404</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9776</v>
+        <v>1.0486</v>
       </c>
       <c r="K6" t="n">
         <v>117</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.507</v>
+        <v>3.4526</v>
       </c>
       <c r="N6" t="n">
         <v>260</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9001</v>
+        <v>3.8496</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7015</v>
+        <v>0.6925</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1227</v>
+        <v>1.1282</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9001</v>
+        <v>3.8496</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3145</v>
+        <v>3.2067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5856</v>
+        <v>0.6429</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1921</v>
+        <v>5.6858</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2196</v>
+        <v>3.0703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5856</v>
+        <v>0.6429</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8052</v>
+        <v>3.7132</v>
       </c>
       <c r="N7" t="n">
         <v>152</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8395</v>
+        <v>3.74</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6906</v>
+        <v>0.6727</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0953</v>
+        <v>1.0783</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8395</v>
+        <v>3.74</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7824</v>
+        <v>3.6495</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0571</v>
+        <v>0.0905</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8405</v>
+        <v>7.1468</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0767</v>
+        <v>3.8592</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0571</v>
+        <v>0.0905</v>
       </c>
       <c r="K8" t="n">
         <v>115</v>
@@ -805,7 +805,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1338</v>
+        <v>3.9497</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7457</v>
+        <v>3.7052</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6738</v>
+        <v>0.6665</v>
       </c>
       <c r="D9" t="n">
-        <v>1.053</v>
+        <v>1.0625</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7457</v>
+        <v>3.7052</v>
       </c>
       <c r="F9" t="n">
-        <v>2.947</v>
+        <v>2.8733</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7987</v>
+        <v>0.8319</v>
       </c>
       <c r="H9" t="n">
-        <v>4.897</v>
+        <v>4.5858</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5462</v>
+        <v>2.4763</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7987</v>
+        <v>0.8319</v>
       </c>
       <c r="K9" t="n">
         <v>117</v>
@@ -851,7 +851,7 @@
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3449</v>
+        <v>3.3082</v>
       </c>
       <c r="N9" t="n">
         <v>260</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6644</v>
+        <v>3.672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6591</v>
+        <v>0.6605</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0163</v>
+        <v>1.0474</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6644</v>
+        <v>3.672</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0892</v>
+        <v>0.0917</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5752</v>
+        <v>3.5803</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0892</v>
+        <v>0.0917</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0464</v>
+        <v>0.0495</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5752</v>
+        <v>3.5803</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6216</v>
+        <v>3.6298</v>
       </c>
       <c r="N10" t="n">
         <v>287</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2405</v>
+        <v>3.1736</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5829</v>
+        <v>0.5709</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8249</v>
+        <v>0.8205</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2405</v>
+        <v>3.1736</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2405</v>
+        <v>3.5637</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.3901</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7559</v>
+        <v>6.8638</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7559</v>
+        <v>3.7064</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.3901</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7559</v>
+        <v>3.3163</v>
       </c>
       <c r="N11" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2063</v>
+        <v>2.9999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5767</v>
+        <v>0.5396</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8095</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2063</v>
+        <v>2.9999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5585</v>
+        <v>3.4456</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3522</v>
+        <v>-0.4457</v>
       </c>
       <c r="H12" t="n">
-        <v>7.0518</v>
+        <v>6.4742</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6666</v>
+        <v>3.496</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3522</v>
+        <v>-0.4457</v>
       </c>
       <c r="K12" t="n">
         <v>96</v>
@@ -989,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3144</v>
+        <v>3.0503</v>
       </c>
       <c r="N12" t="n">
         <v>133</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0386</v>
+        <v>2.9058</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5466</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7338</v>
+        <v>0.6986</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0386</v>
+        <v>2.9058</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4783</v>
+        <v>2.9058</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4397</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7691</v>
+        <v>3.635</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5196</v>
+        <v>3.635</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4397</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0799</v>
+        <v>3.635</v>
       </c>
       <c r="N13" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.513</v>
+        <v>2.5833</v>
       </c>
       <c r="C14" t="n">
-        <v>0.452</v>
+        <v>0.4647</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4965</v>
+        <v>0.5518</v>
       </c>
       <c r="E14" t="n">
-        <v>2.513</v>
+        <v>2.5833</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0576</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4554</v>
+        <v>1.6049</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0576</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4554</v>
+        <v>1.6049</v>
       </c>
       <c r="K14" t="n">
         <v>117</v>
@@ -1081,7 +1081,7 @@
         <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0053</v>
+        <v>2.1332</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4067</v>
+        <v>0.3851</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3828</v>
+        <v>0.3503</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2612</v>
+        <v>2.1408</v>
       </c>
       <c r="N15" t="n">
         <v>139</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3737</v>
+        <v>0.3705</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2999</v>
+        <v>0.3136</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0775</v>
+        <v>2.06</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3538</v>
+        <v>0.3422</v>
       </c>
       <c r="D17" t="n">
-        <v>0.25</v>
+        <v>0.2418</v>
       </c>
       <c r="E17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="F17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="I17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.967</v>
+        <v>1.9023</v>
       </c>
       <c r="N17" t="n">
         <v>139</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8376</v>
+        <v>1.818</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3305</v>
+        <v>0.327</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1916</v>
+        <v>0.2034</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8376</v>
+        <v>1.818</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8376</v>
+        <v>-0.105</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.923</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8376</v>
+        <v>-0.105</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8376</v>
+        <v>-0.0567</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.923</v>
       </c>
       <c r="K18" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8376</v>
+        <v>1.8663</v>
       </c>
       <c r="N18" t="n">
-        <v>146</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.814</v>
+        <v>1.7721</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3263</v>
+        <v>0.3188</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1809</v>
+        <v>0.1825</v>
       </c>
       <c r="E19" t="n">
-        <v>1.814</v>
+        <v>1.7721</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5792</v>
+        <v>1.7721</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7652</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6011</v>
+        <v>1.7721</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8724</v>
+        <v>1.7721</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7652</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1072</v>
+        <v>1.7721</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6883</v>
+        <v>1.684</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3037</v>
+        <v>0.3029</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1242</v>
+        <v>0.1424</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6883</v>
+        <v>1.684</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1331</v>
+        <v>2.4756</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8214</v>
+        <v>-0.7916</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1331</v>
+        <v>3.2736</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0692</v>
+        <v>1.7677</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8214</v>
+        <v>-0.7916</v>
       </c>
       <c r="K20" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7522</v>
+        <v>0.9761000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>260</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6692</v>
+        <v>1.5804</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3003</v>
+        <v>0.2843</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1155</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6692</v>
+        <v>1.5804</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3784</v>
+        <v>2.3155</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.7351</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8935</v>
+        <v>2.7454</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5045</v>
+        <v>1.4825</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.7351</v>
       </c>
       <c r="K21" t="n">
         <v>96</v>
@@ -1403,7 +1403,7 @@
         <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7952999999999999</v>
+        <v>0.7474</v>
       </c>
       <c r="N21" t="n">
         <v>133</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2657</v>
+        <v>0.2589</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0287</v>
+        <v>0.031</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4769</v>
+        <v>1.4393</v>
       </c>
       <c r="N22" t="n">
         <v>139</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2246</v>
+        <v>0.2102</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0743</v>
+        <v>-0.0922</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2486</v>
+        <v>1.1687</v>
       </c>
       <c r="N23" t="n">
         <v>146</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2015</v>
+        <v>0.1964</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1323</v>
+        <v>-0.1271</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1202</v>
+        <v>1.0921</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1998</v>
+        <v>0.1909</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1366</v>
+        <v>-0.1412</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1107</v>
+        <v>1.0611</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7605</v>
+        <v>0.71</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1368</v>
+        <v>0.1277</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2947</v>
+        <v>-0.301</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7605</v>
+        <v>0.71</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6578</v>
+        <v>1.6237</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8973</v>
+        <v>-0.9137</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6578</v>
+        <v>1.6237</v>
       </c>
       <c r="I26" t="n">
-        <v>0.862</v>
+        <v>0.8768</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8973</v>
+        <v>-0.9137</v>
       </c>
       <c r="K26" t="n">
         <v>96</v>
@@ -1633,7 +1633,7 @@
         <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0353</v>
+        <v>-0.03689999999999993</v>
       </c>
       <c r="N26" t="n">
         <v>133</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1018</v>
+        <v>0.1007</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3824</v>
+        <v>-0.3692</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5662</v>
+        <v>0.5601</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2092</v>
+        <v>0.0432</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0376</v>
+        <v>0.0078</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5436</v>
+        <v>-0.6045</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2092</v>
+        <v>0.0432</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7551</v>
+        <v>0.6224</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5792</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7551</v>
+        <v>0.6224</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3926</v>
+        <v>0.3361</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5792</v>
       </c>
       <c r="K28" t="n">
         <v>115</v>
@@ -1725,7 +1725,7 @@
         <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1533</v>
+        <v>-0.2431</v>
       </c>
       <c r="N28" t="n">
         <v>152</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0221</v>
+        <v>0.0025</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5826</v>
+        <v>-0.618</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1227</v>
+        <v>0.0137</v>
       </c>
       <c r="N29" t="n">
         <v>76</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0133</v>
+        <v>-0.0027</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6047</v>
+        <v>-0.631</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0737</v>
+        <v>-0.015</v>
       </c>
       <c r="N30" t="n">
         <v>119</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0112</v>
+        <v>-0.006</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6098</v>
+        <v>-0.6395</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0625</v>
+        <v>-0.0336</v>
       </c>
       <c r="N31" t="n">
         <v>146</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2693</v>
+        <v>-0.1065</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0484</v>
+        <v>-0.0192</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.6727</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2693</v>
+        <v>-0.1065</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2693</v>
+        <v>0.5956</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2693</v>
+        <v>0.5956</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2693</v>
+        <v>0.3216</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2693</v>
+        <v>-0.3804999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>76</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2724</v>
+        <v>-0.2907</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.049</v>
+        <v>-0.0523</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.761</v>
+        <v>-0.7565</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2724</v>
+        <v>-0.2907</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5977</v>
+        <v>-0.2907</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5977</v>
+        <v>-0.2907</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3108</v>
+        <v>-0.2907</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="L33" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5592999999999999</v>
+        <v>-0.2907</v>
       </c>
       <c r="N33" t="n">
-        <v>260</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0784</v>
+        <v>-0.0906</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8348</v>
+        <v>-0.8536</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.436</v>
+        <v>-0.5039</v>
       </c>
       <c r="N34" t="n">
         <v>76</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0902</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8643</v>
+        <v>-0.8759</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5013</v>
+        <v>-0.553</v>
       </c>
       <c r="N35" t="n">
         <v>76</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1053</v>
+        <v>-0.1149</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9024</v>
+        <v>-0.9151</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5856</v>
+        <v>-0.639</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1315</v>
+        <v>-0.1361</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.968</v>
+        <v>-0.9685</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7309</v>
+        <v>-0.7564</v>
       </c>
       <c r="N37" t="n">
         <v>119</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2175</v>
+        <v>-0.224</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1838</v>
+        <v>-1.191</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2089</v>
+        <v>-1.2451</v>
       </c>
       <c r="N38" t="n">
         <v>76</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5026</v>
+        <v>-0.4857</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.8995</v>
+        <v>-1.8535</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.7944</v>
+        <v>-2.7004</v>
       </c>
       <c r="N39" t="n">
         <v>146</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.8932</v>
+        <v>-2.7254</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5204</v>
+        <v>-0.4902</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.9441</v>
+        <v>-1.8649</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.8932</v>
+        <v>-2.7254</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.3681</v>
+        <v>-2.1674</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5251</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.3681</v>
+        <v>-2.1674</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2313</v>
+        <v>-1.1704</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5251</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="K40" t="n">
         <v>115</v>
@@ -2277,7 +2277,7 @@
         <v>37</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7564</v>
+        <v>-1.7284</v>
       </c>
       <c r="N40" t="n">
         <v>152</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.1647</v>
+        <v>-3.6325</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7491</v>
+        <v>-0.6534</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.5182</v>
+        <v>-2.2778</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.1647</v>
+        <v>-3.6325</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.6621</v>
+        <v>-4.1451</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4974</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.6621</v>
+        <v>-4.1451</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4241</v>
+        <v>-2.2383</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4974</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>143</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9267</v>
+        <v>-1.7257</v>
       </c>
       <c r="N41" t="n">
         <v>287</v>
@@ -2429,10 +2429,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6459</v>
+        <v>0.644</v>
       </c>
       <c r="J2" t="n">
-        <v>13.5639</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6348</v>
+        <v>0.6337</v>
       </c>
       <c r="J3" t="n">
-        <v>13.3308</v>
+        <v>13.3077</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0786</v>
+        <v>-0.0844</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.6506</v>
+        <v>-1.7724</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.93</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1159</v>
+        <v>-0.1238</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.4339</v>
+        <v>-2.5998</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2042</v>
+        <v>-0.2142</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.2882</v>
+        <v>-4.4982</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0968</v>
+        <v>0.098</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0328</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.076</v>
+        <v>0.0764</v>
       </c>
       <c r="J8" t="n">
-        <v>1.596</v>
+        <v>1.6044</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.143</v>
+        <v>-0.1593</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.003</v>
+        <v>-3.3453</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1631</v>
+        <v>-0.1798</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.4251</v>
+        <v>-3.7758</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4512</v>
+        <v>-0.4605</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.475199999999999</v>
+        <v>-9.670500000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6925</v>
+        <v>0.6886</v>
       </c>
       <c r="J12" t="n">
-        <v>15.235</v>
+        <v>15.1492</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2828</v>
+        <v>0.2999</v>
       </c>
       <c r="J13" t="n">
-        <v>6.2216</v>
+        <v>6.5978</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2214</v>
+        <v>0.2391</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8708</v>
+        <v>5.2602</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2214</v>
+        <v>0.2391</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8708</v>
+        <v>5.2602</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.197</v>
+        <v>-0.2062</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.334</v>
+        <v>-4.5364</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3576</v>
+        <v>0.3562</v>
       </c>
       <c r="J17" t="n">
-        <v>7.8672</v>
+        <v>7.8364</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1394</v>
+        <v>0.1448</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0668</v>
+        <v>3.1856</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0885</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8502</v>
+        <v>1.947</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.73</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2982</v>
+        <v>-0.3125</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5604</v>
+        <v>-6.875</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4298</v>
+        <v>-0.4392</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.4556</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2762</v>
+        <v>0.2595</v>
       </c>
       <c r="J22" t="n">
-        <v>4.4192</v>
+        <v>4.152</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1165</v>
+        <v>0.1008</v>
       </c>
       <c r="J23" t="n">
-        <v>1.864</v>
+        <v>1.6128</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3142</v>
+        <v>-0.3323</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.0272</v>
+        <v>-5.3168</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3519</v>
+        <v>-0.3685</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.6304</v>
+        <v>-5.896</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6025</v>
+        <v>-0.6044</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.670400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.91</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5576</v>
+        <v>1.6986</v>
       </c>
       <c r="J27" t="n">
-        <v>24.9216</v>
+        <v>27.1776</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1836</v>
+        <v>1.216</v>
       </c>
       <c r="J28" t="n">
-        <v>18.9376</v>
+        <v>19.456</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0439</v>
+        <v>1.0118</v>
       </c>
       <c r="J29" t="n">
-        <v>16.7024</v>
+        <v>16.1888</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>14.5248</v>
+        <v>13.8464</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0.731</v>
+        <v>0.71</v>
       </c>
       <c r="J31" t="n">
-        <v>11.696</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1723</v>
+        <v>0.1588</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1014</v>
+        <v>2.8584</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0728</v>
+        <v>0.053</v>
       </c>
       <c r="J33" t="n">
-        <v>1.3104</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0805</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.449</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.48</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5113</v>
+        <v>-0.5192</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.2034</v>
+        <v>-9.345599999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5849</v>
+        <v>-0.588</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.5282</v>
+        <v>-10.584</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1746</v>
+        <v>1.1954</v>
       </c>
       <c r="J37" t="n">
-        <v>21.1428</v>
+        <v>21.5172</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.51</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1255</v>
+        <v>1.1241</v>
       </c>
       <c r="J38" t="n">
-        <v>20.259</v>
+        <v>20.2338</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.44</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0374</v>
+        <v>0.9972</v>
       </c>
       <c r="J39" t="n">
-        <v>18.6732</v>
+        <v>17.9496</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2704</v>
+        <v>0.2879</v>
       </c>
       <c r="J40" t="n">
-        <v>4.8672</v>
+        <v>5.1822</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2417</v>
+        <v>0.2613</v>
       </c>
       <c r="J41" t="n">
-        <v>4.3506</v>
+        <v>4.7034</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4163</v>
+        <v>0.41</v>
       </c>
       <c r="J42" t="n">
-        <v>12.0727</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0956</v>
+        <v>-0.1081</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.7724</v>
+        <v>-3.1349</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0956</v>
+        <v>-0.1081</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.7724</v>
+        <v>-3.1349</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.3819</v>
+        <v>-4.7966</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1724</v>
+        <v>-0.187</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.9996</v>
+        <v>-5.423</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.962</v>
+        <v>0.8979</v>
       </c>
       <c r="J47" t="n">
-        <v>27.898</v>
+        <v>26.0391</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5567</v>
+        <v>0.5376</v>
       </c>
       <c r="J48" t="n">
-        <v>16.1443</v>
+        <v>15.5904</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4803</v>
+        <v>0.4688</v>
       </c>
       <c r="J49" t="n">
-        <v>13.9287</v>
+        <v>13.5952</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.2823</v>
+        <v>-2.2069</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5985</v>
+        <v>-0.5617</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.3565</v>
+        <v>-16.2893</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5576</v>
+        <v>0.6151</v>
       </c>
       <c r="J52" t="n">
-        <v>11.7096</v>
+        <v>12.9171</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.0895</v>
       </c>
       <c r="J53" t="n">
-        <v>1.8564</v>
+        <v>1.8795</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2274</v>
+        <v>-0.2433</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.7754</v>
+        <v>-5.1093</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2863</v>
+        <v>-0.3013</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.0123</v>
+        <v>-6.3273</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3906</v>
+        <v>-0.4021</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.2026</v>
+        <v>-8.444100000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6005</v>
+        <v>0.661</v>
       </c>
       <c r="J57" t="n">
-        <v>12.6105</v>
+        <v>13.881</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2118</v>
+        <v>0.2187</v>
       </c>
       <c r="J58" t="n">
-        <v>4.4478</v>
+        <v>4.5927</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1806</v>
+        <v>0.189</v>
       </c>
       <c r="J59" t="n">
-        <v>3.7926</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1138</v>
+        <v>0.1245</v>
       </c>
       <c r="J60" t="n">
-        <v>2.3898</v>
+        <v>2.6145</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.99</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.073</v>
+        <v>-0.0721</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.533</v>
+        <v>-1.5141</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.8062</v>
       </c>
       <c r="J62" t="n">
-        <v>11.8304</v>
+        <v>12.8992</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0384</v>
+        <v>0.012</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.51</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4818</v>
+        <v>-0.4918</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.7088</v>
+        <v>-7.8688</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5281</v>
+        <v>-0.5352</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.4496</v>
+        <v>-8.5632</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.37</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.611</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.776</v>
+        <v>-9.798400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2431</v>
+        <v>1.3677</v>
       </c>
       <c r="J67" t="n">
-        <v>19.8896</v>
+        <v>21.8832</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.78</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1415</v>
+        <v>1.2604</v>
       </c>
       <c r="J68" t="n">
-        <v>18.264</v>
+        <v>20.1664</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.53</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8542</v>
+        <v>0.9527</v>
       </c>
       <c r="J69" t="n">
-        <v>13.6672</v>
+        <v>15.2432</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5968</v>
+        <v>0.6707</v>
       </c>
       <c r="J70" t="n">
-        <v>9.5488</v>
+        <v>10.7312</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0166</v>
+        <v>0.0566</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2656</v>
+        <v>0.9056</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7585</v>
+        <v>0.8328</v>
       </c>
       <c r="J72" t="n">
-        <v>13.653</v>
+        <v>14.9904</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3131</v>
+        <v>-0.3295</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.6358</v>
+        <v>-5.931</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3321</v>
+        <v>-0.3479</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.9778</v>
+        <v>-6.2622</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3698</v>
+        <v>-0.3842</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.6564</v>
+        <v>-6.9156</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4259</v>
+        <v>-0.4376</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.6662</v>
+        <v>-7.8768</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2752</v>
+        <v>1.3924</v>
       </c>
       <c r="J77" t="n">
-        <v>22.9536</v>
+        <v>25.0632</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6071</v>
+        <v>0.6764</v>
       </c>
       <c r="J78" t="n">
-        <v>10.9278</v>
+        <v>12.1752</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4147</v>
+        <v>0.46</v>
       </c>
       <c r="J79" t="n">
-        <v>7.4646</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3531</v>
+        <v>0.3732</v>
       </c>
       <c r="J80" t="n">
-        <v>6.3558</v>
+        <v>6.7176</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.302</v>
+        <v>-0.2814</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.436</v>
+        <v>-5.0652</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.25</v>
       </c>
       <c r="I82" t="n">
-        <v>0.483</v>
+        <v>0.5281</v>
       </c>
       <c r="J82" t="n">
-        <v>9.177</v>
+        <v>10.0339</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1729</v>
+        <v>-0.1899</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.2851</v>
+        <v>-3.6081</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.193</v>
+        <v>-0.2101</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.667</v>
+        <v>-3.9919</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2328</v>
+        <v>-0.2497</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.4232</v>
+        <v>-4.7443</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3954</v>
+        <v>-0.4074</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.5126</v>
+        <v>-7.7406</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9474</v>
+        <v>1.0439</v>
       </c>
       <c r="J87" t="n">
-        <v>18.0006</v>
+        <v>19.8341</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8593</v>
+        <v>0.9495</v>
       </c>
       <c r="J88" t="n">
-        <v>16.3267</v>
+        <v>18.0405</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.42</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7569</v>
+        <v>0.839</v>
       </c>
       <c r="J89" t="n">
-        <v>14.3811</v>
+        <v>15.941</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3902</v>
+        <v>0.4266</v>
       </c>
       <c r="J90" t="n">
-        <v>7.4138</v>
+        <v>8.105399999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.3057</v>
+        <v>-1.1727</v>
       </c>
       <c r="J91" t="n">
-        <v>-24.8083</v>
+        <v>-22.2813</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.89</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6597</v>
+        <v>1.6458</v>
       </c>
       <c r="J92" t="n">
-        <v>46.4716</v>
+        <v>46.0824</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4263</v>
+        <v>0.4202</v>
       </c>
       <c r="J93" t="n">
-        <v>11.9364</v>
+        <v>11.7656</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2933</v>
+        <v>0.2971</v>
       </c>
       <c r="J94" t="n">
-        <v>8.212400000000001</v>
+        <v>8.3188</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.8307</v>
+        <v>-0.7664</v>
       </c>
       <c r="J95" t="n">
-        <v>-23.2596</v>
+        <v>-21.4592</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.72</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8554</v>
+        <v>-0.788</v>
       </c>
       <c r="J96" t="n">
-        <v>-23.9512</v>
+        <v>-22.064</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.11</v>
       </c>
       <c r="I97" t="n">
-        <v>0.296</v>
+        <v>0.2933</v>
       </c>
       <c r="J97" t="n">
-        <v>8.288</v>
+        <v>8.212400000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.275</v>
+        <v>0.2734</v>
       </c>
       <c r="J98" t="n">
-        <v>7.7</v>
+        <v>7.6552</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.82</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2076</v>
+        <v>-0.2236</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.8128</v>
+        <v>-6.2608</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2671</v>
+        <v>-0.2824</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.4788</v>
+        <v>-7.9072</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2865</v>
+        <v>-0.3015</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.022</v>
+        <v>-8.442</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3922</v>
+        <v>1.3751</v>
       </c>
       <c r="J102" t="n">
-        <v>29.2362</v>
+        <v>28.8771</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.3197</v>
+        <v>1.2983</v>
       </c>
       <c r="J103" t="n">
-        <v>27.7137</v>
+        <v>27.2643</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.41</v>
       </c>
       <c r="I104" t="n">
-        <v>1.0017</v>
+        <v>0.9493</v>
       </c>
       <c r="J104" t="n">
-        <v>21.0357</v>
+        <v>19.9353</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2823</v>
+        <v>0.2962</v>
       </c>
       <c r="J105" t="n">
-        <v>5.9283</v>
+        <v>6.2202</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.54</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.3139</v>
+        <v>-1.1786</v>
       </c>
       <c r="J106" t="n">
-        <v>-27.5919</v>
+        <v>-24.7506</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6078</v>
+        <v>0.5783</v>
       </c>
       <c r="J107" t="n">
-        <v>12.7638</v>
+        <v>12.1443</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0618</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.2978</v>
+        <v>-1.5813</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1926</v>
+        <v>-0.2098</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.0446</v>
+        <v>-4.4058</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2713</v>
+        <v>-0.2877</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.6973</v>
+        <v>-6.0417</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.478</v>
+        <v>-0.486</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.038</v>
+        <v>-10.206</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0074</v>
+        <v>0.9473</v>
       </c>
       <c r="J112" t="n">
-        <v>23.1702</v>
+        <v>21.7879</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.32</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8613</v>
+        <v>0.8084</v>
       </c>
       <c r="J113" t="n">
-        <v>19.8099</v>
+        <v>18.5932</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3447</v>
+        <v>0.3458</v>
       </c>
       <c r="J114" t="n">
-        <v>7.9281</v>
+        <v>7.9534</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.02</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0641</v>
+        <v>0.0793</v>
       </c>
       <c r="J115" t="n">
-        <v>1.4743</v>
+        <v>1.8239</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5437</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.3423</v>
+        <v>-12.5051</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.552</v>
+        <v>0.5371</v>
       </c>
       <c r="J117" t="n">
-        <v>12.696</v>
+        <v>12.3533</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.02</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
       <c r="J118" t="n">
-        <v>1.5732</v>
+        <v>1.7273</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0198</v>
+        <v>-0.0247</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.4554</v>
+        <v>-0.5681</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.92</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1102</v>
+        <v>-0.1225</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.5346</v>
+        <v>-2.8175</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2964</v>
+        <v>-0.3091</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.8172</v>
+        <v>-7.1093</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3357</v>
+        <v>1.3168</v>
       </c>
       <c r="J122" t="n">
-        <v>24.0426</v>
+        <v>23.7024</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.92</v>
+        <v>0.8699</v>
       </c>
       <c r="J123" t="n">
-        <v>16.56</v>
+        <v>15.6582</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8991</v>
+        <v>0.8511</v>
       </c>
       <c r="J124" t="n">
-        <v>16.1838</v>
+        <v>15.3198</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.34</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8562</v>
+        <v>0.8132</v>
       </c>
       <c r="J125" t="n">
-        <v>15.4116</v>
+        <v>14.6376</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5705</v>
+        <v>-0.5265</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.269</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0709</v>
+        <v>1.0232</v>
       </c>
       <c r="J127" t="n">
-        <v>19.2762</v>
+        <v>18.4176</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1728</v>
+        <v>-0.1898</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.1104</v>
+        <v>-3.4164</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.71</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.5818</v>
+        <v>-5.8572</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3197</v>
+        <v>-0.3347</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.7546</v>
+        <v>-6.0246</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4874</v>
+        <v>-0.4948</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.773199999999999</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.44</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8377</v>
+        <v>0.7984</v>
       </c>
       <c r="J132" t="n">
-        <v>30.1572</v>
+        <v>28.7424</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3349</v>
+        <v>0.3388</v>
       </c>
       <c r="J133" t="n">
-        <v>12.0564</v>
+        <v>12.1968</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2176</v>
+        <v>0.2267</v>
       </c>
       <c r="J134" t="n">
-        <v>7.8336</v>
+        <v>8.161199999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2731</v>
+        <v>-0.2852</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.8316</v>
+        <v>-10.2672</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3022</v>
+        <v>-0.3138</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.8792</v>
+        <v>-11.2968</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.946</v>
+        <v>0.8814</v>
       </c>
       <c r="J137" t="n">
-        <v>34.056</v>
+        <v>31.7304</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="J138" t="n">
-        <v>22.8816</v>
+        <v>21.8592</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5856</v>
+        <v>0.5627</v>
       </c>
       <c r="J139" t="n">
-        <v>21.0816</v>
+        <v>20.2572</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.11</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3512</v>
+        <v>0.3501</v>
       </c>
       <c r="J140" t="n">
-        <v>12.6432</v>
+        <v>12.6036</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.1852</v>
+        <v>-1.0738</v>
       </c>
       <c r="J141" t="n">
-        <v>-42.6672</v>
+        <v>-38.6568</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4504</v>
+        <v>0.4314</v>
       </c>
       <c r="J142" t="n">
-        <v>8.107200000000001</v>
+        <v>7.7652</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1909</v>
+        <v>0.1855</v>
       </c>
       <c r="J143" t="n">
-        <v>3.4362</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.88</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1389</v>
+        <v>-0.1562</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.5002</v>
+        <v>-2.8116</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3627</v>
+        <v>-0.3769</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.5286</v>
+        <v>-6.7842</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.42</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5745</v>
+        <v>-0.5772</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.341</v>
+        <v>-10.3896</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.9</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6086</v>
+        <v>1.602</v>
       </c>
       <c r="J147" t="n">
-        <v>28.9548</v>
+        <v>28.836</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.3</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7759</v>
+        <v>0.7408</v>
       </c>
       <c r="J148" t="n">
-        <v>13.9662</v>
+        <v>13.3344</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5946</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>10.7028</v>
+        <v>10.4238</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1962</v>
+        <v>0.2156</v>
       </c>
       <c r="J150" t="n">
-        <v>3.5316</v>
+        <v>3.8808</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4221</v>
+        <v>-0.3932</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.5978</v>
+        <v>-7.0776</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.81</v>
       </c>
       <c r="I152" t="n">
-        <v>0.913</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>14.608</v>
+        <v>14.3632</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7114</v>
       </c>
       <c r="J153" t="n">
-        <v>11.3792</v>
+        <v>11.3824</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2284</v>
+        <v>0.2504</v>
       </c>
       <c r="J154" t="n">
-        <v>3.6544</v>
+        <v>4.0064</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1891</v>
+        <v>0.2116</v>
       </c>
       <c r="J155" t="n">
-        <v>3.0256</v>
+        <v>3.3856</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0581</v>
+        <v>0.0789</v>
       </c>
       <c r="J156" t="n">
-        <v>0.9296</v>
+        <v>1.2624</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0339</v>
+        <v>0.0251</v>
       </c>
       <c r="J157" t="n">
-        <v>0.5424</v>
+        <v>0.4016</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.056</v>
+        <v>-0.0708</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.896</v>
+        <v>-1.1328</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.89</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1275</v>
+        <v>-0.1446</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.04</v>
+        <v>-2.3136</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2378</v>
+        <v>-0.2557</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.8048</v>
+        <v>-4.0912</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4737</v>
+        <v>-0.4827</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.5792</v>
+        <v>-7.7232</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3488</v>
+        <v>0.3449</v>
       </c>
       <c r="J162" t="n">
-        <v>10.1152</v>
+        <v>10.0021</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.2789</v>
+        <v>-1.5573</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1587</v>
+        <v>-0.1738</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.6023</v>
+        <v>-5.0402</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1587</v>
+        <v>-0.1738</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.6023</v>
+        <v>-5.0402</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2403</v>
+        <v>-0.2555</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.9687</v>
+        <v>-7.4095</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.51</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1594</v>
+        <v>1.1225</v>
       </c>
       <c r="J167" t="n">
-        <v>33.6226</v>
+        <v>32.5525</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6348</v>
+        <v>0.6115</v>
       </c>
       <c r="J168" t="n">
-        <v>18.4092</v>
+        <v>17.7335</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.389</v>
+        <v>0.3888</v>
       </c>
       <c r="J169" t="n">
-        <v>11.281</v>
+        <v>11.2752</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.335</v>
+        <v>0.3391</v>
       </c>
       <c r="J170" t="n">
-        <v>9.715</v>
+        <v>9.8339</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3394</v>
+        <v>-0.322</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.842599999999999</v>
+        <v>-9.337999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3728</v>
+        <v>0.3585</v>
       </c>
       <c r="J172" t="n">
-        <v>7.0832</v>
+        <v>6.8115</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.98</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0131</v>
+        <v>-0.0251</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.2489</v>
+        <v>-0.4769</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3142</v>
+        <v>-0.3304</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.9698</v>
+        <v>-6.2776</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3332</v>
+        <v>-0.3488</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.3308</v>
+        <v>-6.6272</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.64</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.371</v>
+        <v>-0.3851</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.049</v>
+        <v>-7.3169</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.88</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5851</v>
+        <v>1.5774</v>
       </c>
       <c r="J177" t="n">
-        <v>30.1169</v>
+        <v>29.9706</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6183</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>11.7477</v>
+        <v>11.4057</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4199</v>
+        <v>0.4218</v>
       </c>
       <c r="J179" t="n">
-        <v>7.9781</v>
+        <v>8.014200000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I180" t="n">
-        <v>0.367</v>
+        <v>0.3735</v>
       </c>
       <c r="J180" t="n">
-        <v>6.973</v>
+        <v>7.0965</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0677</v>
+        <v>-0.0469</v>
       </c>
       <c r="J181" t="n">
-        <v>-1.2863</v>
+        <v>-0.8911</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.53</v>
       </c>
       <c r="I182" t="n">
-        <v>1.194</v>
+        <v>1.1579</v>
       </c>
       <c r="J182" t="n">
-        <v>34.626</v>
+        <v>33.5791</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9023</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>26.1667</v>
+        <v>24.5137</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3419</v>
+        <v>0.3439</v>
       </c>
       <c r="J184" t="n">
-        <v>9.915100000000001</v>
+        <v>9.973100000000001</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4189</v>
+        <v>-0.3971</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.1481</v>
+        <v>-11.5159</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4752</v>
+        <v>-0.4484</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.7808</v>
+        <v>-13.0036</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="J187" t="n">
-        <v>0.7946</v>
+        <v>0.5713</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.97</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0373</v>
+        <v>-0.0485</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.0817</v>
+        <v>-1.4065</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0639</v>
+        <v>-0.077</v>
       </c>
       <c r="J189" t="n">
-        <v>-1.8531</v>
+        <v>-2.233</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2142</v>
+        <v>-0.231</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.2118</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3592</v>
+        <v>-0.3725</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.4168</v>
+        <v>-10.8025</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1475</v>
+        <v>1.1047</v>
       </c>
       <c r="J192" t="n">
-        <v>26.3925</v>
+        <v>25.4081</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5111</v>
+        <v>0.4955</v>
       </c>
       <c r="J193" t="n">
-        <v>11.7553</v>
+        <v>11.3965</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0761</v>
+        <v>0.0876</v>
       </c>
       <c r="J194" t="n">
-        <v>1.7503</v>
+        <v>2.0148</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3734</v>
+        <v>-0.359</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.588200000000001</v>
+        <v>-8.257</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.86</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4861</v>
+        <v>-0.4617</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.1803</v>
+        <v>-10.6191</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3541</v>
+        <v>0.3488</v>
       </c>
       <c r="J197" t="n">
-        <v>8.144299999999999</v>
+        <v>8.022399999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2931</v>
+        <v>0.2912</v>
       </c>
       <c r="J198" t="n">
-        <v>6.7413</v>
+        <v>6.6976</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1882</v>
+        <v>-0.204</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.3286</v>
+        <v>-4.692</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2583</v>
+        <v>-0.2736</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.9409</v>
+        <v>-6.2928</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3164</v>
+        <v>-0.3304</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.2772</v>
+        <v>-7.5992</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6166</v>
+        <v>0.594</v>
       </c>
       <c r="J202" t="n">
-        <v>13.5652</v>
+        <v>13.068</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.12</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2987</v>
+        <v>0.2997</v>
       </c>
       <c r="J203" t="n">
-        <v>6.5714</v>
+        <v>6.5934</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1005</v>
+        <v>0.1062</v>
       </c>
       <c r="J204" t="n">
-        <v>2.211</v>
+        <v>2.3364</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0452</v>
+        <v>0.0487</v>
       </c>
       <c r="J205" t="n">
-        <v>0.9944</v>
+        <v>1.0714</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6567</v>
+        <v>-0.6523</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.4474</v>
+        <v>-14.3506</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0801</v>
+        <v>1.0384</v>
       </c>
       <c r="J207" t="n">
-        <v>23.7622</v>
+        <v>22.8448</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9759</v>
+        <v>0.9203</v>
       </c>
       <c r="J208" t="n">
-        <v>21.4698</v>
+        <v>20.2466</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.28</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7369</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>16.2118</v>
+        <v>15.5122</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4009</v>
+        <v>0.4029</v>
       </c>
       <c r="J210" t="n">
-        <v>8.819800000000001</v>
+        <v>8.863799999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2284</v>
+        <v>-0.2133</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.0248</v>
+        <v>-4.6926</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.43</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9165</v>
+        <v>0.8548</v>
       </c>
       <c r="J212" t="n">
-        <v>18.33</v>
+        <v>17.096</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1803</v>
+        <v>0.1777</v>
       </c>
       <c r="J213" t="n">
-        <v>3.606</v>
+        <v>3.554</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.74</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2805</v>
+        <v>-0.2968</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.61</v>
+        <v>-5.936</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4407</v>
+        <v>-0.4508</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.814</v>
+        <v>-9.016</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.51</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4958</v>
+        <v>-0.5029</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.916</v>
+        <v>-10.058</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.8</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4796</v>
+        <v>1.4685</v>
       </c>
       <c r="J217" t="n">
-        <v>29.592</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.62</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2643</v>
+        <v>1.2406</v>
       </c>
       <c r="J218" t="n">
-        <v>25.286</v>
+        <v>24.812</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.37</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9207</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>18.414</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1314</v>
+        <v>-0.1129</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.628</v>
+        <v>-2.258</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7008</v>
+        <v>-0.6435</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.016</v>
+        <v>-12.87</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.65</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1301</v>
+        <v>1.0974</v>
       </c>
       <c r="J222" t="n">
-        <v>24.8622</v>
+        <v>24.1428</v>
       </c>
     </row>
     <row r="223">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.224</v>
+        <v>-0.2386</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.928</v>
+        <v>-5.2492</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4063</v>
+        <v>-0.416</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.938599999999999</v>
+        <v>-9.151999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4431</v>
+        <v>-0.4512</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.926399999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.72</v>
       </c>
       <c r="I227" t="n">
-        <v>1.405</v>
+        <v>1.3864</v>
       </c>
       <c r="J227" t="n">
-        <v>30.91</v>
+        <v>30.5008</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7381</v>
+        <v>0.7059</v>
       </c>
       <c r="J228" t="n">
-        <v>16.2382</v>
+        <v>15.5298</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7381</v>
+        <v>0.7059</v>
       </c>
       <c r="J229" t="n">
-        <v>16.2382</v>
+        <v>15.5298</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2052</v>
+        <v>0.2219</v>
       </c>
       <c r="J230" t="n">
-        <v>4.5144</v>
+        <v>4.8818</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5527</v>
+        <v>-0.514</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.1594</v>
+        <v>-11.308</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4918</v>
+        <v>0.4797</v>
       </c>
       <c r="J232" t="n">
-        <v>10.3278</v>
+        <v>10.0737</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4733</v>
+        <v>0.4626</v>
       </c>
       <c r="J233" t="n">
-        <v>9.939299999999999</v>
+        <v>9.714600000000001</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0327</v>
+        <v>-0.0402</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.6867</v>
+        <v>-0.8442</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2828</v>
+        <v>-0.2967</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.9388</v>
+        <v>-6.2307</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4151</v>
+        <v>-0.4245</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.7171</v>
+        <v>-8.9145</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.37</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9898</v>
+        <v>0.9246</v>
       </c>
       <c r="J237" t="n">
-        <v>20.7858</v>
+        <v>19.4166</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.2</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5889</v>
+        <v>0.5649</v>
       </c>
       <c r="J238" t="n">
-        <v>12.3669</v>
+        <v>11.8629</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1806</v>
+        <v>0.189</v>
       </c>
       <c r="J239" t="n">
-        <v>3.7926</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0183</v>
+        <v>-0.0125</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.3843</v>
+        <v>-0.2625</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6707</v>
+        <v>-0.627</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.0847</v>
+        <v>-13.167</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4726</v>
+        <v>0.455</v>
       </c>
       <c r="J242" t="n">
-        <v>10.3972</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2899</v>
+        <v>0.2843</v>
       </c>
       <c r="J243" t="n">
-        <v>6.3778</v>
+        <v>6.2546</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.213</v>
+        <v>-0.23</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.686</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3767</v>
+        <v>-0.3895</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.2874</v>
+        <v>-8.569000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.414</v>
+        <v>-0.4252</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.108000000000001</v>
+        <v>-9.3544</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.38</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9979</v>
+        <v>0.9353</v>
       </c>
       <c r="J247" t="n">
-        <v>21.9538</v>
+        <v>20.5766</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6788</v>
+        <v>0.6466</v>
       </c>
       <c r="J248" t="n">
-        <v>14.9336</v>
+        <v>14.2252</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.107</v>
+        <v>0.1198</v>
       </c>
       <c r="J249" t="n">
-        <v>2.354</v>
+        <v>2.6356</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0255</v>
+        <v>-0.0175</v>
       </c>
       <c r="J250" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.385</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.38</v>
+        <v>-0.3636</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.359999999999999</v>
+        <v>-7.9992</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.55</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6821</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>15.6883</v>
+        <v>15.6147</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2344</v>
+        <v>0.2519</v>
       </c>
       <c r="J253" t="n">
-        <v>5.3912</v>
+        <v>5.7937</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.12</v>
       </c>
       <c r="I254" t="n">
-        <v>0.182</v>
+        <v>0.1997</v>
       </c>
       <c r="J254" t="n">
-        <v>4.186</v>
+        <v>4.5931</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.1</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1542</v>
+        <v>0.1718</v>
       </c>
       <c r="J255" t="n">
-        <v>3.5466</v>
+        <v>3.9514</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.98</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0539</v>
+        <v>-0.0566</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.2397</v>
+        <v>-1.3018</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.09</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2034</v>
+        <v>0.2051</v>
       </c>
       <c r="J257" t="n">
-        <v>4.6782</v>
+        <v>4.7173</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0219</v>
+        <v>0.0162</v>
       </c>
       <c r="J258" t="n">
-        <v>0.5037</v>
+        <v>0.3726</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.83</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1937</v>
+        <v>-0.2106</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.4551</v>
+        <v>-4.8438</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.77</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2532</v>
+        <v>-0.2696</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.8236</v>
+        <v>-6.2008</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.68</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3398</v>
+        <v>-0.3539</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.8154</v>
+        <v>-8.139699999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1221</v>
+        <v>0.1142</v>
       </c>
       <c r="J262" t="n">
-        <v>2.442</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.86</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1572</v>
+        <v>-0.1754</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.144</v>
+        <v>-3.508</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2071</v>
+        <v>-0.2255</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.142</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2548</v>
+        <v>-0.2729</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.096</v>
+        <v>-5.458</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3971</v>
+        <v>-0.4104</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.942</v>
+        <v>-8.208</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.73</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4148</v>
+        <v>1.3971</v>
       </c>
       <c r="J267" t="n">
-        <v>28.296</v>
+        <v>27.942</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.33</v>
       </c>
       <c r="I268" t="n">
-        <v>0.849</v>
+        <v>0.8041</v>
       </c>
       <c r="J268" t="n">
-        <v>16.98</v>
+        <v>16.082</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5523</v>
+        <v>0.5399</v>
       </c>
       <c r="J269" t="n">
-        <v>11.046</v>
+        <v>10.798</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.05</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1406</v>
+        <v>0.1613</v>
       </c>
       <c r="J270" t="n">
-        <v>2.812</v>
+        <v>3.226</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3257</v>
+        <v>-0.3054</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.514</v>
+        <v>-6.108</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1535</v>
+        <v>1.1247</v>
       </c>
       <c r="J272" t="n">
-        <v>20.763</v>
+        <v>20.2446</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1173</v>
+        <v>1.0855</v>
       </c>
       <c r="J273" t="n">
-        <v>20.1114</v>
+        <v>19.539</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1052</v>
+        <v>1.0723</v>
       </c>
       <c r="J274" t="n">
-        <v>19.8936</v>
+        <v>19.3014</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.21</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5463</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J275" t="n">
-        <v>9.833399999999999</v>
+        <v>9.734400000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.2</v>
       </c>
       <c r="I276" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5188</v>
       </c>
       <c r="J276" t="n">
-        <v>9.390599999999999</v>
+        <v>9.3384</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.98</v>
       </c>
       <c r="I277" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0107</v>
       </c>
       <c r="J277" t="n">
-        <v>0.1728</v>
+        <v>-0.1926</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.79</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2195</v>
+        <v>-0.2396</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.951</v>
+        <v>-4.3128</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2389</v>
+        <v>-0.2587</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.3002</v>
+        <v>-4.6566</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3504</v>
+        <v>-0.3673</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.3072</v>
+        <v>-6.6114</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4346</v>
+        <v>-0.4475</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.8228</v>
+        <v>-8.055</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.29</v>
       </c>
       <c r="I282" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J282" t="n">
-        <v>25.6732</v>
+        <v>27.1208</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>2.05</v>
       </c>
       <c r="I283" t="n">
-        <v>1.6997</v>
+        <v>1.7095</v>
       </c>
       <c r="J283" t="n">
-        <v>23.7958</v>
+        <v>23.933</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.52</v>
       </c>
       <c r="I284" t="n">
-        <v>1.1106</v>
+        <v>1.0825</v>
       </c>
       <c r="J284" t="n">
-        <v>15.5484</v>
+        <v>15.155</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.1</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2195</v>
+        <v>0.2522</v>
       </c>
       <c r="J285" t="n">
-        <v>3.073</v>
+        <v>3.5308</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2631</v>
+        <v>-0.2286</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.6834</v>
+        <v>-3.2004</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1395</v>
+        <v>-0.164</v>
       </c>
       <c r="J287" t="n">
-        <v>-1.953</v>
+        <v>-2.296</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1619</v>
+        <v>-0.1861</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.2666</v>
+        <v>-2.6054</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.1838</v>
+        <v>-0.2075</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.5732</v>
+        <v>-2.905</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3213</v>
+        <v>-0.3414</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.4982</v>
+        <v>-4.7796</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.22</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7413</v>
+        <v>-0.7333</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.3782</v>
+        <v>-10.2662</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0197</v>
+        <v>-0.0348</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.3546</v>
+        <v>-0.6264</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.89</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1204</v>
+        <v>-0.1392</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.1672</v>
+        <v>-2.5056</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.83</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1849</v>
+        <v>-0.204</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.3282</v>
+        <v>-3.672</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3278</v>
+        <v>-0.3445</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.9004</v>
+        <v>-6.201</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.431</v>
+        <v>-0.4431</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.758</v>
+        <v>-7.9758</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.01</v>
       </c>
       <c r="I297" t="n">
-        <v>1.7218</v>
+        <v>1.7222</v>
       </c>
       <c r="J297" t="n">
-        <v>30.9924</v>
+        <v>30.9996</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7699</v>
+        <v>0.7368</v>
       </c>
       <c r="J298" t="n">
-        <v>13.8582</v>
+        <v>13.2624</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.2</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5364</v>
+        <v>0.529</v>
       </c>
       <c r="J299" t="n">
-        <v>9.655200000000001</v>
+        <v>9.522</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.19</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5117</v>
+        <v>0.5067</v>
       </c>
       <c r="J300" t="n">
-        <v>9.210599999999999</v>
+        <v>9.1206</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3736</v>
+        <v>-0.346</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.7248</v>
+        <v>-6.228</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.01</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1907</v>
+        <v>0.1557</v>
       </c>
       <c r="J302" t="n">
-        <v>3.0512</v>
+        <v>2.4912</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.66</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3273</v>
+        <v>-0.3478</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.2368</v>
+        <v>-5.5648</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3991</v>
+        <v>-0.4167</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.3856</v>
+        <v>-6.6672</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.55</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.832</v>
+        <v>-7.0896</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.44</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5304</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.4864</v>
+        <v>-8.636799999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.15</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8338</v>
+        <v>1.8512</v>
       </c>
       <c r="J307" t="n">
-        <v>29.3408</v>
+        <v>29.6192</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0097</v>
+        <v>0.9635</v>
       </c>
       <c r="J308" t="n">
-        <v>16.1552</v>
+        <v>15.416</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.8347</v>
+        <v>0.7986</v>
       </c>
       <c r="J309" t="n">
-        <v>13.3552</v>
+        <v>12.7776</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5577</v>
+        <v>0.5535</v>
       </c>
       <c r="J310" t="n">
-        <v>8.9232</v>
+        <v>8.856</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3282</v>
+        <v>0.3464</v>
       </c>
       <c r="J311" t="n">
-        <v>5.2512</v>
+        <v>5.5424</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2803</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4894</v>
+        <v>1.5576</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1452</v>
+        <v>3.254</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2803</v>
+        <v>8.659000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>4.5422</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8273</v>
+        <v>5.7438</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0482</v>
+        <v>1.0332</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0285</v>
+        <v>1.9518</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8273</v>
+        <v>5.7438</v>
       </c>
       <c r="F3" t="n">
         <v>0.7848000000000001</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3061</v>
+        <v>5.3865</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9544</v>
+        <v>0.9689</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7912</v>
+        <v>1.7922</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3061</v>
+        <v>5.3865</v>
       </c>
       <c r="F4" t="n">
         <v>2.9046</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9649</v>
+        <v>5.2463</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8931</v>
+        <v>0.9437</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6359</v>
+        <v>1.7296</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9649</v>
+        <v>5.2463</v>
       </c>
       <c r="F5" t="n">
         <v>3.5436</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8813</v>
+        <v>3.9931</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6982</v>
+        <v>0.7183</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1426</v>
+        <v>1.1698</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8813</v>
+        <v>3.9931</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8327</v>
+        <v>2.8374</v>
       </c>
       <c r="G6" t="n">
         <v>1.0486</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4519</v>
+        <v>4.4673</v>
       </c>
       <c r="I6" t="n">
-        <v>2.404</v>
+        <v>2.4123</v>
       </c>
       <c r="J6" t="n">
         <v>1.0486</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4526</v>
+        <v>3.4609</v>
       </c>
       <c r="N6" t="n">
         <v>260</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8496</v>
+        <v>3.9713</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6925</v>
+        <v>0.7143</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1282</v>
+        <v>1.1601</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8496</v>
+        <v>3.9713</v>
       </c>
       <c r="F7" t="n">
         <v>3.2067</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.74</v>
+        <v>3.8806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6727</v>
+        <v>0.698</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0783</v>
+        <v>1.1196</v>
       </c>
       <c r="E8" t="n">
-        <v>3.74</v>
+        <v>3.8806</v>
       </c>
       <c r="F8" t="n">
         <v>3.6495</v>
@@ -814,173 +814,173 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>ArtFr0st</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7052</v>
+        <v>3.731</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6665</v>
+        <v>0.6711</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0625</v>
+        <v>1.0527</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7052</v>
+        <v>3.731</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8733</v>
+        <v>0.0917</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8319</v>
+        <v>3.5803</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5858</v>
+        <v>0.0917</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4763</v>
+        <v>0.0495</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8319</v>
+        <v>3.5803</v>
       </c>
       <c r="K9" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="L9" t="n">
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3082</v>
+        <v>3.6298</v>
       </c>
       <c r="N9" t="n">
-        <v>260</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ArtFr0st</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.672</v>
+        <v>3.7209</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6605</v>
+        <v>0.6693</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0474</v>
+        <v>1.0482</v>
       </c>
       <c r="E10" t="n">
-        <v>3.672</v>
+        <v>3.7209</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0917</v>
+        <v>2.8786</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5803</v>
+        <v>0.8319</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0917</v>
+        <v>4.6032</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0495</v>
+        <v>2.4857</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5803</v>
+        <v>0.8319</v>
       </c>
       <c r="K10" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
         <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6298</v>
+        <v>3.3176</v>
       </c>
       <c r="N10" t="n">
-        <v>287</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1736</v>
+        <v>3.2551</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5709</v>
+        <v>0.5855</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8205</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1736</v>
+        <v>3.2551</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5637</v>
+        <v>2.9058</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8638</v>
+        <v>3.635</v>
       </c>
       <c r="I11" t="n">
-        <v>3.7064</v>
+        <v>3.635</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3163</v>
+        <v>3.635</v>
       </c>
       <c r="N11" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9999</v>
+        <v>3.1876</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5396</v>
+        <v>0.5734</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9999</v>
+        <v>3.1876</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4456</v>
+        <v>3.5637</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4457</v>
+        <v>-0.3901</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4742</v>
+        <v>6.8638</v>
       </c>
       <c r="I12" t="n">
-        <v>3.496</v>
+        <v>3.7064</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4457</v>
+        <v>-0.3901</v>
       </c>
       <c r="K12" t="n">
         <v>96</v>
@@ -989,7 +989,7 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0503</v>
+        <v>3.3163</v>
       </c>
       <c r="N12" t="n">
         <v>133</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9058</v>
+        <v>3.1538</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6986</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9058</v>
+        <v>3.1538</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9058</v>
+        <v>3.4456</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.4457</v>
       </c>
       <c r="H13" t="n">
-        <v>3.635</v>
+        <v>6.4742</v>
       </c>
       <c r="I13" t="n">
-        <v>3.635</v>
+        <v>3.496</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.4457</v>
       </c>
       <c r="K13" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.635</v>
+        <v>3.0503</v>
       </c>
       <c r="N13" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5833</v>
+        <v>2.5789</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4647</v>
+        <v>0.4639</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5518</v>
+        <v>0.5381</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5833</v>
+        <v>2.5789</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9756</v>
       </c>
       <c r="G14" t="n">
         <v>1.6049</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9756</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5283</v>
+        <v>0.5268</v>
       </c>
       <c r="J14" t="n">
         <v>1.6049</v>
@@ -1081,7 +1081,7 @@
         <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1332</v>
+        <v>2.1317</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1408</v>
+        <v>2.1844</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3851</v>
+        <v>0.3929</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3503</v>
+        <v>0.3619</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1408</v>
+        <v>2.1844</v>
       </c>
       <c r="F15" t="n">
         <v>2.1408</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.06</v>
+        <v>2.0484</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3705</v>
+        <v>0.3685</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3136</v>
+        <v>0.3012</v>
       </c>
       <c r="E16" t="n">
-        <v>2.06</v>
+        <v>2.0484</v>
       </c>
       <c r="F16" t="n">
         <v>2.06</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9023</v>
+        <v>1.9284</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3422</v>
+        <v>0.3469</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2418</v>
+        <v>0.2476</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9023</v>
+        <v>1.9284</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9023</v>
+        <v>-0.1065</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.923</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9023</v>
+        <v>-0.1065</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9023</v>
+        <v>-0.0575</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.923</v>
       </c>
       <c r="K17" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9023</v>
+        <v>1.8655</v>
       </c>
       <c r="N17" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.818</v>
+        <v>1.8497</v>
       </c>
       <c r="C18" t="n">
-        <v>0.327</v>
+        <v>0.3327</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2034</v>
+        <v>0.2124</v>
       </c>
       <c r="E18" t="n">
-        <v>1.818</v>
+        <v>1.8497</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.105</v>
+        <v>1.9023</v>
       </c>
       <c r="G18" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.105</v>
+        <v>1.9023</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0567</v>
+        <v>1.9023</v>
       </c>
       <c r="J18" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L18" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8663</v>
+        <v>1.9023</v>
       </c>
       <c r="N18" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7721</v>
+        <v>1.7493</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3188</v>
+        <v>0.3147</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1825</v>
+        <v>0.1676</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7721</v>
+        <v>1.7493</v>
       </c>
       <c r="F19" t="n">
         <v>1.7721</v>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.684</v>
+        <v>1.5999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3029</v>
+        <v>0.2878</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1424</v>
+        <v>0.1008</v>
       </c>
       <c r="E20" t="n">
-        <v>1.684</v>
+        <v>1.5999</v>
       </c>
       <c r="F20" t="n">
         <v>2.4756</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5804</v>
+        <v>1.5749</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2843</v>
+        <v>0.2833</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0897</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5804</v>
+        <v>1.5749</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3155</v>
+        <v>1.4393</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7351</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7454</v>
+        <v>1.4393</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4825</v>
+        <v>1.4393</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7351</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7474</v>
+        <v>1.4393</v>
       </c>
       <c r="N21" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.4393</v>
+        <v>1.3941</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2589</v>
+        <v>0.2508</v>
       </c>
       <c r="D22" t="n">
-        <v>0.031</v>
+        <v>0.0089</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4393</v>
+        <v>1.3941</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4393</v>
+        <v>2.3155</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.7351</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4393</v>
+        <v>2.7454</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4393</v>
+        <v>1.4825</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.7351</v>
       </c>
       <c r="K22" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.4393</v>
+        <v>0.7474</v>
       </c>
       <c r="N22" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1687</v>
+        <v>1.2375</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2102</v>
+        <v>0.2226</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0922</v>
+        <v>-0.0611</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1687</v>
+        <v>1.2375</v>
       </c>
       <c r="F23" t="n">
         <v>1.1687</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0921</v>
+        <v>1.0207</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1964</v>
+        <v>0.1836</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1271</v>
+        <v>-0.1579</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0921</v>
+        <v>1.0207</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0921</v>
+        <v>1.0926</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0921</v>
+        <v>1.0926</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0921</v>
+        <v>1.0926</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0921</v>
+        <v>1.0926</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0611</v>
+        <v>0.8931</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1909</v>
+        <v>0.1606</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1412</v>
+        <v>-0.2149</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0611</v>
+        <v>0.8931</v>
       </c>
       <c r="F25" t="n">
         <v>1.0611</v>
@@ -1596,354 +1596,354 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.71</v>
+        <v>0.6391</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1277</v>
+        <v>0.115</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.301</v>
+        <v>-0.3283</v>
       </c>
       <c r="E26" t="n">
-        <v>0.71</v>
+        <v>0.6391</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6237</v>
+        <v>0.5184</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9137</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6237</v>
+        <v>0.5184</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8768</v>
+        <v>0.5184</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9137</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="L26" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.03689999999999993</v>
+        <v>0.5184</v>
       </c>
       <c r="N26" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5601</v>
+        <v>0.5775</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1007</v>
+        <v>0.1039</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3692</v>
+        <v>-0.3559</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5601</v>
+        <v>0.5775</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5601</v>
+        <v>1.6237</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.9137</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5601</v>
+        <v>1.6237</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5601</v>
+        <v>0.8768</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.9137</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5601</v>
+        <v>-0.03689999999999993</v>
       </c>
       <c r="N27" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0432</v>
+        <v>0.4799</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0078</v>
+        <v>0.0863</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6045</v>
+        <v>-0.3995</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0432</v>
+        <v>0.4799</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6224</v>
+        <v>0.0137</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6224</v>
+        <v>0.0137</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3361</v>
+        <v>0.0137</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="L28" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2431</v>
+        <v>0.0137</v>
       </c>
       <c r="N28" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0137</v>
+        <v>0.0822</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0025</v>
+        <v>0.0148</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.618</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0137</v>
+        <v>0.0822</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0137</v>
+        <v>-0.0301</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0137</v>
+        <v>-0.0301</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0137</v>
+        <v>-0.0301</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0137</v>
+        <v>-0.0301</v>
       </c>
       <c r="N29" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.015</v>
+        <v>-0.0124</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0027</v>
+        <v>-0.0022</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.631</v>
+        <v>-0.6194</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.015</v>
+        <v>-0.0124</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.015</v>
+        <v>0.6224</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.015</v>
+        <v>0.6224</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.015</v>
+        <v>0.3361</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.5792</v>
       </c>
       <c r="K30" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.015</v>
+        <v>-0.2431</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0336</v>
+        <v>-0.1809</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.006</v>
+        <v>-0.0325</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6395</v>
+        <v>-0.6946</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0336</v>
+        <v>-0.1809</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0336</v>
+        <v>0.6511</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0336</v>
+        <v>0.6511</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0336</v>
+        <v>0.3516</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0336</v>
+        <v>-0.3504999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>146</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1065</v>
+        <v>-0.2721</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0192</v>
+        <v>-0.0489</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6727</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1065</v>
+        <v>-0.2721</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5956</v>
+        <v>-0.0336</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5956</v>
+        <v>-0.0336</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3216</v>
+        <v>-0.0336</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="L32" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3804999999999999</v>
+        <v>-0.0336</v>
       </c>
       <c r="N32" t="n">
-        <v>260</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2907</v>
+        <v>-0.2858</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0523</v>
+        <v>-0.0514</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7565</v>
+        <v>-0.7415</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2907</v>
+        <v>-0.2858</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2907</v>
+        <v>-0.5039</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2907</v>
+        <v>-0.5039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2907</v>
+        <v>-0.5039</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2907</v>
+        <v>-0.5039</v>
       </c>
       <c r="N33" t="n">
         <v>76</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5039</v>
+        <v>-0.4867</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0906</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8536</v>
+        <v>-0.8312</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5039</v>
+        <v>-0.4867</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5039</v>
+        <v>-0.2907</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5039</v>
+        <v>-0.2907</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5039</v>
+        <v>-0.2907</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5039</v>
+        <v>-0.2907</v>
       </c>
       <c r="N34" t="n">
         <v>76</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.553</v>
+        <v>-0.798</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1435</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8759</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.553</v>
+        <v>-0.798</v>
       </c>
       <c r="F35" t="n">
         <v>-0.553</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.639</v>
+        <v>-0.8388</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1149</v>
+        <v>-0.1509</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9151</v>
+        <v>-0.9885</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.639</v>
+        <v>-0.8388</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.639</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.639</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.639</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.639</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7564</v>
+        <v>-1.112</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1361</v>
+        <v>-0.2</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9685</v>
+        <v>-1.1105</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7564</v>
+        <v>-1.112</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7564</v>
+        <v>-0.7557</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7564</v>
+        <v>-0.7557</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7564</v>
+        <v>-0.7557</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7564</v>
+        <v>-0.7557</v>
       </c>
       <c r="N37" t="n">
         <v>119</v>
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2944</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.224</v>
+        <v>-0.2328</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.191</v>
+        <v>-1.192</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2944</v>
       </c>
       <c r="F38" t="n">
         <v>-1.2451</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.7004</v>
+        <v>-2.8622</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4857</v>
+        <v>-0.5148</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.8535</v>
+        <v>-1.8923</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.7004</v>
+        <v>-2.8622</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.7004</v>
+        <v>-2.1674</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.7004</v>
+        <v>-2.1674</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.7004</v>
+        <v>-1.1704</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.7004</v>
+        <v>-1.7284</v>
       </c>
       <c r="N39" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7254</v>
+        <v>-2.986</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4902</v>
+        <v>-0.5371</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.8649</v>
+        <v>-1.9476</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.7254</v>
+        <v>-2.986</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.1674</v>
+        <v>-2.7004</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.1674</v>
+        <v>-2.7004</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1704</v>
+        <v>-2.7004</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="L40" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7284</v>
+        <v>-2.7004</v>
       </c>
       <c r="N40" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.6325</v>
+        <v>-3.8971</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6534</v>
+        <v>-0.701</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.2778</v>
+        <v>-2.3546</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.6325</v>
+        <v>-3.8971</v>
       </c>
       <c r="F41" t="n">
         <v>-4.1451</v>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12429,10 +12429,10 @@
         <v>1.55</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6803</v>
       </c>
       <c r="J252" t="n">
-        <v>15.6147</v>
+        <v>15.6469</v>
       </c>
     </row>
     <row r="253">
@@ -12469,16 +12469,16 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2519</v>
+        <v>0.2524</v>
       </c>
       <c r="J253" t="n">
-        <v>5.7937</v>
+        <v>5.8052</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12506,19 +12506,19 @@
         <v>23</v>
       </c>
       <c r="H254" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1997</v>
+        <v>0.1725</v>
       </c>
       <c r="J254" t="n">
-        <v>4.5931</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12546,13 +12546,13 @@
         <v>23</v>
       </c>
       <c r="H255" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1718</v>
+        <v>0.158</v>
       </c>
       <c r="J255" t="n">
-        <v>3.9514</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="256">
@@ -12586,13 +12586,13 @@
         <v>23</v>
       </c>
       <c r="H256" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0566</v>
+        <v>-0.0717</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.3018</v>
+        <v>-1.6491</v>
       </c>
     </row>
     <row r="257">
@@ -12626,13 +12626,13 @@
         <v>23</v>
       </c>
       <c r="H257" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2051</v>
+        <v>0.2351</v>
       </c>
       <c r="J257" t="n">
-        <v>4.7173</v>
+        <v>5.4073</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0162</v>
+        <v>0.0147</v>
       </c>
       <c r="J258" t="n">
-        <v>0.3726</v>
+        <v>0.3381</v>
       </c>
     </row>
     <row r="259">
@@ -12706,13 +12706,13 @@
         <v>23</v>
       </c>
       <c r="H259" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2106</v>
+        <v>-0.2012</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.8438</v>
+        <v>-4.6276</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.77</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2696</v>
+        <v>-0.2704</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.2008</v>
+        <v>-6.2192</v>
       </c>
     </row>
     <row r="261">
@@ -12786,13 +12786,13 @@
         <v>23</v>
       </c>
       <c r="H261" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3539</v>
+        <v>-0.3456</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.139699999999999</v>
+        <v>-7.9488</v>
       </c>
     </row>
     <row r="262">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">

--- a/database/event/7499/event_7499_evp_summary.xlsx
+++ b/database/event/7499/event_7499_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.659000000000001</v>
+        <v>8.353999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5576</v>
+        <v>1.5027</v>
       </c>
       <c r="D2" t="n">
-        <v>3.254</v>
+        <v>3.1999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.659000000000001</v>
+        <v>8.353999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5422</v>
+        <v>4.3291</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7381</v>
+        <v>3.6462</v>
       </c>
       <c r="H2" t="n">
-        <v>10.0922</v>
+        <v>9.810700000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4497</v>
+        <v>5.5084</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7381</v>
+        <v>3.6462</v>
       </c>
       <c r="K2" t="n">
         <v>144</v>
@@ -529,7 +529,7 @@
         <v>143</v>
       </c>
       <c r="M2" t="n">
-        <v>9.187799999999999</v>
+        <v>9.1546</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7438</v>
+        <v>5.6703</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0332</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9518</v>
+        <v>1.9773</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7438</v>
+        <v>5.6703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.6378</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0425</v>
+        <v>5.116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.6378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4238</v>
+        <v>0.3581</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0425</v>
+        <v>5.116</v>
       </c>
       <c r="K3" t="n">
         <v>144</v>
@@ -575,7 +575,7 @@
         <v>143</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4663</v>
+        <v>5.4741</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3865</v>
+        <v>5.2717</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9689</v>
+        <v>0.9483</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7922</v>
+        <v>1.7957</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3865</v>
+        <v>5.2717</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9046</v>
+        <v>2.8637</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4015</v>
+        <v>2.3276</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6891</v>
+        <v>4.3089</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5321</v>
+        <v>2.4193</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4015</v>
+        <v>2.3276</v>
       </c>
       <c r="K4" t="n">
         <v>144</v>
@@ -621,7 +621,7 @@
         <v>143</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9336</v>
+        <v>4.7469</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2463</v>
+        <v>5.1304</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9437</v>
+        <v>0.9228</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7296</v>
+        <v>1.7314</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2463</v>
+        <v>5.1304</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5436</v>
+        <v>3.4622</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4213</v>
+        <v>1.3868</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7973</v>
+        <v>6.5558</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6705</v>
+        <v>3.6809</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4213</v>
+        <v>1.3868</v>
       </c>
       <c r="K5" t="n">
         <v>96</v>
@@ -667,7 +667,7 @@
         <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0918</v>
+        <v>5.0677</v>
       </c>
       <c r="N5" t="n">
         <v>133</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9931</v>
+        <v>3.9525</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7183</v>
+        <v>0.711</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1698</v>
+        <v>1.1948</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9931</v>
+        <v>3.9525</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8374</v>
+        <v>2.8341</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0486</v>
+        <v>1.0113</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4673</v>
+        <v>4.1979</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4123</v>
+        <v>2.357</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0486</v>
+        <v>1.0113</v>
       </c>
       <c r="K6" t="n">
         <v>117</v>
@@ -713,7 +713,7 @@
         <v>143</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4609</v>
+        <v>3.368300000000001</v>
       </c>
       <c r="N6" t="n">
         <v>260</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9713</v>
+        <v>3.9308</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7143</v>
+        <v>0.7071</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1601</v>
+        <v>1.1849</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9713</v>
+        <v>3.9308</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2067</v>
+        <v>3.1657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6429</v>
+        <v>0.6434</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6858</v>
+        <v>5.4427</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0703</v>
+        <v>3.0559</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6429</v>
+        <v>0.6434</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7132</v>
+        <v>3.6993</v>
       </c>
       <c r="N7" t="n">
         <v>152</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8806</v>
+        <v>3.7696</v>
       </c>
       <c r="C8" t="n">
-        <v>0.698</v>
+        <v>0.6781</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1196</v>
+        <v>1.1114</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8806</v>
+        <v>3.7696</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6495</v>
+        <v>3.5547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0905</v>
+        <v>0.0743</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1468</v>
+        <v>6.9031</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8592</v>
+        <v>3.8759</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0905</v>
+        <v>0.0743</v>
       </c>
       <c r="K8" t="n">
         <v>115</v>
@@ -805,7 +805,7 @@
         <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9497</v>
+        <v>3.9502</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.731</v>
+        <v>3.6787</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6711</v>
+        <v>0.6617</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0527</v>
+        <v>1.07</v>
       </c>
       <c r="E9" t="n">
-        <v>3.731</v>
+        <v>3.6787</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0917</v>
+        <v>0.1428</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5803</v>
+        <v>3.4769</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0917</v>
+        <v>0.1428</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0495</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5803</v>
+        <v>3.4769</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6298</v>
+        <v>3.5571</v>
       </c>
       <c r="N9" t="n">
         <v>287</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7209</v>
+        <v>3.5499</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6693</v>
+        <v>0.6385</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0482</v>
+        <v>1.0114</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7209</v>
+        <v>3.5499</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8786</v>
+        <v>2.9243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8319</v>
+        <v>0.6152</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6032</v>
+        <v>4.5363</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4857</v>
+        <v>2.547</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8319</v>
+        <v>0.6152</v>
       </c>
       <c r="K10" t="n">
         <v>117</v>
@@ -897,7 +897,7 @@
         <v>143</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3176</v>
+        <v>3.1622</v>
       </c>
       <c r="N10" t="n">
         <v>260</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2551</v>
+        <v>3.1244</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5855</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.8175</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2551</v>
+        <v>3.1244</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9058</v>
+        <v>3.4805</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.3701</v>
       </c>
       <c r="H11" t="n">
-        <v>3.635</v>
+        <v>6.6248</v>
       </c>
       <c r="I11" t="n">
-        <v>3.635</v>
+        <v>3.7196</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.3701</v>
       </c>
       <c r="K11" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.635</v>
+        <v>3.3495</v>
       </c>
       <c r="N11" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1876</v>
+        <v>3.1145</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5734</v>
+        <v>0.5602</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1876</v>
+        <v>3.1145</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5637</v>
+        <v>2.7652</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6.8638</v>
+        <v>3.3869</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7064</v>
+        <v>3.3869</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3901</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3163</v>
+        <v>3.3869</v>
       </c>
       <c r="N12" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1538</v>
+        <v>3.0479</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5673</v>
+        <v>0.5482</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1538</v>
+        <v>3.0479</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4456</v>
+        <v>3.368</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4457</v>
+        <v>-0.474</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4742</v>
+        <v>6.2021</v>
       </c>
       <c r="I13" t="n">
-        <v>3.496</v>
+        <v>3.4823</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4457</v>
+        <v>-0.474</v>
       </c>
       <c r="K13" t="n">
         <v>96</v>
@@ -1035,7 +1035,7 @@
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0503</v>
+        <v>3.0083</v>
       </c>
       <c r="N13" t="n">
         <v>133</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5789</v>
+        <v>2.6206</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4639</v>
+        <v>0.4714</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5381</v>
+        <v>0.588</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5789</v>
+        <v>2.6206</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9756</v>
+        <v>0.9901</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6049</v>
+        <v>1.6321</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9756</v>
+        <v>0.9901</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5268</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6049</v>
+        <v>1.6321</v>
       </c>
       <c r="K14" t="n">
         <v>117</v>
@@ -1081,7 +1081,7 @@
         <v>143</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1317</v>
+        <v>2.188</v>
       </c>
       <c r="N14" t="n">
         <v>260</v>
@@ -1090,32 +1090,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1844</v>
+        <v>2.1538</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3929</v>
+        <v>0.3874</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3619</v>
+        <v>0.3754</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1844</v>
+        <v>2.1538</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1408</v>
+        <v>2.1654</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1408</v>
+        <v>2.1654</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1408</v>
+        <v>2.1654</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1408</v>
+        <v>2.1654</v>
       </c>
       <c r="N15" t="n">
         <v>139</v>
@@ -1136,32 +1136,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0484</v>
+        <v>2.0634</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3685</v>
+        <v>0.3712</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3012</v>
+        <v>0.3342</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0484</v>
+        <v>2.0634</v>
       </c>
       <c r="F16" t="n">
-        <v>2.06</v>
+        <v>2.0198</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.0198</v>
       </c>
       <c r="I16" t="n">
-        <v>2.06</v>
+        <v>2.0198</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.06</v>
+        <v>2.0198</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9284</v>
+        <v>1.8764</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3469</v>
+        <v>0.3375</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2476</v>
+        <v>0.249</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9284</v>
+        <v>1.8764</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1065</v>
+        <v>1.929</v>
       </c>
       <c r="G17" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1065</v>
+        <v>1.929</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0575</v>
+        <v>1.929</v>
       </c>
       <c r="J17" t="n">
-        <v>1.923</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L17" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8655</v>
+        <v>1.929</v>
       </c>
       <c r="N17" t="n">
-        <v>260</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8497</v>
+        <v>1.7988</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3327</v>
+        <v>0.3236</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2124</v>
+        <v>0.2137</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8497</v>
+        <v>1.7988</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9023</v>
+        <v>-0.0743</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.7612</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9023</v>
+        <v>-0.0743</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9023</v>
+        <v>-0.0417</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.7612</v>
       </c>
       <c r="K18" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9023</v>
+        <v>1.7195</v>
       </c>
       <c r="N18" t="n">
-        <v>139</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7493</v>
+        <v>1.7419</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3147</v>
+        <v>0.3133</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1676</v>
+        <v>0.1877</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7493</v>
+        <v>1.7419</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7721</v>
+        <v>1.7647</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7721</v>
+        <v>1.7647</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7721</v>
+        <v>1.7647</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7721</v>
+        <v>1.7647</v>
       </c>
       <c r="N19" t="n">
         <v>146</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5999</v>
+        <v>1.7241</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2878</v>
+        <v>0.3101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1008</v>
+        <v>0.1796</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5999</v>
+        <v>1.7241</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4756</v>
+        <v>2.5764</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7916</v>
+        <v>-0.7682</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2736</v>
+        <v>3.2303</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7677</v>
+        <v>1.8137</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7916</v>
+        <v>-0.7682</v>
       </c>
       <c r="K20" t="n">
         <v>115</v>
@@ -1357,7 +1357,7 @@
         <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9761000000000001</v>
+        <v>1.0455</v>
       </c>
       <c r="N20" t="n">
         <v>152</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5749</v>
+        <v>1.503</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2833</v>
+        <v>0.2704</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0897</v>
+        <v>0.0789</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5749</v>
+        <v>1.503</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4393</v>
+        <v>2.4024</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.7131</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4393</v>
+        <v>2.577</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4393</v>
+        <v>1.4469</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.7131</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4393</v>
+        <v>0.7338000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3941</v>
+        <v>1.4216</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2508</v>
+        <v>0.2557</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0089</v>
+        <v>0.0418</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3941</v>
+        <v>1.4216</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3155</v>
+        <v>1.286</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7351</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7454</v>
+        <v>1.286</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4825</v>
+        <v>1.286</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7351</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7474</v>
+        <v>1.286</v>
       </c>
       <c r="N22" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2375</v>
+        <v>1.0962</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2226</v>
+        <v>0.1972</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0611</v>
+        <v>-0.1064</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2375</v>
+        <v>1.0962</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1687</v>
+        <v>1.0274</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1687</v>
+        <v>1.0274</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1687</v>
+        <v>1.0274</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1687</v>
+        <v>1.0274</v>
       </c>
       <c r="N23" t="n">
         <v>146</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0207</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1836</v>
+        <v>0.1504</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1579</v>
+        <v>-0.2249</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0207</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0926</v>
+        <v>0.9081</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0926</v>
+        <v>0.9081</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0926</v>
+        <v>0.9081</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0926</v>
+        <v>0.9081</v>
       </c>
       <c r="N24" t="n">
         <v>119</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8931</v>
+        <v>0.7962</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1606</v>
+        <v>0.1432</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2149</v>
+        <v>-0.2431</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8931</v>
+        <v>0.7962</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0611</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0611</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0611</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0611</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>139</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6391</v>
+        <v>0.6183</v>
       </c>
       <c r="C26" t="n">
-        <v>0.115</v>
+        <v>0.1112</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3283</v>
+        <v>-0.3241</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6391</v>
+        <v>0.6183</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5184</v>
+        <v>1.6621</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.9113</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5184</v>
+        <v>1.6621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5184</v>
+        <v>0.9332</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.9113</v>
       </c>
       <c r="K26" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5184</v>
+        <v>0.02190000000000003</v>
       </c>
       <c r="N26" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5775</v>
+        <v>0.4887</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1039</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3559</v>
+        <v>-0.3832</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5775</v>
+        <v>0.4887</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6237</v>
+        <v>0.368</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.9137</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6237</v>
+        <v>0.368</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8768</v>
+        <v>0.368</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9137</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="L27" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.03689999999999993</v>
+        <v>0.368</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4799</v>
+        <v>0.4277</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0863</v>
+        <v>0.0769</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3995</v>
+        <v>-0.411</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4799</v>
+        <v>0.4277</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0137</v>
+        <v>-0.0385</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0137</v>
+        <v>-0.0385</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0137</v>
+        <v>-0.0385</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0137</v>
+        <v>-0.0385</v>
       </c>
       <c r="N28" t="n">
         <v>76</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0822</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0148</v>
+        <v>0.0146</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.5688</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0822</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0301</v>
+        <v>-0.0311</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0301</v>
+        <v>-0.0311</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0301</v>
+        <v>-0.0311</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0301</v>
+        <v>-0.0311</v>
       </c>
       <c r="N29" t="n">
         <v>119</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0124</v>
+        <v>0.0558</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0022</v>
+        <v>0.01</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6194</v>
+        <v>-0.5804</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0124</v>
+        <v>0.0558</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6224</v>
+        <v>0.6552</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5792</v>
+        <v>-0.5438</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6224</v>
+        <v>0.6552</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3361</v>
+        <v>0.3679</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5792</v>
+        <v>-0.5438</v>
       </c>
       <c r="K30" t="n">
         <v>115</v>
@@ -1817,7 +1817,7 @@
         <v>37</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2431</v>
+        <v>-0.1758999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>152</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1809</v>
+        <v>-0.2214</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0325</v>
+        <v>-0.0398</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6946</v>
+        <v>-0.7066</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1809</v>
+        <v>-0.2214</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6511</v>
+        <v>0.6716</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.7631</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6511</v>
+        <v>0.6716</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3516</v>
+        <v>0.3771</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.7631</v>
       </c>
       <c r="K31" t="n">
         <v>117</v>
@@ -1863,7 +1863,7 @@
         <v>143</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3504999999999999</v>
+        <v>-0.386</v>
       </c>
       <c r="N31" t="n">
         <v>260</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2721</v>
+        <v>-0.2595</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0489</v>
+        <v>-0.0467</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.724</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2721</v>
+        <v>-0.2595</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0336</v>
+        <v>-0.021</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0336</v>
+        <v>-0.021</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0336</v>
+        <v>-0.021</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0336</v>
+        <v>-0.021</v>
       </c>
       <c r="N32" t="n">
         <v>146</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2858</v>
+        <v>-0.314</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0514</v>
+        <v>-0.0565</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7415</v>
+        <v>-0.7488</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2858</v>
+        <v>-0.314</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5039</v>
+        <v>-0.5321</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5039</v>
+        <v>-0.5321</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5039</v>
+        <v>-0.5321</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5039</v>
+        <v>-0.5321</v>
       </c>
       <c r="N33" t="n">
         <v>76</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4867</v>
+        <v>-0.5471</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0984</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8312</v>
+        <v>-0.855</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4867</v>
+        <v>-0.5471</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2907</v>
+        <v>-0.3511</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2907</v>
+        <v>-0.3511</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2907</v>
+        <v>-0.3511</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2907</v>
+        <v>-0.3511</v>
       </c>
       <c r="N34" t="n">
         <v>76</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.798</v>
+        <v>-0.8064</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1435</v>
+        <v>-0.1451</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.9731</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.798</v>
+        <v>-0.8064</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.553</v>
+        <v>-0.5614</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.553</v>
+        <v>-0.5614</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.553</v>
+        <v>-0.5614</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.553</v>
+        <v>-0.5614</v>
       </c>
       <c r="N35" t="n">
         <v>76</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8388</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1509</v>
+        <v>-0.156</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9885</v>
+        <v>-1.0009</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8388</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6662</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6662</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6662</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6662</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.112</v>
+        <v>-1.1463</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2</v>
+        <v>-0.2062</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1105</v>
+        <v>-1.128</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.112</v>
+        <v>-1.1463</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7557</v>
+        <v>-0.79</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7557</v>
+        <v>-0.79</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7557</v>
+        <v>-0.79</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7557</v>
+        <v>-0.79</v>
       </c>
       <c r="N37" t="n">
         <v>119</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2944</v>
+        <v>-1.2921</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2328</v>
+        <v>-0.2324</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.192</v>
+        <v>-1.1944</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2944</v>
+        <v>-1.2921</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2428</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2428</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2428</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2451</v>
+        <v>-1.2428</v>
       </c>
       <c r="N38" t="n">
         <v>76</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.8622</v>
+        <v>-2.6843</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5148</v>
+        <v>-0.4828</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.8923</v>
+        <v>-1.8286</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.8622</v>
+        <v>-2.6843</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.1674</v>
+        <v>-2.0238</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.1674</v>
+        <v>-2.0238</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1363</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>115</v>
@@ -2231,7 +2231,7 @@
         <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7284</v>
+        <v>-1.66</v>
       </c>
       <c r="N39" t="n">
         <v>152</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.986</v>
+        <v>-2.9112</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5371</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.9476</v>
+        <v>-1.932</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.986</v>
+        <v>-2.9112</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.7004</v>
+        <v>-2.6256</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.7004</v>
+        <v>-2.6256</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.7004</v>
+        <v>-2.6256</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.7004</v>
+        <v>-2.6256</v>
       </c>
       <c r="N40" t="n">
         <v>146</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8971</v>
+        <v>-3.6292</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.701</v>
+        <v>-0.6528</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3546</v>
+        <v>-2.2591</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8971</v>
+        <v>-3.6292</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.1451</v>
+        <v>-3.9251</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5605</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.1451</v>
+        <v>-3.9251</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2383</v>
+        <v>-2.2038</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5605</v>
       </c>
       <c r="K41" t="n">
         <v>144</v>
@@ -2323,7 +2323,7 @@
         <v>143</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7257</v>
+        <v>-1.6433</v>
       </c>
       <c r="N41" t="n">
         <v>287</v>
@@ -2429,10 +2429,10 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.644</v>
+        <v>0.5725</v>
       </c>
       <c r="J2" t="n">
-        <v>13.524</v>
+        <v>12.0225</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6337</v>
+        <v>0.5623</v>
       </c>
       <c r="J3" t="n">
-        <v>13.3077</v>
+        <v>11.8083</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0844</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7724</v>
+        <v>-1.4406</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.93</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1238</v>
+        <v>-0.1052</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.5998</v>
+        <v>-2.2092</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2142</v>
+        <v>-0.1942</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.4982</v>
+        <v>-4.0782</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.098</v>
+        <v>0.0833</v>
       </c>
       <c r="J7" t="n">
-        <v>2.058</v>
+        <v>1.7493</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0764</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6044</v>
+        <v>1.3272</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1593</v>
+        <v>-0.1416</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.3453</v>
+        <v>-2.9736</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1798</v>
+        <v>-0.1614</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.7758</v>
+        <v>-3.3894</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4605</v>
+        <v>-0.4555</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.670500000000001</v>
+        <v>-9.5655</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6886</v>
+        <v>0.6167</v>
       </c>
       <c r="J12" t="n">
-        <v>15.1492</v>
+        <v>13.5674</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2999</v>
+        <v>0.247</v>
       </c>
       <c r="J13" t="n">
-        <v>6.5978</v>
+        <v>5.434</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.15</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2391</v>
+        <v>0.1933</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2602</v>
+        <v>4.2526</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2391</v>
+        <v>0.1933</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2602</v>
+        <v>4.2526</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.86</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2062</v>
+        <v>-0.1865</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.5364</v>
+        <v>-4.103</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3562</v>
+        <v>0.3501</v>
       </c>
       <c r="J17" t="n">
-        <v>7.8364</v>
+        <v>7.7022</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1448</v>
+        <v>0.1277</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1856</v>
+        <v>2.8094</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0885</v>
+        <v>0.0736</v>
       </c>
       <c r="J19" t="n">
-        <v>1.947</v>
+        <v>1.6192</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.73</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3125</v>
+        <v>-0.295</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.875</v>
+        <v>-6.49</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.59</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4392</v>
+        <v>-0.4323</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.6624</v>
+        <v>-9.5106</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.07</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2595</v>
+        <v>0.2216</v>
       </c>
       <c r="J22" t="n">
-        <v>4.152</v>
+        <v>3.5456</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1008</v>
+        <v>0.0832</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6128</v>
+        <v>1.3312</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3323</v>
+        <v>-0.317</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3168</v>
+        <v>-5.072</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3685</v>
+        <v>-0.3549</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.896</v>
+        <v>-5.6784</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.38</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6044</v>
+        <v>-0.6189</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.670400000000001</v>
+        <v>-9.9024</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.91</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6986</v>
+        <v>1.7308</v>
       </c>
       <c r="J27" t="n">
-        <v>27.1776</v>
+        <v>27.6928</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.58</v>
       </c>
       <c r="I28" t="n">
-        <v>1.216</v>
+        <v>1.2415</v>
       </c>
       <c r="J28" t="n">
-        <v>19.456</v>
+        <v>19.864</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0118</v>
+        <v>1.0181</v>
       </c>
       <c r="J29" t="n">
-        <v>16.1888</v>
+        <v>16.2896</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8596</v>
       </c>
       <c r="J30" t="n">
-        <v>13.8464</v>
+        <v>13.7536</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.3</v>
       </c>
       <c r="I31" t="n">
-        <v>0.71</v>
+        <v>0.6927</v>
       </c>
       <c r="J31" t="n">
-        <v>11.36</v>
+        <v>11.0832</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.03</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1588</v>
+        <v>0.1305</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8584</v>
+        <v>2.349</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.053</v>
+        <v>0.0483</v>
       </c>
       <c r="J33" t="n">
-        <v>0.954</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.92</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.0854</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.7928</v>
+        <v>-1.5372</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.48</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5192</v>
+        <v>-0.5206</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.345599999999999</v>
+        <v>-9.370799999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.588</v>
+        <v>-0.5997</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.584</v>
+        <v>-10.7946</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1954</v>
+        <v>1.2113</v>
       </c>
       <c r="J37" t="n">
-        <v>21.5172</v>
+        <v>21.8034</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.51</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1241</v>
+        <v>1.1321</v>
       </c>
       <c r="J38" t="n">
-        <v>20.2338</v>
+        <v>20.3778</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.44</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9972</v>
+        <v>0.9931</v>
       </c>
       <c r="J39" t="n">
-        <v>17.9496</v>
+        <v>17.8758</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2879</v>
+        <v>0.2563</v>
       </c>
       <c r="J40" t="n">
-        <v>5.1822</v>
+        <v>4.6134</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2613</v>
+        <v>0.2302</v>
       </c>
       <c r="J41" t="n">
-        <v>4.7034</v>
+        <v>4.1436</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.41</v>
+        <v>0.3537</v>
       </c>
       <c r="J42" t="n">
-        <v>11.89</v>
+        <v>10.2573</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.93</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1081</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.1349</v>
+        <v>-2.6477</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1081</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.1349</v>
+        <v>-2.6477</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.88</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.7966</v>
+        <v>-4.2253</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.187</v>
+        <v>-0.1667</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.423</v>
+        <v>-4.8343</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.36</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8979</v>
+        <v>0.8796</v>
       </c>
       <c r="J47" t="n">
-        <v>26.0391</v>
+        <v>25.5084</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5376</v>
+        <v>0.4986</v>
       </c>
       <c r="J48" t="n">
-        <v>15.5904</v>
+        <v>14.4594</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.16</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4688</v>
+        <v>0.4291</v>
       </c>
       <c r="J49" t="n">
-        <v>13.5952</v>
+        <v>12.4439</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.2069</v>
+        <v>-1.6182</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5617</v>
+        <v>-0.5224</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.2893</v>
+        <v>-15.1496</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.33</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6151</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>12.9171</v>
+        <v>12.3942</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0895</v>
+        <v>0.0646</v>
       </c>
       <c r="J53" t="n">
-        <v>1.8795</v>
+        <v>1.3566</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2433</v>
+        <v>-0.2236</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.1093</v>
+        <v>-4.6956</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3013</v>
+        <v>-0.2832</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.3273</v>
+        <v>-5.9472</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.63</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4021</v>
+        <v>-0.3912</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.444100000000001</v>
+        <v>-8.215199999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.661</v>
+        <v>0.6463</v>
       </c>
       <c r="J57" t="n">
-        <v>13.881</v>
+        <v>13.5723</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2187</v>
+        <v>0.1867</v>
       </c>
       <c r="J58" t="n">
-        <v>4.5927</v>
+        <v>3.9207</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.189</v>
+        <v>0.1594</v>
       </c>
       <c r="J59" t="n">
-        <v>3.969</v>
+        <v>3.3474</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1245</v>
+        <v>0.1013</v>
       </c>
       <c r="J60" t="n">
-        <v>2.6145</v>
+        <v>2.1273</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.99</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0721</v>
+        <v>-0.0524</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.5141</v>
+        <v>-1.1004</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.44</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8062</v>
+        <v>0.7966</v>
       </c>
       <c r="J62" t="n">
-        <v>12.8992</v>
+        <v>12.7456</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.99</v>
       </c>
       <c r="I63" t="n">
-        <v>0.012</v>
+        <v>0.0211</v>
       </c>
       <c r="J63" t="n">
-        <v>0.192</v>
+        <v>0.3376</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.51</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4918</v>
+        <v>-0.4895</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.8688</v>
+        <v>-7.832</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.46</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5352</v>
+        <v>-0.5386</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.5632</v>
+        <v>-8.617599999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.37</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.6281</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.798400000000001</v>
+        <v>-10.0496</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.87</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3677</v>
+        <v>1.3749</v>
       </c>
       <c r="J67" t="n">
-        <v>21.8832</v>
+        <v>21.9984</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.78</v>
       </c>
       <c r="I68" t="n">
-        <v>1.2604</v>
+        <v>1.2612</v>
       </c>
       <c r="J68" t="n">
-        <v>20.1664</v>
+        <v>20.1792</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.53</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9527</v>
+        <v>0.9453</v>
       </c>
       <c r="J69" t="n">
-        <v>15.2432</v>
+        <v>15.1248</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6707</v>
+        <v>0.6662</v>
       </c>
       <c r="J70" t="n">
-        <v>10.7312</v>
+        <v>10.6592</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.03</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0566</v>
+        <v>0.0314</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9056</v>
+        <v>0.5024</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.49</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8328</v>
+        <v>0.8146</v>
       </c>
       <c r="J72" t="n">
-        <v>14.9904</v>
+        <v>14.6628</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.7</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3295</v>
+        <v>-0.3133</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.931</v>
+        <v>-5.6394</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.68</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3479</v>
+        <v>-0.3327</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.2622</v>
+        <v>-5.9886</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.64</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3842</v>
+        <v>-0.3714</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.9156</v>
+        <v>-6.6852</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4376</v>
+        <v>-0.4296</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.8768</v>
+        <v>-7.7328</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.85</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3924</v>
+        <v>1.4036</v>
       </c>
       <c r="J77" t="n">
-        <v>25.0632</v>
+        <v>25.2648</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.31</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6764</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>12.1752</v>
+        <v>11.9844</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.17</v>
       </c>
       <c r="I79" t="n">
-        <v>0.46</v>
+        <v>0.4363</v>
       </c>
       <c r="J79" t="n">
-        <v>8.279999999999999</v>
+        <v>7.8534</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3732</v>
+        <v>0.3409</v>
       </c>
       <c r="J80" t="n">
-        <v>6.7176</v>
+        <v>6.1362</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2814</v>
+        <v>-0.2447</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.0652</v>
+        <v>-4.4046</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.25</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5281</v>
+        <v>0.5039</v>
       </c>
       <c r="J82" t="n">
-        <v>10.0339</v>
+        <v>9.5741</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1899</v>
+        <v>-0.1712</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.6081</v>
+        <v>-3.2528</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.83</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2101</v>
+        <v>-0.191</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.9919</v>
+        <v>-3.629</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2497</v>
+        <v>-0.2305</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.7443</v>
+        <v>-4.3795</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.62</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4074</v>
+        <v>-0.3968</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.7406</v>
+        <v>-7.5392</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0439</v>
+        <v>1.0328</v>
       </c>
       <c r="J87" t="n">
-        <v>19.8341</v>
+        <v>19.6232</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9495</v>
+        <v>0.9356</v>
       </c>
       <c r="J88" t="n">
-        <v>18.0405</v>
+        <v>17.7764</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.42</v>
       </c>
       <c r="I89" t="n">
-        <v>0.839</v>
+        <v>0.8239</v>
       </c>
       <c r="J89" t="n">
-        <v>15.941</v>
+        <v>15.6541</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4266</v>
+        <v>0.395</v>
       </c>
       <c r="J90" t="n">
-        <v>8.105399999999999</v>
+        <v>7.505</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.54</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.1727</v>
+        <v>-1.2004</v>
       </c>
       <c r="J91" t="n">
-        <v>-22.2813</v>
+        <v>-22.8076</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.89</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6458</v>
+        <v>1.704</v>
       </c>
       <c r="J92" t="n">
-        <v>46.0824</v>
+        <v>47.712</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4202</v>
+        <v>0.3813</v>
       </c>
       <c r="J93" t="n">
-        <v>11.7656</v>
+        <v>10.6764</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2971</v>
+        <v>0.2619</v>
       </c>
       <c r="J94" t="n">
-        <v>8.3188</v>
+        <v>7.3332</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.7664</v>
+        <v>-0.7406</v>
       </c>
       <c r="J95" t="n">
-        <v>-21.4592</v>
+        <v>-20.7368</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.72</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.788</v>
+        <v>-0.7641</v>
       </c>
       <c r="J96" t="n">
-        <v>-22.064</v>
+        <v>-21.3948</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.11</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2933</v>
+        <v>0.2438</v>
       </c>
       <c r="J97" t="n">
-        <v>8.212400000000001</v>
+        <v>6.8264</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2734</v>
+        <v>0.2253</v>
       </c>
       <c r="J98" t="n">
-        <v>7.6552</v>
+        <v>6.3084</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.82</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2236</v>
+        <v>-0.2037</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.2608</v>
+        <v>-5.7036</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.76</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2824</v>
+        <v>-0.2636</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.9072</v>
+        <v>-7.3808</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3015</v>
+        <v>-0.2834</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.442</v>
+        <v>-7.9352</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.72</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3751</v>
+        <v>1.3988</v>
       </c>
       <c r="J102" t="n">
-        <v>28.8771</v>
+        <v>29.3748</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.66</v>
       </c>
       <c r="I103" t="n">
-        <v>1.2983</v>
+        <v>1.3175</v>
       </c>
       <c r="J103" t="n">
-        <v>27.2643</v>
+        <v>27.6675</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.41</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9493</v>
+        <v>0.9405</v>
       </c>
       <c r="J104" t="n">
-        <v>19.9353</v>
+        <v>19.7505</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2962</v>
+        <v>0.2647</v>
       </c>
       <c r="J105" t="n">
-        <v>6.2202</v>
+        <v>5.5587</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.54</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.1786</v>
+        <v>-1.2086</v>
       </c>
       <c r="J106" t="n">
-        <v>-24.7506</v>
+        <v>-25.3806</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.26</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5783</v>
+        <v>0.526</v>
       </c>
       <c r="J107" t="n">
-        <v>12.1443</v>
+        <v>11.046</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.95</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.5813</v>
+        <v>-1.3251</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2098</v>
+        <v>-0.1908</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.4058</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.75</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2877</v>
+        <v>-0.2694</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.0417</v>
+        <v>-5.6574</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.486</v>
+        <v>-0.4841</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.206</v>
+        <v>-10.1661</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9473</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>21.7879</v>
+        <v>21.505</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.32</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8084</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>18.5932</v>
+        <v>18.0044</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3458</v>
+        <v>0.3097</v>
       </c>
       <c r="J114" t="n">
-        <v>7.9534</v>
+        <v>7.1231</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.02</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0793</v>
+        <v>0.0624</v>
       </c>
       <c r="J115" t="n">
-        <v>1.8239</v>
+        <v>1.4352</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5437</v>
+        <v>-0.5042</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.5051</v>
+        <v>-11.5966</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5371</v>
+        <v>0.4782</v>
       </c>
       <c r="J117" t="n">
-        <v>12.3533</v>
+        <v>10.9986</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.02</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0751</v>
+        <v>0.0534</v>
       </c>
       <c r="J118" t="n">
-        <v>1.7273</v>
+        <v>1.2282</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0247</v>
+        <v>-0.0179</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.5681</v>
+        <v>-0.4117</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.92</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1225</v>
+        <v>-0.1042</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.8175</v>
+        <v>-2.3966</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.74</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3091</v>
+        <v>-0.2917</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.1093</v>
+        <v>-6.7091</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.68</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3168</v>
+        <v>1.3369</v>
       </c>
       <c r="J122" t="n">
-        <v>23.7024</v>
+        <v>24.0642</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.37</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8699</v>
+        <v>0.8554</v>
       </c>
       <c r="J123" t="n">
-        <v>15.6582</v>
+        <v>15.3972</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.36</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8511</v>
+        <v>0.8354</v>
       </c>
       <c r="J124" t="n">
-        <v>15.3198</v>
+        <v>15.0372</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.34</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8132</v>
+        <v>0.7953</v>
       </c>
       <c r="J125" t="n">
-        <v>14.6376</v>
+        <v>14.3154</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.85</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5265</v>
+        <v>-0.4913</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.477</v>
+        <v>-8.843400000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0232</v>
+        <v>1.0148</v>
       </c>
       <c r="J127" t="n">
-        <v>18.4176</v>
+        <v>18.2664</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.85</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1898</v>
+        <v>-0.1711</v>
       </c>
       <c r="J128" t="n">
-        <v>-3.4164</v>
+        <v>-3.0798</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.71</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.8572</v>
+        <v>-5.5566</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3347</v>
+        <v>-0.3185</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.0246</v>
+        <v>-5.733</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.52</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4948</v>
+        <v>-0.4941</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.9064</v>
+        <v>-8.893800000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.44</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7984</v>
+        <v>0.7452</v>
       </c>
       <c r="J132" t="n">
-        <v>28.7424</v>
+        <v>26.8272</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3388</v>
+        <v>0.2861</v>
       </c>
       <c r="J133" t="n">
-        <v>12.1968</v>
+        <v>10.2996</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.09</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2267</v>
+        <v>0.1837</v>
       </c>
       <c r="J134" t="n">
-        <v>8.161199999999999</v>
+        <v>6.6132</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2852</v>
+        <v>-0.2667</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.2672</v>
+        <v>-9.6012</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3138</v>
+        <v>-0.2969</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.2968</v>
+        <v>-10.6884</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.35</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8814</v>
+        <v>0.8616</v>
       </c>
       <c r="J137" t="n">
-        <v>31.7304</v>
+        <v>31.0176</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.22</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6072</v>
+        <v>0.5696</v>
       </c>
       <c r="J138" t="n">
-        <v>21.8592</v>
+        <v>20.5056</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5627</v>
+        <v>0.5238</v>
       </c>
       <c r="J139" t="n">
-        <v>20.2572</v>
+        <v>18.8568</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.11</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3501</v>
+        <v>0.3117</v>
       </c>
       <c r="J140" t="n">
-        <v>12.6036</v>
+        <v>11.2212</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.0738</v>
+        <v>-1.0824</v>
       </c>
       <c r="J141" t="n">
-        <v>-38.6568</v>
+        <v>-38.9664</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.17</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4314</v>
+        <v>0.3801</v>
       </c>
       <c r="J142" t="n">
-        <v>7.7652</v>
+        <v>6.8418</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1855</v>
+        <v>0.1484</v>
       </c>
       <c r="J143" t="n">
-        <v>3.339</v>
+        <v>2.6712</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.88</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1562</v>
+        <v>-0.1396</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.8116</v>
+        <v>-2.5128</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.65</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3769</v>
+        <v>-0.3636</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.7842</v>
+        <v>-6.5448</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.42</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5772</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.3896</v>
+        <v>-10.5876</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.9</v>
       </c>
       <c r="I147" t="n">
-        <v>1.602</v>
+        <v>1.6448</v>
       </c>
       <c r="J147" t="n">
-        <v>28.836</v>
+        <v>29.6064</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.3</v>
       </c>
       <c r="I148" t="n">
-        <v>0.7408</v>
+        <v>0.7169</v>
       </c>
       <c r="J148" t="n">
-        <v>13.3344</v>
+        <v>12.9042</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5494</v>
       </c>
       <c r="J149" t="n">
-        <v>10.4238</v>
+        <v>9.889200000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2156</v>
+        <v>0.1865</v>
       </c>
       <c r="J150" t="n">
-        <v>3.8808</v>
+        <v>3.357</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3932</v>
+        <v>-0.3542</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.0776</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.81</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.8284</v>
       </c>
       <c r="J152" t="n">
-        <v>14.3632</v>
+        <v>13.2544</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.61</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7114</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>11.3824</v>
+        <v>10.2336</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2504</v>
+        <v>0.2054</v>
       </c>
       <c r="J154" t="n">
-        <v>4.0064</v>
+        <v>3.2864</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.14</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2116</v>
+        <v>0.1707</v>
       </c>
       <c r="J155" t="n">
-        <v>3.3856</v>
+        <v>2.7312</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0789</v>
+        <v>0.0565</v>
       </c>
       <c r="J156" t="n">
-        <v>1.2624</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0251</v>
+        <v>0.0231</v>
       </c>
       <c r="J157" t="n">
-        <v>0.4016</v>
+        <v>0.3696</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0708</v>
+        <v>-0.0589</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.1328</v>
+        <v>-0.9424</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.89</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1446</v>
+        <v>-0.1286</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.3136</v>
+        <v>-2.0576</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.78</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2557</v>
+        <v>-0.2373</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.0912</v>
+        <v>-3.7968</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.53</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4827</v>
+        <v>-0.4799</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.7232</v>
+        <v>-7.6784</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3449</v>
+        <v>0.2918</v>
       </c>
       <c r="J162" t="n">
-        <v>10.0021</v>
+        <v>8.462199999999999</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.5573</v>
+        <v>-1.2499</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1738</v>
+        <v>-0.1542</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.0402</v>
+        <v>-4.4718</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1738</v>
+        <v>-0.1542</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.0402</v>
+        <v>-4.4718</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2555</v>
+        <v>-0.2358</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.4095</v>
+        <v>-6.8382</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.51</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1225</v>
+        <v>1.1348</v>
       </c>
       <c r="J167" t="n">
-        <v>32.5525</v>
+        <v>32.9092</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.23</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6115</v>
+        <v>0.5776</v>
       </c>
       <c r="J168" t="n">
-        <v>17.7335</v>
+        <v>16.7504</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3888</v>
+        <v>0.3537</v>
       </c>
       <c r="J169" t="n">
-        <v>11.2752</v>
+        <v>10.2573</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.11</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3391</v>
+        <v>0.3051</v>
       </c>
       <c r="J170" t="n">
-        <v>9.8339</v>
+        <v>8.847899999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.322</v>
+        <v>-0.2814</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.337999999999999</v>
+        <v>-8.160600000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.13</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3585</v>
+        <v>0.3094</v>
       </c>
       <c r="J172" t="n">
-        <v>6.8115</v>
+        <v>5.8786</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.98</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0251</v>
+        <v>-0.0179</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.4769</v>
+        <v>-0.3401</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.7</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3304</v>
+        <v>-0.3142</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.2776</v>
+        <v>-5.9698</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.68</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3488</v>
+        <v>-0.3336</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.6272</v>
+        <v>-6.3384</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.64</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3851</v>
+        <v>-0.3723</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.3169</v>
+        <v>-7.0737</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.88</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5774</v>
+        <v>1.6178</v>
       </c>
       <c r="J177" t="n">
-        <v>29.9706</v>
+        <v>30.7382</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.23</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5712</v>
       </c>
       <c r="J178" t="n">
-        <v>11.4057</v>
+        <v>10.8528</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.15</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4218</v>
+        <v>0.3895</v>
       </c>
       <c r="J179" t="n">
-        <v>8.014200000000001</v>
+        <v>7.4005</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.13</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3735</v>
+        <v>0.3411</v>
       </c>
       <c r="J180" t="n">
-        <v>7.0965</v>
+        <v>6.4809</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.0469</v>
+        <v>-0.042</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.8911</v>
+        <v>-0.798</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.53</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1579</v>
+        <v>1.1719</v>
       </c>
       <c r="J182" t="n">
-        <v>33.5791</v>
+        <v>33.9851</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.34</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8227</v>
       </c>
       <c r="J183" t="n">
-        <v>24.5137</v>
+        <v>23.8583</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.11</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3439</v>
+        <v>0.3085</v>
       </c>
       <c r="J184" t="n">
-        <v>9.973100000000001</v>
+        <v>8.9465</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3971</v>
+        <v>-0.355</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.5159</v>
+        <v>-10.295</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4484</v>
+        <v>-0.4067</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.0036</v>
+        <v>-11.7943</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0197</v>
+        <v>0.0146</v>
       </c>
       <c r="J187" t="n">
-        <v>0.5713</v>
+        <v>0.4234</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.97</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0485</v>
+        <v>-0.0389</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.4065</v>
+        <v>-1.1281</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.95</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.077</v>
+        <v>-0.0644</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.233</v>
+        <v>-1.8676</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.231</v>
+        <v>-0.2115</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.699</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3725</v>
+        <v>-0.3589</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.8025</v>
+        <v>-10.4081</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.48</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1047</v>
+        <v>1.1178</v>
       </c>
       <c r="J192" t="n">
-        <v>25.4081</v>
+        <v>25.7094</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.17</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4955</v>
+        <v>0.4552</v>
       </c>
       <c r="J193" t="n">
-        <v>11.3965</v>
+        <v>10.4696</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0876</v>
+        <v>0.0693</v>
       </c>
       <c r="J194" t="n">
-        <v>2.0148</v>
+        <v>1.5939</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.359</v>
+        <v>-0.3164</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.257</v>
+        <v>-7.2772</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.86</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4617</v>
+        <v>-0.4192</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.6191</v>
+        <v>-9.6416</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3488</v>
+        <v>0.2958</v>
       </c>
       <c r="J197" t="n">
-        <v>8.022399999999999</v>
+        <v>6.8034</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.11</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2912</v>
+        <v>0.2416</v>
       </c>
       <c r="J198" t="n">
-        <v>6.6976</v>
+        <v>5.5568</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.84</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.204</v>
+        <v>-0.1841</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.692</v>
+        <v>-4.2343</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2736</v>
+        <v>-0.2545</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.2928</v>
+        <v>-5.8535</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3304</v>
+        <v>-0.3139</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.5992</v>
+        <v>-7.2197</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.29</v>
       </c>
       <c r="I202" t="n">
-        <v>0.594</v>
+        <v>0.5364</v>
       </c>
       <c r="J202" t="n">
-        <v>13.068</v>
+        <v>11.8008</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.12</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2997</v>
+        <v>0.249</v>
       </c>
       <c r="J203" t="n">
-        <v>6.5934</v>
+        <v>5.478</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1062</v>
+        <v>0.0781</v>
       </c>
       <c r="J204" t="n">
-        <v>2.3364</v>
+        <v>1.7182</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.01</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0487</v>
+        <v>0.0325</v>
       </c>
       <c r="J205" t="n">
-        <v>1.0714</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.34</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6523</v>
+        <v>-0.6785</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.3506</v>
+        <v>-14.927</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.46</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0384</v>
+        <v>1.0426</v>
       </c>
       <c r="J207" t="n">
-        <v>22.8448</v>
+        <v>22.9372</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.39</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9203</v>
+        <v>0.9067</v>
       </c>
       <c r="J208" t="n">
-        <v>20.2466</v>
+        <v>19.9474</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.28</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>15.5122</v>
+        <v>14.9138</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4029</v>
+        <v>0.3699</v>
       </c>
       <c r="J210" t="n">
-        <v>8.863799999999999</v>
+        <v>8.1378</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2133</v>
+        <v>-0.1796</v>
       </c>
       <c r="J211" t="n">
-        <v>-4.6926</v>
+        <v>-3.9512</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.43</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8548</v>
+        <v>0.8202</v>
       </c>
       <c r="J212" t="n">
-        <v>17.096</v>
+        <v>16.404</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.05</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1777</v>
+        <v>0.1403</v>
       </c>
       <c r="J213" t="n">
-        <v>3.554</v>
+        <v>2.806</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.74</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2968</v>
+        <v>-0.2788</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.936</v>
+        <v>-5.576</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.57</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4508</v>
+        <v>-0.4446</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.016</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.51</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5029</v>
+        <v>-0.5031</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.058</v>
+        <v>-10.062</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.8</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4685</v>
+        <v>1.4985</v>
       </c>
       <c r="J217" t="n">
-        <v>29.37</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.62</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2406</v>
+        <v>1.2571</v>
       </c>
       <c r="J218" t="n">
-        <v>24.812</v>
+        <v>25.142</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.37</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8558</v>
       </c>
       <c r="J219" t="n">
-        <v>17.41</v>
+        <v>17.116</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1129</v>
+        <v>-0.0935</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.258</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6435</v>
+        <v>-0.6141</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.87</v>
+        <v>-12.282</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.65</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0974</v>
+        <v>1.0921</v>
       </c>
       <c r="J222" t="n">
-        <v>24.1428</v>
+        <v>24.0262</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.13</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3187</v>
+        <v>0.2667</v>
       </c>
       <c r="J223" t="n">
-        <v>7.0114</v>
+        <v>5.8674</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2386</v>
+        <v>-0.2184</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.2492</v>
+        <v>-4.8048</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.62</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.416</v>
+        <v>-0.407</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.151999999999999</v>
+        <v>-8.954000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.58</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4512</v>
+        <v>-0.446</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.926399999999999</v>
+        <v>-9.811999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.72</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3864</v>
+        <v>1.4117</v>
       </c>
       <c r="J227" t="n">
-        <v>30.5008</v>
+        <v>31.0574</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7059</v>
+        <v>0.6784</v>
       </c>
       <c r="J228" t="n">
-        <v>15.5298</v>
+        <v>14.9248</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.28</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7059</v>
+        <v>0.6784</v>
       </c>
       <c r="J229" t="n">
-        <v>15.5298</v>
+        <v>14.9248</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.07</v>
       </c>
       <c r="I230" t="n">
-        <v>0.2219</v>
+        <v>0.1927</v>
       </c>
       <c r="J230" t="n">
-        <v>4.8818</v>
+        <v>4.2394</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.514</v>
+        <v>-0.476</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.308</v>
+        <v>-10.472</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4797</v>
+        <v>0.4218</v>
       </c>
       <c r="J232" t="n">
-        <v>10.0737</v>
+        <v>8.857799999999999</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4626</v>
+        <v>0.405</v>
       </c>
       <c r="J233" t="n">
-        <v>9.714600000000001</v>
+        <v>8.505000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.98</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0402</v>
+        <v>-0.0312</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.8442</v>
+        <v>-0.6552</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.75</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2967</v>
+        <v>-0.2784</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.2307</v>
+        <v>-5.8464</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4245</v>
+        <v>-0.4163</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.9145</v>
+        <v>-8.7423</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.37</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9246</v>
+        <v>0.9096</v>
       </c>
       <c r="J237" t="n">
-        <v>19.4166</v>
+        <v>19.1016</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.2</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5649</v>
+        <v>0.5258</v>
       </c>
       <c r="J238" t="n">
-        <v>11.8629</v>
+        <v>11.0418</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.189</v>
+        <v>0.1594</v>
       </c>
       <c r="J239" t="n">
-        <v>3.969</v>
+        <v>3.3474</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0125</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.2625</v>
+        <v>-0.1764</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.627</v>
+        <v>-0.5906</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.167</v>
+        <v>-12.4026</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.19</v>
       </c>
       <c r="I242" t="n">
-        <v>0.455</v>
+        <v>0.4011</v>
       </c>
       <c r="J242" t="n">
-        <v>10.01</v>
+        <v>8.824199999999999</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.1</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2843</v>
+        <v>0.2366</v>
       </c>
       <c r="J243" t="n">
-        <v>6.2546</v>
+        <v>5.2052</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.23</v>
+        <v>-0.2108</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.06</v>
+        <v>-4.6376</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.64</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3895</v>
+        <v>-0.3773</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.569000000000001</v>
+        <v>-8.300599999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4252</v>
+        <v>-0.4163</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.3544</v>
+        <v>-9.1586</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.38</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9353</v>
+        <v>0.9214</v>
       </c>
       <c r="J247" t="n">
-        <v>20.5766</v>
+        <v>20.2708</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.24</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6466</v>
+        <v>0.6111</v>
       </c>
       <c r="J248" t="n">
-        <v>14.2252</v>
+        <v>13.4442</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1198</v>
+        <v>0.0977</v>
       </c>
       <c r="J249" t="n">
-        <v>2.6356</v>
+        <v>2.1494</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.0175</v>
+        <v>-0.0127</v>
       </c>
       <c r="J250" t="n">
-        <v>-0.385</v>
+        <v>-0.2794</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3636</v>
+        <v>-0.3212</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.9992</v>
+        <v>-7.0664</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.55</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6803</v>
+        <v>0.6086</v>
       </c>
       <c r="J252" t="n">
-        <v>15.6469</v>
+        <v>13.9978</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.16</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2524</v>
+        <v>0.2046</v>
       </c>
       <c r="J253" t="n">
-        <v>5.8052</v>
+        <v>4.7058</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.1</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1725</v>
+        <v>0.1355</v>
       </c>
       <c r="J254" t="n">
-        <v>3.9675</v>
+        <v>3.1165</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.09</v>
       </c>
       <c r="I255" t="n">
-        <v>0.158</v>
+        <v>0.1233</v>
       </c>
       <c r="J255" t="n">
-        <v>3.634</v>
+        <v>2.8359</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.97</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0717</v>
+        <v>-0.0574</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.6491</v>
+        <v>-1.3202</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.11</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2351</v>
+        <v>0.2206</v>
       </c>
       <c r="J257" t="n">
-        <v>5.4073</v>
+        <v>5.0738</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0147</v>
+        <v>0.0121</v>
       </c>
       <c r="J258" t="n">
-        <v>0.3381</v>
+        <v>0.2783</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.84</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2012</v>
+        <v>-0.1819</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.6276</v>
+        <v>-4.1837</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.77</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2704</v>
+        <v>-0.2514</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.2192</v>
+        <v>-5.7822</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3456</v>
+        <v>-0.33</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.9488</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.02</v>
       </c>
       <c r="I262" t="n">
-        <v>0.1142</v>
+        <v>0.0887</v>
       </c>
       <c r="J262" t="n">
-        <v>2.284</v>
+        <v>1.774</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.86</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1754</v>
+        <v>-0.1588</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.508</v>
+        <v>-3.176</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2255</v>
+        <v>-0.2078</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.51</v>
+        <v>-4.156</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.76</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2729</v>
+        <v>-0.2551</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.458</v>
+        <v>-5.102</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.61</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4104</v>
+        <v>-0.3997</v>
       </c>
       <c r="J266" t="n">
-        <v>-8.208</v>
+        <v>-7.994</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.73</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3971</v>
+        <v>1.423</v>
       </c>
       <c r="J267" t="n">
-        <v>27.942</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.33</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8041</v>
+        <v>0.7819</v>
       </c>
       <c r="J268" t="n">
-        <v>16.082</v>
+        <v>15.638</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.2</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5399</v>
+        <v>0.5081</v>
       </c>
       <c r="J269" t="n">
-        <v>10.798</v>
+        <v>10.162</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.05</v>
       </c>
       <c r="I270" t="n">
-        <v>0.1613</v>
+        <v>0.1354</v>
       </c>
       <c r="J270" t="n">
-        <v>3.226</v>
+        <v>2.708</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3054</v>
+        <v>-0.2669</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.108</v>
+        <v>-5.338</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.54</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1247</v>
+        <v>1.1394</v>
       </c>
       <c r="J272" t="n">
-        <v>20.2446</v>
+        <v>20.5092</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.51</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0855</v>
+        <v>1.0988</v>
       </c>
       <c r="J273" t="n">
-        <v>19.539</v>
+        <v>19.7784</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.5</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0723</v>
+        <v>1.0845</v>
       </c>
       <c r="J274" t="n">
-        <v>19.3014</v>
+        <v>19.521</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.21</v>
       </c>
       <c r="I275" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5129</v>
       </c>
       <c r="J275" t="n">
-        <v>9.734400000000001</v>
+        <v>9.232200000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>1.2</v>
       </c>
       <c r="I276" t="n">
-        <v>0.5188</v>
+        <v>0.4901</v>
       </c>
       <c r="J276" t="n">
-        <v>9.3384</v>
+        <v>8.8218</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.98</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.0107</v>
+        <v>-0.0019</v>
       </c>
       <c r="J277" t="n">
-        <v>-0.1926</v>
+        <v>-0.0342</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.79</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2396</v>
+        <v>-0.2237</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.3128</v>
+        <v>-4.0266</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.77</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2587</v>
+        <v>-0.2429</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.6566</v>
+        <v>-4.3722</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.65</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3673</v>
+        <v>-0.3538</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.6114</v>
+        <v>-6.3684</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4475</v>
+        <v>-0.4402</v>
       </c>
       <c r="J281" t="n">
-        <v>-8.055</v>
+        <v>-7.9236</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.29</v>
       </c>
       <c r="I282" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J282" t="n">
-        <v>27.1208</v>
+        <v>27.7452</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>2.05</v>
       </c>
       <c r="I283" t="n">
-        <v>1.7095</v>
+        <v>1.7579</v>
       </c>
       <c r="J283" t="n">
-        <v>23.933</v>
+        <v>24.6106</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.52</v>
       </c>
       <c r="I284" t="n">
-        <v>1.0825</v>
+        <v>1.1022</v>
       </c>
       <c r="J284" t="n">
-        <v>15.155</v>
+        <v>15.4308</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.1</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2522</v>
+        <v>0.2165</v>
       </c>
       <c r="J285" t="n">
-        <v>3.5308</v>
+        <v>3.031</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2286</v>
+        <v>-0.207</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.2004</v>
+        <v>-2.898</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.85</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.164</v>
+        <v>-0.1477</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.296</v>
+        <v>-2.0678</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.83</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1861</v>
+        <v>-0.1703</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.6054</v>
+        <v>-2.3842</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2075</v>
+        <v>-0.1923</v>
       </c>
       <c r="J289" t="n">
-        <v>-2.905</v>
+        <v>-2.6922</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.67</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3414</v>
+        <v>-0.329</v>
       </c>
       <c r="J290" t="n">
-        <v>-4.7796</v>
+        <v>-4.606</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.22</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7333</v>
+        <v>-0.7723</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.2662</v>
+        <v>-10.8122</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.97</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.0348</v>
+        <v>-0.0253</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.6264</v>
+        <v>-0.4554</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.89</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1392</v>
+        <v>-0.1238</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.5056</v>
+        <v>-2.2284</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.83</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.204</v>
+        <v>-0.1874</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.672</v>
+        <v>-3.3732</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.68</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3445</v>
+        <v>-0.3294</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.201</v>
+        <v>-5.9292</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.57</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4431</v>
+        <v>-0.4355</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.9758</v>
+        <v>-7.839</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>2.01</v>
       </c>
       <c r="I297" t="n">
-        <v>1.7222</v>
+        <v>1.7761</v>
       </c>
       <c r="J297" t="n">
-        <v>30.9996</v>
+        <v>31.9698</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.3</v>
       </c>
       <c r="I298" t="n">
-        <v>0.7368</v>
+        <v>0.7151</v>
       </c>
       <c r="J298" t="n">
-        <v>13.2624</v>
+        <v>12.8718</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.2</v>
       </c>
       <c r="I299" t="n">
-        <v>0.529</v>
+        <v>0.4995</v>
       </c>
       <c r="J299" t="n">
-        <v>9.522</v>
+        <v>8.991</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.19</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5067</v>
+        <v>0.4767</v>
       </c>
       <c r="J300" t="n">
-        <v>9.1206</v>
+        <v>8.5806</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.346</v>
+        <v>-0.3089</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.228</v>
+        <v>-5.5602</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.01</v>
       </c>
       <c r="I302" t="n">
-        <v>0.1557</v>
+        <v>0.1502</v>
       </c>
       <c r="J302" t="n">
-        <v>2.4912</v>
+        <v>2.4032</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.66</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.3478</v>
+        <v>-0.3367</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.5648</v>
+        <v>-5.3872</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.58</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.4167</v>
+        <v>-0.4078</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.6672</v>
+        <v>-6.5248</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.55</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.0896</v>
+        <v>-6.9744</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.44</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5427</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.636799999999999</v>
+        <v>-8.683199999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>2.15</v>
       </c>
       <c r="I307" t="n">
-        <v>1.8512</v>
+        <v>1.9156</v>
       </c>
       <c r="J307" t="n">
-        <v>29.6192</v>
+        <v>30.6496</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9635</v>
+        <v>0.9646</v>
       </c>
       <c r="J308" t="n">
-        <v>15.416</v>
+        <v>15.4336</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7986</v>
+        <v>0.7857</v>
       </c>
       <c r="J309" t="n">
-        <v>12.7776</v>
+        <v>12.5712</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5535</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J310" t="n">
-        <v>8.856</v>
+        <v>8.427199999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>1.13</v>
       </c>
       <c r="I311" t="n">
-        <v>0.3464</v>
+        <v>0.3137</v>
       </c>
       <c r="J311" t="n">
-        <v>5.5424</v>
+        <v>5.0192</v>
       </c>
     </row>
   </sheetData>
